--- a/AAII_Financials/Quarterly/IP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IP_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
   <si>
     <t>IP</t>
   </si>
@@ -656,416 +656,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4601000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4613000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4682000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5020000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5133000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5402000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5389000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5237000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5086000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4914000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4770000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4593000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>17565000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5123000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4866000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5352000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5498000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5568000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5667000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5643000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5951000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5901000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5833000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5621000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5711000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5517000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5383000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5132000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3797000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5266000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3282000</v>
+      </c>
+      <c r="E9" s="3">
         <v>3345000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3360000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3642000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3668000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3830000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3806000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3839000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3659000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3423000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3402000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3348000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>12339000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3541000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3427000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3732000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3669000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3766000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3902000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3932000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3800000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3889000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3923000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3946000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3702000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3705000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3749000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3635000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2712000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3622000</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1319000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1268000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1322000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1378000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1465000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1572000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1583000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1398000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1427000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1491000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1368000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1245000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5226000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1582000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1439000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1620000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1829000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1802000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1765000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1711000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2151000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2012000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1910000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1675000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2009000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1812000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1634000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1497000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1085000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1644000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1110,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1203,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,192 +1298,201 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
+        <v>99000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
         <v>72000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>93000</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>266000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-321000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>165000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>32000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>660000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>100000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>26000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>352000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>88000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>61000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>152000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-7000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-19000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>122000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>26000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>22000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>83000</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>347000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>7000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>51000</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>689000</v>
+      </c>
+      <c r="E15" s="3">
         <v>258000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>244000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>241000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>251000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>261000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>267000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>261000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>277000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>280000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>272000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>268000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1091000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>320000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>312000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>323000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>343000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>327000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>321000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>315000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>338000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>335000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>330000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>325000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>339000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>350000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>334000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>320000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>225000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>314000</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4861000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4310000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4356000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4722000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4790000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5030000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4851000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4901000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4981000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4485000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4613000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4320000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>16866000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4742000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4503000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5276000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4979000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4978000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5204000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5085000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5007000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5192000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5175000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5124000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4976000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4851000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5223000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4732000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3542000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4761000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-260000</v>
+      </c>
+      <c r="E18" s="3">
         <v>303000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>326000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>298000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>343000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>372000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>538000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>336000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>105000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>429000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>157000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>273000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>699000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>381000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>363000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>76000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>519000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>590000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>463000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>558000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>944000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>709000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>658000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>497000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>735000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>666000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>160000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>400000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>255000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>505000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,468 +1747,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>44000</v>
+      </c>
+      <c r="E20" s="3">
         <v>34000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>32000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>26000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>72000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>91000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>59000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>103000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>24000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>72000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>212000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>157000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-367000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>49000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>54000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>71000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>49000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>39000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>48000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>44000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-375000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>28000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>15000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>39000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-351000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>3000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>4000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>46000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>49000</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>473000</v>
+      </c>
+      <c r="E21" s="3">
         <v>595000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>602000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>565000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>666000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>724000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>864000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>700000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>406000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>819000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>675000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>739000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1619000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>750000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>729000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>470000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>911000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>956000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>832000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>917000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>907000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1072000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1003000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>861000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>732000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1028000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>520000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>749000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>629000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>868000</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>110000</v>
+      </c>
+      <c r="E22" s="3">
         <v>105000</v>
-      </c>
-      <c r="E22" s="3">
-        <v>103000</v>
       </c>
       <c r="F22" s="3">
         <v>103000</v>
       </c>
       <c r="G22" s="3">
+        <v>103000</v>
+      </c>
+      <c r="H22" s="3">
         <v>93000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>150000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>83000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>77000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>85000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>104000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>117000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>124000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>3000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>148000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>156000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>163000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>168000</v>
-      </c>
-      <c r="T22" s="3">
-        <v>177000</v>
       </c>
       <c r="U22" s="3">
         <v>177000</v>
       </c>
       <c r="V22" s="3">
+        <v>177000</v>
+      </c>
+      <c r="W22" s="3">
         <v>184000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>187000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>184000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>183000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>180000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>187000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>198000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>186000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>187000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>182000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>181000</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-326000</v>
+      </c>
+      <c r="E23" s="3">
         <v>232000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>255000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>221000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>322000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>313000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>514000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>362000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>44000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>397000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>252000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>306000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>329000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>282000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>261000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-16000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>400000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>452000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>334000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>418000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>382000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>553000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>490000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>356000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>197000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>457000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-23000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>217000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>119000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>373000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-61000</v>
+      </c>
+      <c r="E24" s="3">
         <v>39000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>33000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>48000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>148000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-575000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>96000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>95000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-5000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>59000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>46000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>88000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>176000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>50000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>67000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>94000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>262000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>137000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>128000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>106000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>145000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>119000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>130000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>89000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>13000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>136000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-87000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>73000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>54000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>107000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-265000</v>
+      </c>
+      <c r="E26" s="3">
         <v>193000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>222000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>173000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>174000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>888000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>418000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>267000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>49000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>338000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>206000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>218000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>153000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>232000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>194000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-110000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>138000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>315000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>206000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>312000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>237000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>434000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>360000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>267000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>184000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>321000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>64000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>144000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>65000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>266000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-284000</v>
+      </c>
+      <c r="E27" s="3">
         <v>192000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>222000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>172000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-81000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>887000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>416000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>267000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-196000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>432000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>308000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>267000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>230000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>204000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>266000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-141000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>166000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>344000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>292000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>424000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>314000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>526000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>428000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>361000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>248000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>366000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>84000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>192000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>111000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,49 +2600,52 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>-27000</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>13000</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="G29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-237000</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>64000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>95000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>93000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>303000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>432000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>124000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>82000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>252000</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>8</v>
@@ -2593,12 +2653,12 @@
       <c r="R29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S29" s="3">
+      <c r="S29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T29" s="3">
         <v>-1000</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
       <c r="U29" s="3">
         <v>0</v>
       </c>
@@ -2606,37 +2666,40 @@
         <v>0</v>
       </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>2000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>36000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-23000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>368000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>1212000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>29000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>17000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>107000</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2885,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-34000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-32000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-26000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-72000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-91000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-59000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-103000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-24000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-72000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-212000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-157000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>367000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-49000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-54000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-71000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-49000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-39000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-48000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-44000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>375000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-28000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-15000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-39000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>351000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>11000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-46000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-49000</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-284000</v>
+      </c>
+      <c r="E33" s="3">
         <v>165000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>235000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>172000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-318000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>951000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>511000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>360000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>107000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>864000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>432000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>349000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>482000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>204000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>266000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-141000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>165000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>344000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>292000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>424000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>316000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>562000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>405000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>729000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1460000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>395000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>80000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>209000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>218000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-284000</v>
+      </c>
+      <c r="E35" s="3">
         <v>165000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>235000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>172000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-318000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>951000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>511000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>360000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>107000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>864000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>432000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>349000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>482000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>204000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>266000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-141000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>165000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>344000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>292000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>424000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>316000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>562000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>405000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>729000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1460000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>395000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>80000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>209000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>218000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3437,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1113000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1149000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>746000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>636000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>804000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>511000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>826000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1031000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1295000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2122000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>706000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>787000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>595000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>678000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>847000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1239000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>511000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>697000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>787000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>641000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>589000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1026000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1073000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1141000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1018000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>998000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1041000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>998000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1033000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2562000</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3458,26 +3547,26 @@
       <c r="F42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
+      <c r="G42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>151000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>291000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>245000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
-        <v>4850000</v>
+        <v>0</v>
       </c>
       <c r="N42" s="3">
         <v>4850000</v>
@@ -3488,8 +3577,8 @@
       <c r="P42" s="3">
         <v>4850000</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>8</v>
+      <c r="Q42" s="3">
+        <v>4850000</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>8</v>
@@ -3506,8 +3595,8 @@
       <c r="V42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
+      <c r="W42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X42" s="3">
         <v>0</v>
@@ -3536,601 +3625,622 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3492000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3552000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3630000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3729000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3765000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3967000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3968000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3854000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3610000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3976000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4024000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3779000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3419000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3422000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3461000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3649000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3673000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3693000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3876000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3903000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3916000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3963000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3907000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3804000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3287000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3343000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3283000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3078000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2852000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2807000</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1889000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1929000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1911000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1939000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1942000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1976000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1897000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1746000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1814000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2053000</v>
-      </c>
-      <c r="M44" s="3">
-        <v>1828000</v>
       </c>
       <c r="N44" s="3">
         <v>1828000</v>
       </c>
       <c r="O44" s="3">
+        <v>1828000</v>
+      </c>
+      <c r="P44" s="3">
         <v>2050000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2007000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2010000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2002000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2208000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2194000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2224000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2301000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2241000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2130000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2050000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2057000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2313000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2465000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2361000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2394000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2233000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2222000</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>114000</v>
+      </c>
+      <c r="E45" s="3">
         <v>150000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>189000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>311000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>259000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>168000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>204000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>262000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>132000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1745000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>818000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>923000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>322000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>331000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>281000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>325000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>247000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>467000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>501000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>217000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>250000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>199000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>242000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>258000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1659000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>405000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>552000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>251000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>851000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>512000</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6608000</v>
+      </c>
+      <c r="E46" s="3">
         <v>6780000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6476000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6615000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6770000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6622000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7046000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7184000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7096000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9896000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12226000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12167000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>11236000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>11288000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6599000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>7215000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6639000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>7051000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>7388000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>7062000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6996000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7318000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7272000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7260000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>8277000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>7211000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>7237000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6721000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6670000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>8103000</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2475000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2492000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2486000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2485000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2480000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3215000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3214000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2888000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3026000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2983000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2888000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2972000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3435000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3352000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>8505000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>8463000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>8809000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>8735000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>8725000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>8844000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>8718000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>8680000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>8599000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>8546000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>7441000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>7383000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>7367000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>7348000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>7393000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>7353000</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>10598000</v>
+      </c>
+      <c r="E48" s="3">
         <v>10892000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10922000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10875000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10855000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10606000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10617000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10709000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10824000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>12068000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>12279000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>12367000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12987000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>13120000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>13304000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>13421000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>13829000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>13648000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>13775000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>13887000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13469000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13476000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>13589000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>13788000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13713000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>14533000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>14491000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>14520000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>13459000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>12652000</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3224000</v>
+      </c>
+      <c r="E49" s="3">
         <v>3233000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3245000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3253000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3261000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3345000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3124000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3128000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3130000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3274000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3317000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3242000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3315000</v>
-      </c>
-      <c r="P49" s="3">
-        <v>3304000</v>
       </c>
       <c r="Q49" s="3">
         <v>3304000</v>
@@ -4139,49 +4249,52 @@
         <v>3304000</v>
       </c>
       <c r="S49" s="3">
+        <v>3304000</v>
+      </c>
+      <c r="T49" s="3">
         <v>3347000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3412000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3441000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3393000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3374000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3371000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3378000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3414000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3411000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3420000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3409000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3402000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3364000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3362000</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4480,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>554000</v>
+        <v>356000</v>
       </c>
       <c r="E52" s="3">
         <v>554000</v>
       </c>
       <c r="F52" s="3">
+        <v>554000</v>
+      </c>
+      <c r="G52" s="3">
         <v>543000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>574000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1077000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1281000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1249000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1167000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1250000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>738000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>729000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>745000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>776000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>807000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>812000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>847000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1002000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1018000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>992000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1019000</v>
-      </c>
-      <c r="X52" s="3">
-        <v>958000</v>
       </c>
       <c r="Y52" s="3">
         <v>958000</v>
       </c>
       <c r="Z52" s="3">
+        <v>958000</v>
+      </c>
+      <c r="AA52" s="3">
         <v>1022000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1061000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1266000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1373000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1310000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2207000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1131000</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>23261000</v>
+      </c>
+      <c r="E54" s="3">
         <v>23951000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>23683000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>23771000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>23940000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>24865000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>25282000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>25158000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>25243000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>29471000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>31448000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>31477000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>31718000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>31840000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>32519000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>33215000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>33471000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>33848000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>34347000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>34178000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>33576000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>33803000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>33796000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>34030000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>33903000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>33813000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>33877000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>33301000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>33093000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>32601000</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,560 +4837,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2442000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2363000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2394000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2541000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2708000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2668000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2678000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2657000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2606000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2704000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2565000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2354000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2320000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2226000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2206000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2379000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2423000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2349000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2498000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2518000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2413000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2510000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2478000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2534000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2458000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2408000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2362000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2380000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2199000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2031000</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>138000</v>
+      </c>
+      <c r="E58" s="3">
         <v>120000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>248000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>367000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>763000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>616000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>293000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>197000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>196000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>233000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>116000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>31000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>29000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>179000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>33000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>664000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>168000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>402000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>676000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>809000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>639000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>555000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>684000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>587000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>311000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>958000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>824000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>454000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>239000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>78000</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1379000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1399000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1425000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1358000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1529000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1521000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1381000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1288000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1342000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1761000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5954000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6005000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5935000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6071000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6091000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6299000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6055000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1978000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1875000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1626000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1642000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1538000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1456000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1344000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2333000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1503000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1816000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1433000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1631000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1432000</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3959000</v>
+      </c>
+      <c r="E60" s="3">
         <v>3882000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4067000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4266000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5000000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4805000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4352000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4142000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4144000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4698000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8635000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8390000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8284000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8476000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8330000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>9342000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8646000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4729000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5049000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4953000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4694000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4603000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4618000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4465000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5102000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4869000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5002000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4267000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4069000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3541000</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5455000</v>
+      </c>
+      <c r="E61" s="3">
         <v>5549000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5572000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5471000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4816000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4766000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5275000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5468000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5383000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8241000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7073000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7954000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>8064000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>8525000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>9432000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>9561000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>9597000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>9957000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>10050000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>9965000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>10015000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>10700000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>10805000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>10759000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>10846000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>11373000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>10392000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>10823000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>11075000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>10823000</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5492000</v>
+      </c>
+      <c r="E62" s="3">
         <v>5638000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5640000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5645000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5627000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5806000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6612000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6661000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6634000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6909000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7386000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7362000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7502000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7743000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7697000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7451000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7510000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>11706000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>11749000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>11791000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>11484000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>11442000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>11509000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>11541000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>11414000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>12638000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>13918000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>13617000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>13590000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>14008000</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14906000</v>
+      </c>
+      <c r="E66" s="3">
         <v>15069000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>15279000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>15382000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>15443000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>15377000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>16239000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16271000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>16161000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>19849000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>23096000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>23719000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>23864000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>24747000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>25462000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>26358000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>25758000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>26407000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>26865000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>26732000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>26214000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>26763000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>26952000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>26785000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>27381000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>28899000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>29332000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>28726000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>28752000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>28392000</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6200,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>9938000</v>
+        <v>9491000</v>
       </c>
       <c r="E72" s="3">
         <v>9938000</v>
       </c>
       <c r="F72" s="3">
+        <v>9938000</v>
+      </c>
+      <c r="G72" s="3">
         <v>9866000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9855000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>10340000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9557000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9218000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9029000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9103000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>8442000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8214000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8070000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>8122000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>8123000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>8062000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8408000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8447000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>8302000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>8211000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>7465000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>7353000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6988000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6783000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6180000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>4918000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>4717000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>4832000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>4818000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4793000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8355000</v>
+      </c>
+      <c r="E76" s="3">
         <v>8882000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8404000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8389000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8497000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9488000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9043000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8887000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9082000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9622000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8352000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7758000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7854000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7093000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7057000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6857000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7713000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7441000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7482000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7446000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7362000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7040000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>6844000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7245000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6522000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4914000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4545000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4575000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4341000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4209000</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-284000</v>
+      </c>
+      <c r="E81" s="3">
         <v>165000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>235000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>172000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-318000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>951000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>511000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>360000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>107000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>864000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>432000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>349000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>482000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>204000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>266000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-141000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>165000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>344000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>292000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>424000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>316000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>562000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>405000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>729000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1460000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>395000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>80000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>209000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>218000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7002,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>689000</v>
+      </c>
+      <c r="E83" s="3">
         <v>258000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>244000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>241000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>251000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>261000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>267000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>261000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>277000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>318000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>306000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>309000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1287000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>320000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>312000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>323000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>343000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>327000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>321000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>315000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>338000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>335000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>330000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>325000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>348000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>373000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>357000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>345000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>328000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>314000</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>492000</v>
+      </c>
+      <c r="E89" s="3">
         <v>468000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>528000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>345000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>761000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>435000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>390000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>588000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>107000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>690000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>775000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>458000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3061000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>737000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>886000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>640000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>947000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>884000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1046000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>733000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>821000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>941000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>801000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>663000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1188000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-705000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>641000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>633000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>912000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>341000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7702,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-305000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-228000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-267000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-341000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-322000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-238000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-186000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-185000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-201000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-126000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-133000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-89000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-751000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-119000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-252000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-286000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-363000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-285000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-335000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-293000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-286000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-357000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-440000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-489000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-456000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-271000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-290000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-374000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-445000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-266000</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7985,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-310000</v>
+      </c>
+      <c r="E94" s="3">
         <v>245000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-264000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-339000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-315000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-76000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-37000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-180000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-130000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>5598000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>328000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>258000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-269000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>134000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-299000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-35000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-306000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-279000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-421000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-294000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-259000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-346000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-475000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-489000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-383000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-278000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-330000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-400000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2527000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-279000</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7897,73 +8130,73 @@
         <v>-160000</v>
       </c>
       <c r="F96" s="3">
+        <v>-160000</v>
+      </c>
+      <c r="G96" s="3">
         <v>-162000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-164000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-165000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-170000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-174000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-178000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-199000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-201000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-202000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-806000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-202000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-201000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-202000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-201000</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-197000</v>
       </c>
       <c r="U96" s="3">
         <v>-197000</v>
       </c>
       <c r="V96" s="3">
-        <v>-201000</v>
+        <v>-197000</v>
       </c>
       <c r="W96" s="3">
         <v>-201000</v>
       </c>
       <c r="X96" s="3">
+        <v>-201000</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-195000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-196000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-197000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-196000</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-191000</v>
       </c>
       <c r="AC96" s="3">
         <v>-191000</v>
@@ -7972,13 +8205,16 @@
         <v>-191000</v>
       </c>
       <c r="AE96" s="3">
+        <v>-191000</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-190000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-181000</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8495,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-222000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-306000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-230000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-108000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-159000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-669000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-643000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-583000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2301000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3359000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1211000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-504000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2700000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1042000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-982000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>165000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-842000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-671000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-487000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-389000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1000000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-636000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-354000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-56000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-779000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>930000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-266000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-284000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>104000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1232000</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>4000</v>
-      </c>
-      <c r="F101" s="3">
-        <v>6000</v>
       </c>
       <c r="G101" s="3">
         <v>6000</v>
       </c>
       <c r="H101" s="3">
+        <v>6000</v>
+      </c>
+      <c r="I101" s="3">
         <v>-5000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-3000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-14000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>27000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-20000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-8000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>3000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-42000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>15000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-24000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>8000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>2000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-6000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-40000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>5000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>10000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>16000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-18000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="E102" s="3">
         <v>403000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>38000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-96000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>293000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-315000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-293000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-176000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2326000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2915000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-81000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>192000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>84000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-169000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-392000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>728000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-186000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-90000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>146000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>52000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-437000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-47000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-68000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>123000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>20000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-43000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>43000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-35000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1529000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1308000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
   <si>
     <t>IP</t>
   </si>
@@ -656,428 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4619000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4601000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4613000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4682000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5020000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5133000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5402000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5389000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5237000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5086000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4914000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4770000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4593000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>17565000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5123000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4866000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5352000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5498000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5568000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5667000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5643000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5951000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5901000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5833000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5621000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5711000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5517000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5383000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5132000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3797000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5266000</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3424000</v>
+      </c>
+      <c r="E9" s="3">
         <v>3282000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3345000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3360000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3642000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3668000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3830000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3806000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3839000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3659000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3423000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3402000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3348000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>12339000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3541000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3427000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3732000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3669000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3766000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3902000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3932000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3800000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3889000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3923000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3946000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3702000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3705000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3749000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3635000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2712000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3622000</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1195000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1319000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1268000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1322000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1378000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1465000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1572000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1583000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1398000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1427000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1491000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1368000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1245000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5226000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1582000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1439000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1620000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1829000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1802000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1765000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1711000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2151000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2012000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1910000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1675000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2009000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1812000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1634000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1497000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1085000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1644000</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1206,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,198 +1318,207 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E14" s="3">
         <v>99000</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
+      <c r="F14" s="3">
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>72000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>93000</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>266000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-321000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>165000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>32000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>660000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>100000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>26000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>352000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>88000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>61000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>152000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-7000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>122000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>26000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>22000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>83000</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>347000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>7000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>51000</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>278000</v>
+      </c>
+      <c r="E15" s="3">
         <v>689000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>258000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>244000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>241000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>251000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>261000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>267000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>261000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>277000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>280000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>272000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>268000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1091000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>320000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>312000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>323000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>343000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>327000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>321000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>315000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>338000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>335000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>330000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>325000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>339000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>350000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>334000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>320000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>225000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>314000</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4495000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4861000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4310000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4356000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4722000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4790000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5030000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4851000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4901000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4981000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4485000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4613000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4320000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>16866000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4742000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4503000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5276000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4979000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4978000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5204000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5085000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5007000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5192000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5175000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5124000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4976000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4851000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5223000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4732000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3542000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4761000</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>124000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-260000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>303000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>326000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>298000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>343000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>372000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>538000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>336000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>105000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>429000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>157000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>273000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>699000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>381000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>363000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>76000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>519000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>590000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>463000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>558000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>944000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>709000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>658000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>497000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>735000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>666000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>160000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>400000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>255000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>505000</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,483 +1781,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>70000</v>
+      </c>
+      <c r="E20" s="3">
         <v>44000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>34000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>32000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>26000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>72000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>91000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>59000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>103000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>24000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>72000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>212000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>157000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-367000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>49000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>54000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>71000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>49000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>39000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>48000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>44000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-375000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>28000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>15000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>39000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-351000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-11000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>3000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>4000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>46000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>49000</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>472000</v>
+      </c>
+      <c r="E21" s="3">
         <v>473000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>595000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>602000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>565000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>666000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>724000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>864000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>700000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>406000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>819000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>675000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>739000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1619000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>750000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>729000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>470000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>911000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>956000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>832000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>917000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>907000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1072000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1003000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>861000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>732000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1028000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>520000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>749000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>629000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>868000</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>109000</v>
+      </c>
+      <c r="E22" s="3">
         <v>110000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>105000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>103000</v>
       </c>
       <c r="G22" s="3">
         <v>103000</v>
       </c>
       <c r="H22" s="3">
+        <v>103000</v>
+      </c>
+      <c r="I22" s="3">
         <v>93000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>150000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>83000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>77000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>85000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>104000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>117000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>124000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>3000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>148000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>156000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>163000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>168000</v>
-      </c>
-      <c r="U22" s="3">
-        <v>177000</v>
       </c>
       <c r="V22" s="3">
         <v>177000</v>
       </c>
       <c r="W22" s="3">
+        <v>177000</v>
+      </c>
+      <c r="X22" s="3">
         <v>184000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>187000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>184000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>183000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>180000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>187000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>198000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>186000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>187000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>182000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>181000</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>85000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-326000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>232000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>255000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>221000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>322000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>313000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>514000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>362000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>44000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>397000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>252000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>306000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>329000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>282000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>261000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-16000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>400000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>452000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>334000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>418000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>382000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>553000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>490000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>356000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>197000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>457000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-23000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>217000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>119000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>373000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-61000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>39000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>33000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>48000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>148000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-575000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>96000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>95000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-5000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>59000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>46000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>88000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>176000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>50000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>67000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>94000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>262000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>137000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>128000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>106000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>145000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>119000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>130000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>89000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>13000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>136000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-87000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>73000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>54000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>107000</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-265000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>193000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>222000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>173000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>174000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>888000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>418000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>267000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>49000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>338000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>206000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>218000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>153000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>232000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>194000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-110000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>138000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>315000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>206000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>312000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>237000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>434000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>360000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>267000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>184000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>321000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>64000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>144000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>65000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>266000</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>56000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-284000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>192000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>222000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>172000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-81000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>887000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>416000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>267000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-196000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>432000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>308000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>267000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>230000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>204000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>266000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-141000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>166000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>344000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>292000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>424000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>314000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>526000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>428000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>361000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>248000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>366000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>84000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>192000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>111000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2612,43 +2673,43 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>-27000</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>13000</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="H29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-237000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>64000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>95000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>93000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>303000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>432000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>124000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>82000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>252000</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>8</v>
@@ -2656,12 +2717,12 @@
       <c r="S29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T29" s="3">
+      <c r="T29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U29" s="3">
         <v>-1000</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
       <c r="V29" s="3">
         <v>0</v>
       </c>
@@ -2669,37 +2730,40 @@
         <v>0</v>
       </c>
       <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
         <v>2000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>36000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-23000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>368000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>1212000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>29000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>17000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>107000</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,198 +2955,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-70000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-44000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-34000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-32000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-26000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-72000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-91000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-59000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-103000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-24000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-72000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-212000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-157000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>367000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-49000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-54000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-71000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-49000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-39000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-48000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-44000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>375000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-28000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-15000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-39000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>351000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>11000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-46000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-49000</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>56000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-284000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>165000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>235000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>172000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-318000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>951000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>511000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>360000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>107000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>864000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>432000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>349000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>482000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>204000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>266000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-141000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>165000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>344000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>292000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>424000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>316000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>562000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>405000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>729000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1460000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>395000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>80000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>209000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>218000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>56000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-284000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>165000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>235000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>172000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-318000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>951000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>511000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>360000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>107000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>864000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>432000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>349000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>482000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>204000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>266000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-141000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>165000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>344000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>292000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>424000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>316000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>562000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>405000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>729000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1460000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>395000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>80000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>209000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>218000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,103 +3524,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1070000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1113000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1149000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>746000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>636000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>804000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>511000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>826000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1031000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1295000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2122000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>706000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>787000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>595000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>678000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>847000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1239000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>511000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>697000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>787000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>641000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>589000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1026000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1073000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1141000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1018000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>998000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1041000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>998000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1033000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2562000</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3550,26 +3640,26 @@
       <c r="G42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
+      <c r="H42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>151000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>291000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>245000</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
-        <v>4850000</v>
+        <v>0</v>
       </c>
       <c r="O42" s="3">
         <v>4850000</v>
@@ -3580,8 +3670,8 @@
       <c r="Q42" s="3">
         <v>4850000</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>8</v>
+      <c r="R42" s="3">
+        <v>4850000</v>
       </c>
       <c r="S42" s="3" t="s">
         <v>8</v>
@@ -3598,8 +3688,8 @@
       <c r="W42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
+      <c r="X42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y42" s="3">
         <v>0</v>
@@ -3628,622 +3718,643 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3478000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3492000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3552000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3630000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3729000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3765000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3967000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3968000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3854000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3610000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3976000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4024000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3779000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3419000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3422000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3461000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3649000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3673000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3693000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3876000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3903000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3916000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3963000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3907000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3804000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3287000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3343000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3283000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3078000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2852000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2807000</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1771000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1889000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1929000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1911000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1939000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1942000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1976000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1897000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1746000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1814000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2053000</v>
-      </c>
-      <c r="N44" s="3">
-        <v>1828000</v>
       </c>
       <c r="O44" s="3">
         <v>1828000</v>
       </c>
       <c r="P44" s="3">
+        <v>1828000</v>
+      </c>
+      <c r="Q44" s="3">
         <v>2050000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2007000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2010000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2002000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2208000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2194000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2224000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2301000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2241000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2130000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2050000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2057000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2313000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2465000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2361000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2394000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2233000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2222000</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>140000</v>
+      </c>
+      <c r="E45" s="3">
         <v>114000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>150000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>189000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>311000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>259000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>168000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>204000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>262000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>132000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1745000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>818000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>923000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>322000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>331000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>281000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>325000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>247000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>467000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>501000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>217000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>250000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>199000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>242000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>258000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1659000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>405000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>552000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>251000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>851000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>512000</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6459000</v>
+      </c>
+      <c r="E46" s="3">
         <v>6608000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6780000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6476000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6615000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6770000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6622000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7046000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7184000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7096000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9896000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12226000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12167000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>11236000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>11288000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6599000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>7215000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6639000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>7051000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>7388000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>7062000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6996000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7318000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7272000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>7260000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>8277000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>7211000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>7237000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6721000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>6670000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>8103000</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2477000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2475000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2492000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2486000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2485000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2480000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3215000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3214000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2888000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3026000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2983000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2888000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2972000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3435000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3352000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>8505000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>8463000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>8809000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>8735000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>8725000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>8844000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>8718000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>8680000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>8599000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>8546000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>7441000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>7383000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>7367000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>7348000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>7393000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>7353000</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>10472000</v>
+      </c>
+      <c r="E48" s="3">
         <v>10598000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10892000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10922000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10875000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10855000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10606000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10617000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10709000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10824000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>12068000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>12279000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12367000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12987000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>13120000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>13304000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>13421000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>13829000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>13648000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>13775000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13887000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13469000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>13476000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>13589000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13788000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13713000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>14533000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>14491000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>14520000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>13459000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>12652000</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3215000</v>
+      </c>
+      <c r="E49" s="3">
         <v>3224000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3233000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3245000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3253000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3261000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3345000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3124000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3128000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3130000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3274000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3317000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3242000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3315000</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>3304000</v>
       </c>
       <c r="R49" s="3">
         <v>3304000</v>
@@ -4252,49 +4363,52 @@
         <v>3304000</v>
       </c>
       <c r="T49" s="3">
+        <v>3304000</v>
+      </c>
+      <c r="U49" s="3">
         <v>3347000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3412000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3441000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3393000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3374000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3371000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3378000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3414000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3411000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3420000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3409000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3402000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3364000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3362000</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,103 +4600,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>405000</v>
+      </c>
+      <c r="E52" s="3">
         <v>356000</v>
-      </c>
-      <c r="E52" s="3">
-        <v>554000</v>
       </c>
       <c r="F52" s="3">
         <v>554000</v>
       </c>
       <c r="G52" s="3">
+        <v>554000</v>
+      </c>
+      <c r="H52" s="3">
         <v>543000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>574000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1077000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1281000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1249000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1167000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1250000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>738000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>729000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>745000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>776000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>807000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>812000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>847000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1002000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1018000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>992000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1019000</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>958000</v>
       </c>
       <c r="Z52" s="3">
         <v>958000</v>
       </c>
       <c r="AA52" s="3">
+        <v>958000</v>
+      </c>
+      <c r="AB52" s="3">
         <v>1022000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1061000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1266000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1373000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1310000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2207000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1131000</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>23028000</v>
+      </c>
+      <c r="E54" s="3">
         <v>23261000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>23951000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>23683000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>23771000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>23940000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>24865000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>25282000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>25158000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>25243000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>29471000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>31448000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>31477000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>31718000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>31840000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>32519000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>33215000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>33471000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>33848000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>34347000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>34178000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>33576000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>33803000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>33796000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>34030000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>33903000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>33813000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>33877000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>33301000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>33093000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>32601000</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,103 +4968,107 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2322000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2442000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2363000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2394000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2541000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2708000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2668000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2678000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2657000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2606000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2704000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2565000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2354000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2320000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2226000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2206000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2379000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2423000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2349000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2498000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2518000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2413000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2510000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2478000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2534000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2458000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2408000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2362000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2380000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2199000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2031000</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4942,474 +5076,489 @@
         <v>138000</v>
       </c>
       <c r="E58" s="3">
+        <v>138000</v>
+      </c>
+      <c r="F58" s="3">
         <v>120000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>248000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>367000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>763000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>616000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>293000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>197000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>196000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>233000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>116000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>31000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>29000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>179000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>33000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>664000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>168000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>402000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>676000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>809000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>639000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>555000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>684000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>587000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>311000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>958000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>824000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>454000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>239000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>78000</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1394000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1379000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1399000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1425000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1358000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1529000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1521000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1381000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1288000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1342000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1761000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5954000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6005000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5935000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6071000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6091000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6299000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>6055000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1978000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1875000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1626000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1642000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1538000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1456000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1344000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2333000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1503000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1816000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1433000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1631000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1432000</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3854000</v>
+      </c>
+      <c r="E60" s="3">
         <v>3959000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3882000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4067000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4266000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5000000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4805000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4352000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4142000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4144000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4698000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8635000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8390000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8284000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8476000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8330000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>9342000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8646000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4729000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5049000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4953000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4694000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4603000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4618000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4465000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>5102000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4869000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5002000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4267000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4069000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>3541000</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5453000</v>
+      </c>
+      <c r="E61" s="3">
         <v>5455000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5549000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5572000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5471000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4816000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4766000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5275000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5468000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5383000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8241000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7073000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7954000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>8064000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8525000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>9432000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>9561000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>9597000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>9957000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>10050000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>9965000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>10015000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>10700000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>10805000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>10759000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>10846000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>11373000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>10392000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>10823000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>11075000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>10823000</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5464000</v>
+      </c>
+      <c r="E62" s="3">
         <v>5492000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5638000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5640000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5645000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5627000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5806000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6612000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6661000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6634000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6909000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7386000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7362000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7502000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7743000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7697000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7451000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7510000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>11706000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>11749000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>11791000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>11484000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>11442000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>11509000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>11541000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>11414000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>12638000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>13918000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>13617000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>13590000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>14008000</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14771000</v>
+      </c>
+      <c r="E66" s="3">
         <v>14906000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>15069000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>15279000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>15382000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>15443000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>15377000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16239000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>16271000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>16161000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>19849000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>23096000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>23719000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>23864000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>24747000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>25462000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>26358000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>25758000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>26407000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>26865000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>26732000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>26214000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>26763000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>26952000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>26785000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>27381000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>28899000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>29332000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>28726000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>28752000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>28392000</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>9386000</v>
+      </c>
+      <c r="E72" s="3">
         <v>9491000</v>
-      </c>
-      <c r="E72" s="3">
-        <v>9938000</v>
       </c>
       <c r="F72" s="3">
         <v>9938000</v>
       </c>
       <c r="G72" s="3">
+        <v>9938000</v>
+      </c>
+      <c r="H72" s="3">
         <v>9866000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9855000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>10340000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9557000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9218000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9029000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9103000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8442000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8214000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>8070000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>8122000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>8123000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8062000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8408000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>8447000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>8302000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>8211000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>7465000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>7353000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6988000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6783000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6180000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>4918000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>4717000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>4832000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4818000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4793000</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8257000</v>
+      </c>
+      <c r="E76" s="3">
         <v>8355000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8882000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8404000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8389000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8497000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9488000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9043000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8887000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9082000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9622000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8352000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7758000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7854000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7093000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7057000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6857000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7713000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7441000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7482000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7446000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7362000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7040000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6844000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7245000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6522000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4914000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4545000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4575000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4341000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4209000</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>56000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-284000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>165000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>235000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>172000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-318000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>951000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>511000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>360000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>107000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>864000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>432000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>349000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>482000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>204000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>266000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-141000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>165000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>344000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>292000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>424000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>316000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>562000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>405000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>729000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1460000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>395000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>80000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>209000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>218000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,103 +7201,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>278000</v>
+      </c>
+      <c r="E83" s="3">
         <v>689000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>258000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>244000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>241000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>251000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>261000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>267000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>261000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>277000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>318000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>306000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>309000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1287000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>320000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>312000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>323000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>343000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>327000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>321000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>315000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>338000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>335000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>330000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>325000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>348000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>373000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>357000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>345000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>328000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>314000</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>395000</v>
+      </c>
+      <c r="E89" s="3">
         <v>492000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>468000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>528000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>345000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>761000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>435000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>390000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>588000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>107000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>690000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>775000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>458000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3061000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>737000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>886000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>640000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>947000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>884000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1046000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>733000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>821000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>941000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>801000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>663000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1188000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-705000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>641000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>633000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>912000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>341000</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,103 +7923,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-251000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-305000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-228000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-267000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-341000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-322000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-238000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-186000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-185000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-201000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-126000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-133000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-89000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-751000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-119000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-252000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-286000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-363000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-285000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-335000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-293000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-286000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-357000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-440000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-489000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-456000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-271000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-290000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-374000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-445000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-266000</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-247000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-310000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>245000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-264000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-339000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-315000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-76000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-37000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-180000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-130000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>5598000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>328000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>258000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-269000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>134000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-299000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-35000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-306000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-279000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-421000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-294000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-259000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-346000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-475000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-489000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-383000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-278000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-330000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-400000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2527000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-279000</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,13 +8351,14 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-160000</v>
+        <v>-161000</v>
       </c>
       <c r="E96" s="3">
         <v>-160000</v>
@@ -8133,73 +8367,73 @@
         <v>-160000</v>
       </c>
       <c r="G96" s="3">
+        <v>-160000</v>
+      </c>
+      <c r="H96" s="3">
         <v>-162000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-164000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-165000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-170000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-174000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-178000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-199000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-201000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-202000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-806000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-202000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-201000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-202000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-201000</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-197000</v>
       </c>
       <c r="V96" s="3">
         <v>-197000</v>
       </c>
       <c r="W96" s="3">
-        <v>-201000</v>
+        <v>-197000</v>
       </c>
       <c r="X96" s="3">
         <v>-201000</v>
       </c>
       <c r="Y96" s="3">
+        <v>-201000</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-195000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-196000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-197000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-196000</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-191000</v>
       </c>
       <c r="AD96" s="3">
         <v>-191000</v>
@@ -8208,13 +8442,16 @@
         <v>-191000</v>
       </c>
       <c r="AF96" s="3">
+        <v>-191000</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-190000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-181000</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,289 +8741,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-191000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-222000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-306000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-230000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-108000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-159000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-669000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-643000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-583000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2301000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3359000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1211000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-504000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2700000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1042000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-982000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>165000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-842000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-671000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-487000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-389000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1000000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-636000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-354000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-56000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-779000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>930000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-266000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-284000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>104000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1232000</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>4000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-4000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>4000</v>
-      </c>
-      <c r="G101" s="3">
-        <v>6000</v>
       </c>
       <c r="H101" s="3">
         <v>6000</v>
       </c>
       <c r="I101" s="3">
+        <v>6000</v>
+      </c>
+      <c r="J101" s="3">
         <v>-5000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-14000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>27000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-20000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>3000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-42000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>15000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-24000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>8000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>2000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-40000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>5000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>10000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>16000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-18000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-43000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-36000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>403000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>38000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-96000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>293000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-315000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-293000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-176000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2326000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2915000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-81000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>192000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>84000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-169000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-392000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>728000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-186000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-90000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>146000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>52000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-437000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-47000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-68000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>123000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>20000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-43000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>43000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-35000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1529000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1308000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
   <si>
     <t>IP</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4734000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4619000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4601000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4613000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4682000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5020000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5133000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5402000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5389000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5237000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5086000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4914000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4770000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4593000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>17565000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5123000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4866000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5352000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5498000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5568000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5667000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5643000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5951000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5901000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5833000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5621000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5711000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5517000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5383000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5132000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3797000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5266000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3360000</v>
+      </c>
+      <c r="E9" s="3">
         <v>3424000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3282000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3345000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3360000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3642000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3668000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3830000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3806000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3839000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3659000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3423000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3402000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3348000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>12339000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3541000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3427000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3732000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3669000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3766000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3902000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3932000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3800000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3889000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3923000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3946000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3702000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3705000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3749000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3635000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2712000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3622000</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1374000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1195000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1319000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1268000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1322000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1378000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1465000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1572000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1583000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1398000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1427000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1491000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1368000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1245000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5226000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1582000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1439000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1620000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1829000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1802000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1765000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1711000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2151000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2012000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1910000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1675000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2009000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1812000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1634000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1497000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1085000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1644000</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,204 +1338,213 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>3000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>99000</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
+      <c r="G14" s="3">
+        <v>0</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>72000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>93000</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>266000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-321000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>165000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>32000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>660000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>100000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>26000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>352000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>88000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>61000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>152000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-19000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>122000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>26000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>22000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>83000</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>347000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>7000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>51000</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>261000</v>
+      </c>
+      <c r="E15" s="3">
         <v>278000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>689000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>258000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>244000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>241000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>251000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>261000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>267000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>261000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>277000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>280000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>272000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>268000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1091000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>320000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>312000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>323000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>343000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>327000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>321000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>315000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>338000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>335000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>330000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>325000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>339000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>350000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>334000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>320000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>225000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>314000</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4488000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4495000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4861000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4310000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4356000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4722000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4790000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5030000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4851000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4901000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4981000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4485000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4613000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4320000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>16866000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4742000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4503000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5276000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4979000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4978000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5204000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5085000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5007000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5192000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5175000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5124000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4976000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4851000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5223000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4732000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3542000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4761000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>246000</v>
+      </c>
+      <c r="E18" s="3">
         <v>124000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-260000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>303000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>326000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>298000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>343000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>372000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>538000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>336000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>105000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>429000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>157000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>273000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>699000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>381000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>363000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>76000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>519000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>590000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>463000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>558000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>944000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>709000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>658000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>497000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>735000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>666000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>160000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>400000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>255000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>505000</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,498 +1815,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>67000</v>
+      </c>
+      <c r="E20" s="3">
         <v>70000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>44000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>34000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>32000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>26000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>72000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>91000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>59000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>103000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>24000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>72000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>212000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>157000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-367000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>49000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>54000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>71000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>49000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>39000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>48000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>44000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-375000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>28000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>15000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>39000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-351000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-11000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>3000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>4000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>46000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>49000</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>574000</v>
+      </c>
+      <c r="E21" s="3">
         <v>472000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>473000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>595000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>602000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>565000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>666000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>724000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>864000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>700000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>406000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>819000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>675000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>739000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1619000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>750000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>729000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>470000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>911000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>956000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>832000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>917000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>907000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1072000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1003000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>861000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>732000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1028000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>520000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>749000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>629000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>868000</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E22" s="3">
         <v>109000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>110000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>105000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>103000</v>
       </c>
       <c r="H22" s="3">
         <v>103000</v>
       </c>
       <c r="I22" s="3">
+        <v>103000</v>
+      </c>
+      <c r="J22" s="3">
         <v>93000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>150000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>83000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>77000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>85000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>104000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>117000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>124000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>3000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>148000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>156000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>163000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>168000</v>
-      </c>
-      <c r="V22" s="3">
-        <v>177000</v>
       </c>
       <c r="W22" s="3">
         <v>177000</v>
       </c>
       <c r="X22" s="3">
+        <v>177000</v>
+      </c>
+      <c r="Y22" s="3">
         <v>184000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>187000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>184000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>183000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>180000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>187000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>198000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>186000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>187000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>182000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>181000</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>206000</v>
+      </c>
+      <c r="E23" s="3">
         <v>85000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-326000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>232000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>255000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>221000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>322000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>313000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>514000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>362000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>44000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>397000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>252000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>306000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>329000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>282000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>261000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-16000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>400000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>452000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>334000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>418000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>382000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>553000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>490000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>356000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>197000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>457000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-23000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>217000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>119000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>373000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-293000</v>
+      </c>
+      <c r="E24" s="3">
         <v>27000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-61000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>39000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>33000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>48000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>148000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-575000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>96000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>95000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-5000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>59000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>46000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>88000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>176000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>50000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>67000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>94000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>262000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>137000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>128000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>106000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>145000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>119000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>130000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>89000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>13000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>136000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-87000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>73000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>54000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>107000</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>499000</v>
+      </c>
+      <c r="E26" s="3">
         <v>58000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-265000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>193000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>222000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>173000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>174000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>888000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>418000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>267000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>49000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>338000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>206000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>218000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>153000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>232000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>194000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-110000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>138000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>315000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>206000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>312000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>237000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>434000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>360000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>267000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>184000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>321000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>64000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>144000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>65000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>266000</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>498000</v>
+      </c>
+      <c r="E27" s="3">
         <v>56000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-284000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>192000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>222000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>172000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-81000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>887000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>416000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>267000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-196000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>432000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>308000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>267000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>230000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>204000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>266000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-141000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>166000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>344000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>292000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>424000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>314000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>526000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>428000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>361000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>248000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>366000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>84000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>192000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>111000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2676,43 +2737,43 @@
         <v>0</v>
       </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>-27000</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>13000</v>
       </c>
-      <c r="H29" s="3" t="s">
+      <c r="I29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-237000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>64000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>95000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>93000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>303000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>432000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>124000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>82000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>252000</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
@@ -2720,12 +2781,12 @@
       <c r="T29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U29" s="3">
+      <c r="U29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V29" s="3">
         <v>-1000</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
       <c r="W29" s="3">
         <v>0</v>
       </c>
@@ -2733,37 +2794,40 @@
         <v>0</v>
       </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>2000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>36000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-23000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>368000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>1212000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>29000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>17000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>107000</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-67000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-70000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-44000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-34000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-32000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-26000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-72000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-91000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-59000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-103000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-24000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-72000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-212000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-157000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>367000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-49000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-54000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-71000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-49000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-39000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-48000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-44000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>375000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-28000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-15000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-39000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>351000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>11000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-46000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-49000</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>498000</v>
+      </c>
+      <c r="E33" s="3">
         <v>56000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-284000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>165000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>235000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>172000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-318000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>951000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>511000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>360000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>107000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>864000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>432000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>349000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>482000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>204000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>266000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-141000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>165000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>344000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>292000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>424000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>316000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>562000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>405000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>729000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1460000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>395000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>80000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>209000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>218000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>498000</v>
+      </c>
+      <c r="E35" s="3">
         <v>56000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-284000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>165000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>235000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>172000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-318000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>951000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>511000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>360000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>107000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>864000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>432000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>349000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>482000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>204000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>266000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-141000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>165000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>344000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>292000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>424000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>316000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>562000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>405000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>729000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1460000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>395000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>80000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>209000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>218000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,123 +3611,127 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1049000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1070000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1113000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1149000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>746000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>636000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>804000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>511000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>826000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1031000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1295000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2122000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>706000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>787000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>595000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>678000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>847000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1239000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>511000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>697000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>787000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>641000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>589000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1026000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1073000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1141000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1018000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>998000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1041000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>998000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1033000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2562000</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>8</v>
+      <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
       </c>
       <c r="I42" s="3">
         <v>0</v>
@@ -3650,19 +3740,19 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>151000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>291000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>245000</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
-        <v>4850000</v>
+        <v>0</v>
       </c>
       <c r="P42" s="3">
         <v>4850000</v>
@@ -3673,8 +3763,8 @@
       <c r="R42" s="3">
         <v>4850000</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>8</v>
+      <c r="S42" s="3">
+        <v>4850000</v>
       </c>
       <c r="T42" s="3" t="s">
         <v>8</v>
@@ -3691,8 +3781,8 @@
       <c r="X42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y42" s="3">
-        <v>0</v>
+      <c r="Y42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z42" s="3">
         <v>0</v>
@@ -3721,643 +3811,664 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3633000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3478000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3492000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3552000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3630000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3729000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3765000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3967000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3968000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3854000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3610000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3976000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4024000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3779000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3419000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3422000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3461000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3649000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3673000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3693000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3876000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3903000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3916000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3963000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3907000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3804000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3287000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3343000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3283000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3078000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2852000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2807000</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1728000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1771000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1889000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1929000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1911000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1939000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1942000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1976000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1897000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1746000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1814000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2053000</v>
-      </c>
-      <c r="O44" s="3">
-        <v>1828000</v>
       </c>
       <c r="P44" s="3">
         <v>1828000</v>
       </c>
       <c r="Q44" s="3">
+        <v>1828000</v>
+      </c>
+      <c r="R44" s="3">
         <v>2050000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2007000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2010000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2002000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2208000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2194000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2224000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2301000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2241000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2130000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2050000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2057000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2313000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2465000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2361000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2394000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2233000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2222000</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>147000</v>
+      </c>
+      <c r="E45" s="3">
         <v>140000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>114000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>150000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>189000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>311000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>259000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>168000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>204000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>262000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>132000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1745000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>818000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>923000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>322000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>331000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>281000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>325000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>247000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>467000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>501000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>217000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>250000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>199000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>242000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>258000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1659000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>405000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>552000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>251000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>851000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>512000</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6557000</v>
+      </c>
+      <c r="E46" s="3">
         <v>6459000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6608000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6780000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6476000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6615000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6770000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6622000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7046000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7184000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7096000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9896000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12226000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12167000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>11236000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>11288000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6599000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>7215000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6639000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>7051000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>7388000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7062000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6996000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7318000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>7272000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>7260000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>8277000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>7211000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>7237000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>6721000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>6670000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>8103000</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2484000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2477000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2475000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2492000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2486000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2485000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2480000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3215000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3214000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2888000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3026000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2983000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2888000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2972000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3435000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3352000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>8505000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>8463000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>8809000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>8735000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>8725000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>8844000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>8718000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>8680000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>8599000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>8546000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>7441000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>7383000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>7367000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>7348000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>7393000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>7353000</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>10392000</v>
+      </c>
+      <c r="E48" s="3">
         <v>10472000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10598000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10892000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10922000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10875000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10855000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10606000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10617000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10709000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10824000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>12068000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12279000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12367000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12987000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>13120000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>13304000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>13421000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>13829000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>13648000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13775000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13887000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>13469000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>13476000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13589000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13788000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>13713000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>14533000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>14491000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>14520000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>13459000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>12652000</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3204000</v>
+      </c>
+      <c r="E49" s="3">
         <v>3215000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3224000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3233000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3245000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3253000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3261000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3345000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3124000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3128000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3130000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3274000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3317000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3242000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3315000</v>
-      </c>
-      <c r="R49" s="3">
-        <v>3304000</v>
       </c>
       <c r="S49" s="3">
         <v>3304000</v>
@@ -4366,49 +4477,52 @@
         <v>3304000</v>
       </c>
       <c r="U49" s="3">
+        <v>3304000</v>
+      </c>
+      <c r="V49" s="3">
         <v>3347000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3412000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3441000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3393000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3374000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3371000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3378000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3414000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3411000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3420000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3409000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3402000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3364000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3362000</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>426000</v>
+      </c>
+      <c r="E52" s="3">
         <v>405000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>356000</v>
-      </c>
-      <c r="F52" s="3">
-        <v>554000</v>
       </c>
       <c r="G52" s="3">
         <v>554000</v>
       </c>
       <c r="H52" s="3">
+        <v>554000</v>
+      </c>
+      <c r="I52" s="3">
         <v>543000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>574000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1077000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1281000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1249000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1167000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1250000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>738000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>729000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>745000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>776000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>807000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>812000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>847000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1002000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1018000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>992000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1019000</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>958000</v>
       </c>
       <c r="AA52" s="3">
         <v>958000</v>
       </c>
       <c r="AB52" s="3">
+        <v>958000</v>
+      </c>
+      <c r="AC52" s="3">
         <v>1022000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1061000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1266000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1373000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1310000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2207000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1131000</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>23063000</v>
+      </c>
+      <c r="E54" s="3">
         <v>23028000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>23261000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>23951000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>23683000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>23771000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>23940000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>24865000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>25282000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>25158000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>25243000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>29471000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>31448000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>31477000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>31718000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>31840000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>32519000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>33215000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>33471000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>33848000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>34347000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>34178000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>33576000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>33803000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>33796000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>34030000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>33903000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>33813000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>33877000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>33301000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>33093000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>32601000</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,596 +5099,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2350000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2322000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2442000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2363000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2394000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2541000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2708000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2668000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2678000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2657000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2606000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2704000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2565000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2354000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2320000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2226000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2206000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2379000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2423000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2349000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2498000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2518000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2413000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2510000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2478000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2534000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2458000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2408000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2362000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2380000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2199000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2031000</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>138000</v>
+        <v>259000</v>
       </c>
       <c r="E58" s="3">
         <v>138000</v>
       </c>
       <c r="F58" s="3">
+        <v>138000</v>
+      </c>
+      <c r="G58" s="3">
         <v>120000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>248000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>367000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>763000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>616000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>293000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>197000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>196000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>233000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>116000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>31000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>29000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>179000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>33000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>664000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>168000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>402000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>676000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>809000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>639000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>555000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>684000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>587000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>311000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>958000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>824000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>454000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>239000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>78000</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1505000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1394000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1379000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1399000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1425000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1358000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1529000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1521000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1381000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1288000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1342000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1761000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5954000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6005000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5935000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6071000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6091000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>6299000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>6055000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1978000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1875000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1626000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1642000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1538000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1456000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1344000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2333000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1503000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1816000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1433000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1631000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1432000</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4114000</v>
+      </c>
+      <c r="E60" s="3">
         <v>3854000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3959000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3882000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4067000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4266000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5000000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4805000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4352000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4142000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4144000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4698000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8635000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8390000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8284000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8476000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8330000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>9342000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8646000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4729000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5049000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4953000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4694000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4603000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4618000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4465000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5102000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4869000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5002000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4267000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4069000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>3541000</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5329000</v>
+      </c>
+      <c r="E61" s="3">
         <v>5453000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5455000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5549000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5572000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5471000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4816000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4766000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5275000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5468000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5383000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8241000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7073000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7954000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8064000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>8525000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>9432000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>9561000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>9597000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>9957000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>10050000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>9965000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>10015000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>10700000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>10805000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>10759000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>10846000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>11373000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>10392000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>10823000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>11075000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>10823000</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5025000</v>
+      </c>
+      <c r="E62" s="3">
         <v>5464000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5492000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5638000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5640000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5645000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5627000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5806000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6612000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6661000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6634000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6909000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7386000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7362000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7502000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7743000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7697000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7451000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7510000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>11706000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>11749000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>11791000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>11484000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>11442000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>11509000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>11541000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>11414000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>12638000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>13918000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>13617000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>13590000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>14008000</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14468000</v>
+      </c>
+      <c r="E66" s="3">
         <v>14771000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14906000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>15069000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>15279000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>15382000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>15443000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>15377000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>16239000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>16271000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>16161000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>19849000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>23096000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>23719000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>23864000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>24747000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>25462000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>26358000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>25758000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>26407000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>26865000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>26732000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>26214000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>26763000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>26952000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>26785000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>27381000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>28899000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>29332000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>28726000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>28752000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>28392000</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>9719000</v>
+      </c>
+      <c r="E72" s="3">
         <v>9386000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9491000</v>
-      </c>
-      <c r="F72" s="3">
-        <v>9938000</v>
       </c>
       <c r="G72" s="3">
         <v>9938000</v>
       </c>
       <c r="H72" s="3">
+        <v>9938000</v>
+      </c>
+      <c r="I72" s="3">
         <v>9866000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9855000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>10340000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9557000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9218000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9029000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9103000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8442000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>8214000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>8070000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>8122000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8123000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8062000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>8408000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>8447000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>8302000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>8211000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>7465000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>7353000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6988000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6783000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6180000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>4918000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>4717000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4832000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4818000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4793000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8595000</v>
+      </c>
+      <c r="E76" s="3">
         <v>8257000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8355000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8882000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8404000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8389000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8497000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9488000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9043000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8887000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9082000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9622000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8352000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7758000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7854000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7093000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7057000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>6857000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7713000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7441000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7482000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7446000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7362000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7040000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6844000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7245000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6522000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4914000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4545000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4575000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4341000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>4209000</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>498000</v>
+      </c>
+      <c r="E81" s="3">
         <v>56000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-284000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>165000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>235000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>172000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-318000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>951000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>511000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>360000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>107000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>864000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>432000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>349000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>482000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>204000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>266000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-141000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>165000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>344000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>292000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>424000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>316000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>562000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>405000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>729000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1460000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>395000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>80000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>209000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>218000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,106 +7400,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>261000</v>
+      </c>
+      <c r="E83" s="3">
         <v>278000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>689000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>258000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>244000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>241000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>251000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>261000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>267000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>261000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>277000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>318000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>306000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>309000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1287000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>320000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>312000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>323000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>343000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>327000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>321000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>315000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>338000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>335000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>330000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>325000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>348000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>373000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>357000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>345000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>328000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>314000</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>365000</v>
+      </c>
+      <c r="E89" s="3">
         <v>395000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>492000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>468000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>528000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>345000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>761000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>435000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>390000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>588000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>107000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>690000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>775000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>458000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3061000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>737000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>886000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>640000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>947000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>884000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1046000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>733000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>821000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>941000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>801000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>663000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1188000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-705000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>641000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>633000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>912000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>341000</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,106 +8144,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-198000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-251000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-305000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-228000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-267000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-341000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-322000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-238000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-186000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-185000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-201000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-126000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-133000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-89000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-751000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-119000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-252000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-286000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-363000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-285000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-335000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-293000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-286000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-357000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-440000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-489000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-456000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-271000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-290000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-374000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-445000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-266000</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-199000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-247000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-310000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>245000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-264000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-339000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-315000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-76000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-37000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-180000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-130000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>5598000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>328000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>258000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-269000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>134000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-299000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-35000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-306000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-279000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-421000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-294000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-259000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-346000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-475000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-489000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-383000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-278000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-330000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-400000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2527000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-279000</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,16 +8585,17 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-160000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-161000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>-160000</v>
       </c>
       <c r="F96" s="3">
         <v>-160000</v>
@@ -8370,73 +8604,73 @@
         <v>-160000</v>
       </c>
       <c r="H96" s="3">
+        <v>-160000</v>
+      </c>
+      <c r="I96" s="3">
         <v>-162000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-164000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-165000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-170000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-174000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-178000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-199000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-201000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-202000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-806000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-202000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-201000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-202000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-201000</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-197000</v>
       </c>
       <c r="W96" s="3">
         <v>-197000</v>
       </c>
       <c r="X96" s="3">
-        <v>-201000</v>
+        <v>-197000</v>
       </c>
       <c r="Y96" s="3">
         <v>-201000</v>
       </c>
       <c r="Z96" s="3">
+        <v>-201000</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-195000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-196000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-197000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-196000</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-191000</v>
       </c>
       <c r="AE96" s="3">
         <v>-191000</v>
@@ -8445,13 +8679,16 @@
         <v>-191000</v>
       </c>
       <c r="AG96" s="3">
+        <v>-191000</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-190000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-181000</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,298 +8987,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-174000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-191000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-222000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-306000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-230000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-108000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-159000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-669000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-643000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-583000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2301000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3359000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1211000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-504000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2700000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1042000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-982000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>165000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-842000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-671000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-487000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-389000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1000000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-636000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-354000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-56000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-779000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>930000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-266000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-284000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>104000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>1232000</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-13000</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>4000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-4000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>4000</v>
-      </c>
-      <c r="H101" s="3">
-        <v>6000</v>
       </c>
       <c r="I101" s="3">
         <v>6000</v>
       </c>
       <c r="J101" s="3">
+        <v>6000</v>
+      </c>
+      <c r="K101" s="3">
         <v>-5000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-14000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>27000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-8000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>2000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>3000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-42000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>15000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-24000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>8000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>2000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-40000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>5000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>10000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>16000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-18000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-43000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-36000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>403000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>38000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-96000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>293000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-315000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-293000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-176000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2326000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2915000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-81000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>192000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>84000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-169000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-392000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>728000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-186000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-90000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>146000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>52000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-437000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-47000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-68000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>123000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>20000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-43000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>43000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-35000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1529000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1308000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
   <si>
     <t>IP</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4686000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4734000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4619000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4601000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4613000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4682000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5020000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5133000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5402000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5389000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5237000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5086000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4914000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4770000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4593000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>17565000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5123000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4866000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5352000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5498000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5568000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5667000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5643000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5951000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5901000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5833000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5621000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5711000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5517000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5383000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5132000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3797000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>5266000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3329000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3335000</v>
+      </c>
+      <c r="F9" s="3">
+        <v>3424000</v>
+      </c>
+      <c r="G9" s="3">
+        <v>3282000</v>
+      </c>
+      <c r="H9" s="3">
+        <v>3316000</v>
+      </c>
+      <c r="I9" s="3">
         <v>3360000</v>
       </c>
-      <c r="E9" s="3">
-        <v>3424000</v>
-      </c>
-      <c r="F9" s="3">
-        <v>3282000</v>
-      </c>
-      <c r="G9" s="3">
-        <v>3345000</v>
-      </c>
-      <c r="H9" s="3">
-        <v>3360000</v>
-      </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3642000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3668000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3830000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3806000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3839000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3659000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3423000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3402000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3348000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>12339000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3541000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3427000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3732000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3669000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3766000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3902000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3932000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3800000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3889000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3923000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3946000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3702000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3705000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3749000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3635000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2712000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3622000</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1374000</v>
+        <v>1357000</v>
       </c>
       <c r="E10" s="3">
+        <v>1399000</v>
+      </c>
+      <c r="F10" s="3">
         <v>1195000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1319000</v>
       </c>
-      <c r="G10" s="3">
-        <v>1268000</v>
-      </c>
       <c r="H10" s="3">
+        <v>1297000</v>
+      </c>
+      <c r="I10" s="3">
         <v>1322000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1378000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1465000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1572000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1583000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1398000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1427000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1491000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1368000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1245000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5226000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1582000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1439000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1620000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1829000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1802000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1765000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1711000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2151000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2012000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1910000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1675000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2009000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1812000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1634000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1497000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1085000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1644000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,210 +1358,219 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="E14" s="3">
-        <v>3000</v>
+        <v>49000</v>
       </c>
       <c r="F14" s="3">
-        <v>99000</v>
+        <v>13000</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
+        <v>524000</v>
+      </c>
+      <c r="H14" s="3">
+        <v>29000</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>72000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>93000</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>266000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-321000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>165000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>32000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>660000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>100000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>26000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>352000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>88000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>61000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>152000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-19000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>122000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>26000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>22000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>83000</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>347000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>7000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>51000</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>267000</v>
+      </c>
+      <c r="E15" s="3">
         <v>261000</v>
       </c>
-      <c r="E15" s="3">
-        <v>278000</v>
-      </c>
       <c r="F15" s="3">
-        <v>689000</v>
+        <v>273000</v>
       </c>
       <c r="G15" s="3">
+        <v>267000</v>
+      </c>
+      <c r="H15" s="3">
         <v>258000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>244000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>241000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>251000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>261000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>267000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>261000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>277000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>280000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>272000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>268000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1091000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>320000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>312000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>323000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>343000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>327000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>321000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>315000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>338000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>335000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>330000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>325000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>339000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>350000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>334000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>320000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>225000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>314000</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4488000</v>
+        <v>4435000</v>
       </c>
       <c r="E17" s="3">
-        <v>4495000</v>
+        <v>4424000</v>
       </c>
       <c r="F17" s="3">
-        <v>4861000</v>
+        <v>4475000</v>
       </c>
       <c r="G17" s="3">
-        <v>4310000</v>
+        <v>4354000</v>
       </c>
       <c r="H17" s="3">
-        <v>4356000</v>
+        <v>4294000</v>
       </c>
       <c r="I17" s="3">
-        <v>4722000</v>
+        <v>4368000</v>
       </c>
       <c r="J17" s="3">
+        <v>4737000</v>
+      </c>
+      <c r="K17" s="3">
         <v>4790000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5030000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4851000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4901000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4981000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4485000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4613000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4320000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>16866000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4742000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4503000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5276000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4979000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4978000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5204000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5085000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5007000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5192000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5175000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5124000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4976000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4851000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5223000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4732000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3542000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4761000</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>246000</v>
+        <v>251000</v>
       </c>
       <c r="E18" s="3">
-        <v>124000</v>
+        <v>310000</v>
       </c>
       <c r="F18" s="3">
-        <v>-260000</v>
+        <v>144000</v>
       </c>
       <c r="G18" s="3">
-        <v>303000</v>
+        <v>247000</v>
       </c>
       <c r="H18" s="3">
-        <v>326000</v>
+        <v>319000</v>
       </c>
       <c r="I18" s="3">
-        <v>298000</v>
+        <v>314000</v>
       </c>
       <c r="J18" s="3">
+        <v>283000</v>
+      </c>
+      <c r="K18" s="3">
         <v>343000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>372000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>538000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>336000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>105000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>429000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>157000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>273000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>699000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>381000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>363000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>76000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>519000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>590000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>463000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>558000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>944000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>709000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>658000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>497000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>735000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>666000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>160000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>400000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>255000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>505000</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,513 +1849,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>67000</v>
+        <v>1000</v>
       </c>
       <c r="E20" s="3">
-        <v>70000</v>
+        <v>1000</v>
       </c>
       <c r="F20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G20" s="3">
+        <v>19000</v>
+      </c>
+      <c r="H20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K20" s="3">
+        <v>72000</v>
+      </c>
+      <c r="L20" s="3">
+        <v>91000</v>
+      </c>
+      <c r="M20" s="3">
+        <v>59000</v>
+      </c>
+      <c r="N20" s="3">
+        <v>103000</v>
+      </c>
+      <c r="O20" s="3">
+        <v>24000</v>
+      </c>
+      <c r="P20" s="3">
+        <v>72000</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>212000</v>
+      </c>
+      <c r="R20" s="3">
+        <v>157000</v>
+      </c>
+      <c r="S20" s="3">
+        <v>-367000</v>
+      </c>
+      <c r="T20" s="3">
+        <v>49000</v>
+      </c>
+      <c r="U20" s="3">
+        <v>54000</v>
+      </c>
+      <c r="V20" s="3">
+        <v>71000</v>
+      </c>
+      <c r="W20" s="3">
+        <v>49000</v>
+      </c>
+      <c r="X20" s="3">
+        <v>39000</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>48000</v>
+      </c>
+      <c r="Z20" s="3">
         <v>44000</v>
       </c>
-      <c r="G20" s="3">
-        <v>34000</v>
-      </c>
-      <c r="H20" s="3">
-        <v>32000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>26000</v>
-      </c>
-      <c r="J20" s="3">
-        <v>72000</v>
-      </c>
-      <c r="K20" s="3">
-        <v>91000</v>
-      </c>
-      <c r="L20" s="3">
-        <v>59000</v>
-      </c>
-      <c r="M20" s="3">
-        <v>103000</v>
-      </c>
-      <c r="N20" s="3">
-        <v>24000</v>
-      </c>
-      <c r="O20" s="3">
-        <v>72000</v>
-      </c>
-      <c r="P20" s="3">
-        <v>212000</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>157000</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-367000</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="AA20" s="3">
+        <v>-375000</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>28000</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>15000</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>39000</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>-351000</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AI20" s="3">
+        <v>46000</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>49000</v>
       </c>
-      <c r="T20" s="3">
-        <v>54000</v>
-      </c>
-      <c r="U20" s="3">
-        <v>71000</v>
-      </c>
-      <c r="V20" s="3">
-        <v>49000</v>
-      </c>
-      <c r="W20" s="3">
-        <v>39000</v>
-      </c>
-      <c r="X20" s="3">
-        <v>48000</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>44000</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>-375000</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>28000</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>15000</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>39000</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>-351000</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>-11000</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>3000</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>4000</v>
-      </c>
-      <c r="AH20" s="3">
-        <v>46000</v>
-      </c>
-      <c r="AI20" s="3">
-        <v>49000</v>
-      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>574000</v>
+        <v>517000</v>
       </c>
       <c r="E21" s="3">
-        <v>472000</v>
+        <v>570000</v>
       </c>
       <c r="F21" s="3">
-        <v>473000</v>
+        <v>415000</v>
       </c>
       <c r="G21" s="3">
-        <v>595000</v>
+        <v>495000</v>
       </c>
       <c r="H21" s="3">
-        <v>602000</v>
+        <v>576000</v>
       </c>
       <c r="I21" s="3">
-        <v>565000</v>
+        <v>558000</v>
       </c>
       <c r="J21" s="3">
+        <v>523000</v>
+      </c>
+      <c r="K21" s="3">
         <v>666000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>724000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>864000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>700000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>406000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>819000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>675000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>739000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1619000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>750000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>729000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>470000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>911000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>956000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>832000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>917000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>907000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1072000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1003000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>861000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>732000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1028000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>520000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>749000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>629000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>868000</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>106000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>55000</v>
+      </c>
+      <c r="F22" s="3">
+        <v>109000</v>
+      </c>
+      <c r="G22" s="3">
         <v>107000</v>
       </c>
-      <c r="E22" s="3">
-        <v>109000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>110000</v>
-      </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>105000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
+        <v>59000</v>
+      </c>
+      <c r="J22" s="3">
         <v>103000</v>
       </c>
-      <c r="I22" s="3">
-        <v>103000</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>93000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>150000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>83000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>77000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>85000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>104000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>117000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>124000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>3000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>148000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>156000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>163000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>168000</v>
-      </c>
-      <c r="W22" s="3">
-        <v>177000</v>
       </c>
       <c r="X22" s="3">
         <v>177000</v>
       </c>
       <c r="Y22" s="3">
+        <v>177000</v>
+      </c>
+      <c r="Z22" s="3">
         <v>184000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>187000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>184000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>183000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>180000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>187000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>198000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>186000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>187000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>182000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>181000</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>206000</v>
+        <v>79000</v>
       </c>
       <c r="E23" s="3">
-        <v>85000</v>
+        <v>205000</v>
       </c>
       <c r="F23" s="3">
-        <v>-326000</v>
+        <v>83000</v>
       </c>
       <c r="G23" s="3">
-        <v>232000</v>
+        <v>-345000</v>
       </c>
       <c r="H23" s="3">
+        <v>231000</v>
+      </c>
+      <c r="I23" s="3">
         <v>255000</v>
       </c>
-      <c r="I23" s="3">
-        <v>221000</v>
-      </c>
       <c r="J23" s="3">
+        <v>220000</v>
+      </c>
+      <c r="K23" s="3">
         <v>322000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>313000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>514000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>362000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>44000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>397000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>252000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>306000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>329000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>282000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>261000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-16000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>400000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>452000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>334000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>418000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>382000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>553000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>490000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>356000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>197000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>457000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-23000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>217000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>119000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>373000</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-293000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>27000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-61000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>39000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>33000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>48000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>148000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-575000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>96000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>95000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-5000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>59000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>46000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>88000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>176000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>50000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>67000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>94000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>262000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>137000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>128000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>106000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>145000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>119000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>130000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>89000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>13000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>136000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-87000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>73000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>54000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>107000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>499000</v>
+        <v>150000</v>
       </c>
       <c r="E26" s="3">
-        <v>58000</v>
+        <v>498000</v>
       </c>
       <c r="F26" s="3">
-        <v>-265000</v>
+        <v>56000</v>
       </c>
       <c r="G26" s="3">
-        <v>193000</v>
+        <v>-284000</v>
       </c>
       <c r="H26" s="3">
+        <v>192000</v>
+      </c>
+      <c r="I26" s="3">
         <v>222000</v>
       </c>
-      <c r="I26" s="3">
-        <v>173000</v>
-      </c>
       <c r="J26" s="3">
+        <v>172000</v>
+      </c>
+      <c r="K26" s="3">
         <v>174000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>888000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>418000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>267000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>49000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>338000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>206000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>218000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>153000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>232000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>194000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-110000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>138000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>315000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>206000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>312000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>237000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>434000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>360000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>267000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>184000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>321000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>64000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>144000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>65000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>266000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>150000</v>
+      </c>
+      <c r="E27" s="3">
         <v>498000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>56000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-284000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
+        <v>165000</v>
+      </c>
+      <c r="I27" s="3">
+        <v>235000</v>
+      </c>
+      <c r="J27" s="3">
+        <v>172000</v>
+      </c>
+      <c r="K27" s="3">
+        <v>-81000</v>
+      </c>
+      <c r="L27" s="3">
+        <v>887000</v>
+      </c>
+      <c r="M27" s="3">
+        <v>416000</v>
+      </c>
+      <c r="N27" s="3">
+        <v>267000</v>
+      </c>
+      <c r="O27" s="3">
+        <v>-196000</v>
+      </c>
+      <c r="P27" s="3">
+        <v>432000</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>308000</v>
+      </c>
+      <c r="R27" s="3">
+        <v>267000</v>
+      </c>
+      <c r="S27" s="3">
+        <v>230000</v>
+      </c>
+      <c r="T27" s="3">
+        <v>204000</v>
+      </c>
+      <c r="U27" s="3">
+        <v>266000</v>
+      </c>
+      <c r="V27" s="3">
+        <v>-141000</v>
+      </c>
+      <c r="W27" s="3">
+        <v>166000</v>
+      </c>
+      <c r="X27" s="3">
+        <v>344000</v>
+      </c>
+      <c r="Y27" s="3">
+        <v>292000</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>424000</v>
+      </c>
+      <c r="AA27" s="3">
+        <v>314000</v>
+      </c>
+      <c r="AB27" s="3">
+        <v>526000</v>
+      </c>
+      <c r="AC27" s="3">
+        <v>428000</v>
+      </c>
+      <c r="AD27" s="3">
+        <v>361000</v>
+      </c>
+      <c r="AE27" s="3">
+        <v>248000</v>
+      </c>
+      <c r="AF27" s="3">
+        <v>366000</v>
+      </c>
+      <c r="AG27" s="3">
+        <v>84000</v>
+      </c>
+      <c r="AH27" s="3">
         <v>192000</v>
       </c>
-      <c r="H27" s="3">
-        <v>222000</v>
-      </c>
-      <c r="I27" s="3">
-        <v>172000</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-81000</v>
-      </c>
-      <c r="K27" s="3">
-        <v>887000</v>
-      </c>
-      <c r="L27" s="3">
-        <v>416000</v>
-      </c>
-      <c r="M27" s="3">
-        <v>267000</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-196000</v>
-      </c>
-      <c r="O27" s="3">
-        <v>432000</v>
-      </c>
-      <c r="P27" s="3">
-        <v>308000</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>267000</v>
-      </c>
-      <c r="R27" s="3">
-        <v>230000</v>
-      </c>
-      <c r="S27" s="3">
-        <v>204000</v>
-      </c>
-      <c r="T27" s="3">
-        <v>266000</v>
-      </c>
-      <c r="U27" s="3">
-        <v>-141000</v>
-      </c>
-      <c r="V27" s="3">
-        <v>166000</v>
-      </c>
-      <c r="W27" s="3">
-        <v>344000</v>
-      </c>
-      <c r="X27" s="3">
-        <v>292000</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>424000</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>314000</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>526000</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>428000</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>361000</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>248000</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>366000</v>
-      </c>
-      <c r="AF27" s="3">
-        <v>84000</v>
-      </c>
-      <c r="AG27" s="3">
-        <v>192000</v>
-      </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>111000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2740,43 +2801,43 @@
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>-27000</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>13000</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>-237000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>64000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>95000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>93000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>303000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>432000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>124000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>82000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>252000</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -2784,12 +2845,12 @@
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V29" s="3">
+      <c r="V29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W29" s="3">
         <v>-1000</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
       <c r="X29" s="3">
         <v>0</v>
       </c>
@@ -2797,37 +2858,40 @@
         <v>0</v>
       </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>2000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>36000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-23000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>368000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>1212000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>29000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>17000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>107000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-67000</v>
+        <v>-1000</v>
       </c>
       <c r="E32" s="3">
-        <v>-70000</v>
+        <v>-1000</v>
       </c>
       <c r="F32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-72000</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-91000</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-59000</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-103000</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="P32" s="3">
+        <v>-72000</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>-212000</v>
+      </c>
+      <c r="R32" s="3">
+        <v>-157000</v>
+      </c>
+      <c r="S32" s="3">
+        <v>367000</v>
+      </c>
+      <c r="T32" s="3">
+        <v>-49000</v>
+      </c>
+      <c r="U32" s="3">
+        <v>-54000</v>
+      </c>
+      <c r="V32" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="W32" s="3">
+        <v>-49000</v>
+      </c>
+      <c r="X32" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>-48000</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-44000</v>
       </c>
-      <c r="G32" s="3">
-        <v>-34000</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-32000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-26000</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-72000</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-91000</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-59000</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-103000</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-24000</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-72000</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-212000</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-157000</v>
-      </c>
-      <c r="R32" s="3">
-        <v>367000</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="AA32" s="3">
+        <v>375000</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="AE32" s="3">
+        <v>351000</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>11000</v>
+      </c>
+      <c r="AG32" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="AI32" s="3">
+        <v>-46000</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>-49000</v>
       </c>
-      <c r="T32" s="3">
-        <v>-54000</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-71000</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-49000</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-39000</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-48000</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-44000</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>375000</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>-28000</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-15000</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>-39000</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>351000</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>11000</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="AH32" s="3">
-        <v>-46000</v>
-      </c>
-      <c r="AI32" s="3">
-        <v>-49000</v>
-      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>150000</v>
+      </c>
+      <c r="E33" s="3">
         <v>498000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>56000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-284000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>165000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>235000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>172000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-318000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>951000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>511000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>360000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>107000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>864000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>432000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>349000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>482000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>204000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>266000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-141000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>165000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>344000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>292000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>424000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>316000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>562000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>405000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>729000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1460000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>395000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>80000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>209000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>218000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>150000</v>
+      </c>
+      <c r="E35" s="3">
         <v>498000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>56000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-284000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>165000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>235000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>172000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-318000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>951000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>511000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>360000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>107000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>864000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>432000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>349000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>482000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>204000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>266000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-141000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>165000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>344000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>292000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>424000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>316000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>562000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>405000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>729000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1460000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>395000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>80000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>209000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>218000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,109 +3698,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1159000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1049000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1070000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1113000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1149000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>746000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>636000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>804000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>511000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>826000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1031000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1295000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2122000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>706000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>787000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>595000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>678000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>847000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1239000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>511000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>697000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>787000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>641000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>589000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1026000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1073000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1141000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1018000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>998000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1041000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>998000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1033000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2562000</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3743,19 +3833,19 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>151000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>291000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>245000</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
-        <v>4850000</v>
+        <v>0</v>
       </c>
       <c r="Q42" s="3">
         <v>4850000</v>
@@ -3766,8 +3856,8 @@
       <c r="S42" s="3">
         <v>4850000</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>8</v>
+      <c r="T42" s="3">
+        <v>4850000</v>
       </c>
       <c r="U42" s="3" t="s">
         <v>8</v>
@@ -3784,8 +3874,8 @@
       <c r="Y42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z42" s="3">
-        <v>0</v>
+      <c r="Z42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA42" s="3">
         <v>0</v>
@@ -3814,664 +3904,685 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3550000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3633000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3478000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3492000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3552000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3630000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3729000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3765000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3967000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3968000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3854000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3610000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3976000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4024000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3779000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3419000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3422000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3461000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3649000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3673000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3693000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3876000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3903000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3916000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3963000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3907000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3804000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3287000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3343000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3283000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3078000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2852000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2807000</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1795000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1728000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1771000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1889000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1929000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1911000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1939000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1942000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1976000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1897000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1746000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1814000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2053000</v>
-      </c>
-      <c r="P44" s="3">
-        <v>1828000</v>
       </c>
       <c r="Q44" s="3">
         <v>1828000</v>
       </c>
       <c r="R44" s="3">
+        <v>1828000</v>
+      </c>
+      <c r="S44" s="3">
         <v>2050000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2007000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2010000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2002000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2208000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2194000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2224000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2301000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2241000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2130000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2050000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2057000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2313000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2465000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2361000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2394000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2233000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>2222000</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>139000</v>
+      </c>
+      <c r="E45" s="3">
         <v>147000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>140000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>114000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>150000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>189000</v>
       </c>
-      <c r="I45" s="3">
-        <v>311000</v>
-      </c>
       <c r="J45" s="3">
+        <v>239000</v>
+      </c>
+      <c r="K45" s="3">
         <v>259000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>168000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>204000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>262000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>132000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1745000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>818000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>923000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>322000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>331000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>281000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>325000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>247000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>467000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>501000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>217000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>250000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>199000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>242000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>258000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1659000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>405000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>552000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>251000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>851000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>512000</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6643000</v>
+      </c>
+      <c r="E46" s="3">
         <v>6557000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6459000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6608000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6780000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6476000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6615000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6770000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6622000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7046000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7184000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7096000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9896000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12226000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>12167000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>11236000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>11288000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6599000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>7215000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6639000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>7051000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7388000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7062000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6996000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>7318000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>7272000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>7260000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>8277000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>7211000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>7237000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>6721000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>6670000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>8103000</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2484000</v>
+        <v>161000</v>
       </c>
       <c r="E47" s="3">
-        <v>2477000</v>
+        <v>163000</v>
       </c>
       <c r="F47" s="3">
-        <v>2475000</v>
+        <v>160000</v>
       </c>
       <c r="G47" s="3">
-        <v>2492000</v>
+        <v>163000</v>
       </c>
       <c r="H47" s="3">
-        <v>2486000</v>
+        <v>184000</v>
       </c>
       <c r="I47" s="3">
-        <v>2485000</v>
+        <v>183000</v>
       </c>
       <c r="J47" s="3">
+        <v>187000</v>
+      </c>
+      <c r="K47" s="3">
         <v>2480000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3215000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3214000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2888000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3026000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2983000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2888000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2972000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3435000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3352000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>8505000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>8463000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>8809000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>8735000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>8725000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>8844000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>8718000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>8680000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>8599000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>8546000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>7441000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>7383000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>7367000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>7348000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>7393000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>7353000</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>10398000</v>
+      </c>
+      <c r="E48" s="3">
         <v>10392000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10472000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10598000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10892000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10922000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10875000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10855000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10606000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10617000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10709000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10824000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12068000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12279000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12367000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>12987000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>13120000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>13304000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>13421000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>13829000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13648000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13775000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>13887000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>13469000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13476000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13589000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>13788000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>13713000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>14533000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>14491000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>14520000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>13459000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>12652000</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3194000</v>
+      </c>
+      <c r="E49" s="3">
         <v>3204000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3215000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3224000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3233000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3245000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3253000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3261000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3345000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3124000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3128000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3130000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3274000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3317000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3242000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3315000</v>
-      </c>
-      <c r="S49" s="3">
-        <v>3304000</v>
       </c>
       <c r="T49" s="3">
         <v>3304000</v>
@@ -4480,49 +4591,52 @@
         <v>3304000</v>
       </c>
       <c r="V49" s="3">
+        <v>3304000</v>
+      </c>
+      <c r="W49" s="3">
         <v>3347000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3412000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3441000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3393000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3374000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3371000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3378000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3414000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3411000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3420000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3409000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3402000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3364000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3362000</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>426000</v>
+        <v>2523000</v>
       </c>
       <c r="E52" s="3">
-        <v>405000</v>
+        <v>2492000</v>
       </c>
       <c r="F52" s="3">
-        <v>356000</v>
+        <v>2462000</v>
       </c>
       <c r="G52" s="3">
-        <v>554000</v>
+        <v>2430000</v>
       </c>
       <c r="H52" s="3">
-        <v>554000</v>
+        <v>2632000</v>
       </c>
       <c r="I52" s="3">
-        <v>543000</v>
+        <v>2618000</v>
       </c>
       <c r="J52" s="3">
+        <v>2603000</v>
+      </c>
+      <c r="K52" s="3">
         <v>574000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1077000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1281000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1249000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1167000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1250000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>738000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>729000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>745000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>776000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>807000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>812000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>847000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1002000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1018000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>992000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1019000</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>958000</v>
       </c>
       <c r="AB52" s="3">
         <v>958000</v>
       </c>
       <c r="AC52" s="3">
+        <v>958000</v>
+      </c>
+      <c r="AD52" s="3">
         <v>1022000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1061000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1266000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1373000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1310000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2207000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1131000</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>23161000</v>
+      </c>
+      <c r="E54" s="3">
         <v>23063000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>23028000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>23261000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>23951000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>23683000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>23771000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>23940000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>24865000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>25282000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>25158000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>25243000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>29471000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>31448000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>31477000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>31718000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>31840000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>32519000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>33215000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>33471000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>33848000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>34347000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>34178000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>33576000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>33803000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>33796000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>34030000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>33903000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>33813000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>33877000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>33301000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>33093000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>32601000</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,614 +5230,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2436000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2350000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2322000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2442000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2363000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2394000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2541000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2708000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2668000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2678000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2657000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2606000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2704000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2565000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2354000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2320000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2226000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2206000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2379000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2423000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2349000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2498000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2518000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2413000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2510000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2478000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2534000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2458000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2408000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2362000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2380000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2199000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2031000</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>259000</v>
+        <v>413000</v>
       </c>
       <c r="E58" s="3">
-        <v>138000</v>
+        <v>410000</v>
       </c>
       <c r="F58" s="3">
-        <v>138000</v>
+        <v>287000</v>
       </c>
       <c r="G58" s="3">
-        <v>120000</v>
+        <v>291000</v>
       </c>
       <c r="H58" s="3">
-        <v>248000</v>
+        <v>271000</v>
       </c>
       <c r="I58" s="3">
-        <v>367000</v>
+        <v>400000</v>
       </c>
       <c r="J58" s="3">
+        <v>510000</v>
+      </c>
+      <c r="K58" s="3">
         <v>763000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>616000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>293000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>197000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>196000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>233000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>116000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>31000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>29000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>179000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>33000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>664000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>168000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>402000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>676000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>809000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>639000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>555000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>684000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>587000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>311000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>958000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>824000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>454000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>239000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>78000</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1505000</v>
+        <v>867000</v>
       </c>
       <c r="E59" s="3">
-        <v>1394000</v>
+        <v>881000</v>
       </c>
       <c r="F59" s="3">
-        <v>1379000</v>
+        <v>867000</v>
       </c>
       <c r="G59" s="3">
-        <v>1399000</v>
+        <v>829000</v>
       </c>
       <c r="H59" s="3">
-        <v>1425000</v>
+        <v>878000</v>
       </c>
       <c r="I59" s="3">
-        <v>1358000</v>
+        <v>888000</v>
       </c>
       <c r="J59" s="3">
+        <v>865000</v>
+      </c>
+      <c r="K59" s="3">
         <v>1529000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1521000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1381000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1288000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1342000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1761000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5954000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6005000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5935000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6071000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>6091000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>6299000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>6055000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1978000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1875000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1626000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1642000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1538000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1456000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1344000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2333000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1503000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1816000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1433000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1631000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1432000</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4353000</v>
+      </c>
+      <c r="E60" s="3">
         <v>4114000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3854000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3959000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3882000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4067000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4266000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5000000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4805000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4352000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4142000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4144000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4698000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8635000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8390000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8284000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8476000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8330000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>9342000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>8646000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4729000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5049000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4953000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4694000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4603000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4618000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4465000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5102000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4869000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>5002000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4267000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>4069000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>3541000</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>5329000</v>
+        <v>5602000</v>
       </c>
       <c r="E61" s="3">
-        <v>5453000</v>
+        <v>5628000</v>
       </c>
       <c r="F61" s="3">
-        <v>5455000</v>
+        <v>5760000</v>
       </c>
       <c r="G61" s="3">
-        <v>5549000</v>
+        <v>5767000</v>
       </c>
       <c r="H61" s="3">
-        <v>5572000</v>
+        <v>5866000</v>
       </c>
       <c r="I61" s="3">
-        <v>5471000</v>
+        <v>5876000</v>
       </c>
       <c r="J61" s="3">
+        <v>5757000</v>
+      </c>
+      <c r="K61" s="3">
         <v>4816000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4766000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5275000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5468000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5383000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>8241000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7073000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>7954000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>8064000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>8525000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>9432000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>9561000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>9597000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>9957000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>10050000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>9965000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>10015000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>10700000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>10805000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>10759000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>10846000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>11373000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>10392000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>10823000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>11075000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>10823000</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>5025000</v>
+        <v>3247000</v>
       </c>
       <c r="E62" s="3">
-        <v>5464000</v>
+        <v>3216000</v>
       </c>
       <c r="F62" s="3">
-        <v>5492000</v>
+        <v>3200000</v>
       </c>
       <c r="G62" s="3">
-        <v>5638000</v>
+        <v>3208000</v>
       </c>
       <c r="H62" s="3">
-        <v>5640000</v>
+        <v>3198000</v>
       </c>
       <c r="I62" s="3">
-        <v>5645000</v>
+        <v>3179000</v>
       </c>
       <c r="J62" s="3">
+        <v>3193000</v>
+      </c>
+      <c r="K62" s="3">
         <v>5627000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5806000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6612000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6661000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6634000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6909000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7386000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7362000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7502000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7743000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7697000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7451000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>7510000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>11706000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>11749000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>11791000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>11484000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>11442000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>11509000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>11541000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>11414000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>12638000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>13918000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>13617000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>13590000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>14008000</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14532000</v>
+      </c>
+      <c r="E66" s="3">
         <v>14468000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14771000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>14906000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>15069000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>15279000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>15382000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>15443000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>15377000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>16239000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>16271000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>16161000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>19849000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>23096000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>23719000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>23864000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>24747000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>25462000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>26358000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>25758000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>26407000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>26865000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>26732000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>26214000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>26763000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>26952000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>26785000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>27381000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>28899000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>29332000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>28726000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>28752000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>28392000</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>9705000</v>
+      </c>
+      <c r="E72" s="3">
         <v>9719000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9386000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>9491000</v>
-      </c>
-      <c r="G72" s="3">
-        <v>9938000</v>
       </c>
       <c r="H72" s="3">
         <v>9938000</v>
       </c>
       <c r="I72" s="3">
+        <v>9938000</v>
+      </c>
+      <c r="J72" s="3">
         <v>9866000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9855000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>10340000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9557000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9218000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9029000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9103000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>8442000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>8214000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>8070000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8122000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8123000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>8062000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>8408000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>8447000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>8302000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>8211000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>7465000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>7353000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6988000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6783000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6180000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>4918000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4717000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4832000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4818000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>4793000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8629000</v>
+      </c>
+      <c r="E76" s="3">
         <v>8595000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8257000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8355000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8882000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8404000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8389000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8497000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9488000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9043000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8887000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9082000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9622000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8352000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7758000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7854000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7093000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7057000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>6857000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7713000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7441000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7482000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7446000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7362000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7040000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6844000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>7245000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6522000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4914000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4545000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4575000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>4341000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>4209000</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>150000</v>
+      </c>
+      <c r="E81" s="3">
         <v>498000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>56000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-284000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>165000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>235000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>172000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-318000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>951000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>511000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>360000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>107000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>864000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>432000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>349000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>482000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>204000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>266000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-141000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>165000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>344000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>292000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>424000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>316000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>562000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>405000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>729000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1460000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>395000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>80000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>209000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>218000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,109 +7599,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>249000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>235000</v>
+      </c>
+      <c r="F83" s="3">
+        <v>232000</v>
+      </c>
+      <c r="G83" s="3">
+        <v>240000</v>
+      </c>
+      <c r="H83" s="3">
+        <v>250000</v>
+      </c>
+      <c r="I83" s="3">
+        <v>256000</v>
+      </c>
+      <c r="J83" s="3">
+        <v>250000</v>
+      </c>
+      <c r="K83" s="3">
+        <v>251000</v>
+      </c>
+      <c r="L83" s="3">
         <v>261000</v>
       </c>
-      <c r="E83" s="3">
-        <v>278000</v>
-      </c>
-      <c r="F83" s="3">
-        <v>689000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>258000</v>
-      </c>
-      <c r="H83" s="3">
-        <v>244000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>241000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>251000</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
+        <v>267000</v>
+      </c>
+      <c r="N83" s="3">
         <v>261000</v>
       </c>
-      <c r="L83" s="3">
-        <v>267000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>261000</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>277000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>318000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>306000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>309000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1287000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>320000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>312000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>323000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>343000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>327000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>321000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>315000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>338000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>335000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>330000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>325000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>348000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>373000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>357000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>345000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>328000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>314000</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>521000</v>
+      </c>
+      <c r="E89" s="3">
         <v>365000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>395000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>492000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>468000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>528000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>345000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>761000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>435000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>390000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>588000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>107000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>690000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>775000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>458000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3061000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>737000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>886000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>640000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>947000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>884000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1046000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>733000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>821000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>941000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>801000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>663000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1188000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-705000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>641000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>633000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>912000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>341000</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8365,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-212000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-198000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-251000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-305000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-228000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-267000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-341000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-322000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-238000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-186000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-185000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-201000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-126000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-133000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-89000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-751000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-119000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-252000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-286000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-363000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-285000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-335000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-293000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-286000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-357000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-440000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-489000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-456000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-271000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-290000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-374000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-445000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-266000</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-188000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-199000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-247000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-310000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>245000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-264000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-339000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-315000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-76000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-37000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-180000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-130000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>5598000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>328000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>258000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-269000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>134000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-299000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-35000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-306000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-279000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-421000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-294000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-259000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-346000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-475000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-489000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-383000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-278000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-330000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-400000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2527000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-279000</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,94 +8819,95 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-160000</v>
+        <v>161000</v>
       </c>
       <c r="E96" s="3">
-        <v>-161000</v>
+        <v>160000</v>
       </c>
       <c r="F96" s="3">
-        <v>-160000</v>
+        <v>161000</v>
       </c>
       <c r="G96" s="3">
-        <v>-160000</v>
+        <v>160000</v>
       </c>
       <c r="H96" s="3">
-        <v>-160000</v>
+        <v>160000</v>
       </c>
       <c r="I96" s="3">
-        <v>-162000</v>
+        <v>160000</v>
       </c>
       <c r="J96" s="3">
+        <v>162000</v>
+      </c>
+      <c r="K96" s="3">
         <v>-164000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-165000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-170000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-174000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-178000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-199000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-201000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-202000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-806000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-202000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-201000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-202000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-201000</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-197000</v>
       </c>
       <c r="X96" s="3">
         <v>-197000</v>
       </c>
       <c r="Y96" s="3">
-        <v>-201000</v>
+        <v>-197000</v>
       </c>
       <c r="Z96" s="3">
         <v>-201000</v>
       </c>
       <c r="AA96" s="3">
+        <v>-201000</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-195000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-196000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-197000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-196000</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-191000</v>
       </c>
       <c r="AF96" s="3">
         <v>-191000</v>
@@ -8682,13 +8916,16 @@
         <v>-191000</v>
       </c>
       <c r="AH96" s="3">
+        <v>-191000</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-190000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-181000</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,307 +9233,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-223000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-174000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-191000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-222000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-306000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-230000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-108000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-159000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-669000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-643000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-583000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2301000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3359000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1211000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-504000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2700000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1042000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-982000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>165000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-842000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-671000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-487000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-389000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1000000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-636000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-354000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-56000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-779000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>930000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-266000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-284000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>104000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>1232000</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-13000</v>
+        <v>-4000</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="F101" s="3">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="G101" s="3">
-        <v>-4000</v>
+        <v>6000</v>
       </c>
       <c r="H101" s="3">
-        <v>4000</v>
+        <v>-5000</v>
       </c>
       <c r="I101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="K101" s="3">
         <v>6000</v>
       </c>
-      <c r="J101" s="3">
-        <v>6000</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-5000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-14000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>27000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-20000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-8000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>3000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-42000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>15000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-24000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>8000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>2000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-40000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>5000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>10000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>16000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-18000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>110000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-21000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-43000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-36000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>403000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>38000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-96000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>293000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-315000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-293000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-176000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2326000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2915000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-81000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>192000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>84000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-169000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-392000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>728000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-186000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-90000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>146000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>52000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-437000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-47000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-68000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>123000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>20000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-43000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>43000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-35000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1529000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1308000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
   <si>
     <t>IP</t>
   </si>
@@ -656,467 +656,479 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4580000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4686000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4734000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4619000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4601000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4613000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4682000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5020000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5133000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5402000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5389000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5237000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5086000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4914000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4770000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4593000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>17565000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5123000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4866000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5352000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5498000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5568000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5667000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5643000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5951000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5901000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5833000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5621000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5711000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5517000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5383000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5132000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3797000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>5266000</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3167000</v>
+      </c>
+      <c r="E9" s="3">
         <v>3329000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3335000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3424000</v>
       </c>
-      <c r="G9" s="3">
-        <v>3282000</v>
-      </c>
       <c r="H9" s="3">
+        <v>3246000</v>
+      </c>
+      <c r="I9" s="3">
         <v>3316000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3360000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3642000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3668000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3830000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3806000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3839000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3659000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3423000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3402000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3348000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>12339000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3541000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3427000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3732000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3669000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3766000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3902000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3932000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3800000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3889000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3923000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3946000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3702000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3705000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3749000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3635000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2712000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>3622000</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1413000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1357000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1399000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1195000</v>
       </c>
-      <c r="G10" s="3">
-        <v>1319000</v>
-      </c>
       <c r="H10" s="3">
+        <v>1355000</v>
+      </c>
+      <c r="I10" s="3">
         <v>1297000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1322000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1378000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1465000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1572000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1583000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1398000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1427000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1491000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1368000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1245000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>5226000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1582000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1439000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1620000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1829000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1802000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1765000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1711000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2151000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2012000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1910000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1675000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2009000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1812000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1634000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1497000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1085000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1644000</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,8 +1165,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1257,8 +1270,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,216 +1377,225 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>500000</v>
+      </c>
+      <c r="E14" s="3">
         <v>120000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>49000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>13000</v>
       </c>
-      <c r="G14" s="3">
-        <v>524000</v>
-      </c>
       <c r="H14" s="3">
+        <v>557000</v>
+      </c>
+      <c r="I14" s="3">
         <v>29000</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>72000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>93000</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>266000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-321000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>165000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>32000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>660000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>100000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>26000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>352000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>88000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>61000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>152000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-7000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-19000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>122000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>26000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>22000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>83000</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>347000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-6000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>7000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>51000</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>266000</v>
+      </c>
+      <c r="E15" s="3">
         <v>267000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>261000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>273000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>267000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>258000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>244000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>241000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>251000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>261000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>267000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>261000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>277000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>280000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>272000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>268000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1091000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>320000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>312000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>323000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>343000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>327000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>321000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>315000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>338000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>335000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>330000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>325000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>339000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>350000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>334000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>320000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>225000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>314000</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1629,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4248000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4435000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4424000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4475000</v>
       </c>
-      <c r="G17" s="3">
-        <v>4354000</v>
-      </c>
       <c r="H17" s="3">
+        <v>4318000</v>
+      </c>
+      <c r="I17" s="3">
         <v>4294000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4368000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4737000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4790000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5030000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4851000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4901000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4981000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4485000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4613000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4320000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>16866000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4742000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4503000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5276000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4979000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4978000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5204000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5085000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5007000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5192000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5175000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5124000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4976000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4851000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5223000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4732000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3542000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4761000</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>332000</v>
+      </c>
+      <c r="E18" s="3">
         <v>251000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>310000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>144000</v>
       </c>
-      <c r="G18" s="3">
-        <v>247000</v>
-      </c>
       <c r="H18" s="3">
+        <v>283000</v>
+      </c>
+      <c r="I18" s="3">
         <v>319000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>314000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>283000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>343000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>372000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>538000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>336000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>105000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>429000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>157000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>273000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>699000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>381000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>363000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>76000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>519000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>590000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>463000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>558000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>944000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>709000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>658000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>497000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>735000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>666000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>160000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>400000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>255000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>505000</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,8 +1882,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1862,516 +1895,531 @@
         <v>1000</v>
       </c>
       <c r="F20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G20" s="3">
         <v>2000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>19000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1000</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>72000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>91000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>59000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>103000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>24000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>72000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>212000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>157000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-367000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>49000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>54000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>71000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>49000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>39000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>48000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>44000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-375000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>28000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>15000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>39000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-351000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-11000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>3000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>4000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>46000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>49000</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>597000</v>
+      </c>
+      <c r="E21" s="3">
         <v>517000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>570000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>415000</v>
       </c>
-      <c r="G21" s="3">
-        <v>495000</v>
-      </c>
       <c r="H21" s="3">
+        <v>531000</v>
+      </c>
+      <c r="I21" s="3">
         <v>576000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>558000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>523000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>666000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>724000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>864000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>700000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>406000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>819000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>675000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>739000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1619000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>750000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>729000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>470000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>911000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>956000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>832000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>917000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>907000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1072000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1003000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>861000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>732000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1028000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>520000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>749000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>629000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>868000</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>108000</v>
+      </c>
+      <c r="E22" s="3">
         <v>106000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>55000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>109000</v>
       </c>
-      <c r="G22" s="3">
-        <v>107000</v>
-      </c>
       <c r="H22" s="3">
+        <v>110000</v>
+      </c>
+      <c r="I22" s="3">
         <v>105000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>59000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>103000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>93000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>150000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>83000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>77000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>85000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>104000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>117000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>124000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>3000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>148000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>156000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>163000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>168000</v>
-      </c>
-      <c r="X22" s="3">
-        <v>177000</v>
       </c>
       <c r="Y22" s="3">
         <v>177000</v>
       </c>
       <c r="Z22" s="3">
+        <v>177000</v>
+      </c>
+      <c r="AA22" s="3">
         <v>184000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>187000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>184000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>183000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>180000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>187000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>198000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>186000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>187000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>182000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>181000</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-225000</v>
+      </c>
+      <c r="E23" s="3">
         <v>79000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>205000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>83000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-345000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>231000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>255000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>220000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>322000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>313000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>514000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>362000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>44000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>397000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>252000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>306000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>329000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>282000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>261000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-16000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>400000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>452000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>334000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>418000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>382000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>553000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>490000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>356000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>197000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>457000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-23000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>217000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>119000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>373000</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-78000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-71000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-293000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>27000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-61000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>39000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>33000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>48000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>148000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-575000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>96000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>95000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-5000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>59000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>46000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>88000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>176000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>50000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>67000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>94000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>262000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>137000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>128000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>106000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>145000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>119000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>130000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>89000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>13000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>136000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-87000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>73000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>54000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>107000</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2522,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-147000</v>
+      </c>
+      <c r="E26" s="3">
         <v>150000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>498000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>56000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-284000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>192000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>222000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>172000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>174000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>888000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>418000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>267000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>49000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>338000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>206000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>218000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>153000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>232000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>194000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-110000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>138000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>315000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>206000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>312000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>237000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>434000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>360000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>267000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>184000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>321000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>64000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>144000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>65000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>266000</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-147000</v>
+      </c>
+      <c r="E27" s="3">
         <v>150000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>498000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>56000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-284000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>165000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>235000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>172000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-81000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>887000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>416000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>267000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-196000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>432000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>308000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>267000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>230000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>204000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>266000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-141000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>166000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>344000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>292000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>424000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>314000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>526000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>428000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>361000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>248000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>366000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>84000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>192000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>111000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2804,43 +2864,43 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-27000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>13000</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>-237000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>64000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>95000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>93000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>303000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>432000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>124000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>82000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>252000</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
@@ -2848,12 +2908,12 @@
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3">
         <v>-1000</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
       <c r="Y29" s="3">
         <v>0</v>
       </c>
@@ -2861,37 +2921,40 @@
         <v>0</v>
       </c>
       <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>2000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>36000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-23000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>368000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>1212000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>29000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>17000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>107000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,8 +3164,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3110,204 +3179,210 @@
         <v>-1000</v>
       </c>
       <c r="F32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G32" s="3">
         <v>-2000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-19000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1000</v>
       </c>
-      <c r="I32" s="3" t="s">
+      <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-72000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-91000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-59000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-103000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-24000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-72000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-212000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-157000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>367000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-49000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-54000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-71000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-49000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-39000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-48000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-44000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>375000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-28000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-15000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-39000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>351000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>11000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-46000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-49000</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-147000</v>
+      </c>
+      <c r="E33" s="3">
         <v>150000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>498000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>56000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-284000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>165000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>235000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>172000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-318000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>951000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>511000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>360000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>107000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>864000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>432000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>349000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>482000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>204000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>266000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-141000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>165000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>344000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>292000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>424000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>316000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>562000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>405000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>729000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1460000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>395000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>80000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>209000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>218000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3485,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-147000</v>
+      </c>
+      <c r="E35" s="3">
         <v>150000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>498000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>56000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-284000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>165000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>235000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>172000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-318000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>951000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>511000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>360000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>107000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>864000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>432000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>349000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>482000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>204000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>266000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-141000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>165000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>344000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>292000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>424000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>316000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>562000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>405000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>729000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1460000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>395000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>80000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>209000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>218000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,112 +3784,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1170000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1159000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1049000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1070000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1113000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1149000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>746000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>636000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>804000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>511000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>826000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1031000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1295000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2122000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>706000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>787000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>595000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>678000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>847000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1239000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>511000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>697000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>787000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>641000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>589000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1026000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1073000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1141000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1018000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>998000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1041000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>998000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1033000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2562000</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3836,19 +3925,19 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>151000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>291000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>245000</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
-        <v>4850000</v>
+        <v>0</v>
       </c>
       <c r="R42" s="3">
         <v>4850000</v>
@@ -3859,8 +3948,8 @@
       <c r="T42" s="3">
         <v>4850000</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>8</v>
+      <c r="U42" s="3">
+        <v>4850000</v>
       </c>
       <c r="V42" s="3" t="s">
         <v>8</v>
@@ -3877,8 +3966,8 @@
       <c r="Z42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA42" s="3">
-        <v>0</v>
+      <c r="AA42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB42" s="3">
         <v>0</v>
@@ -3907,685 +3996,706 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3362000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3550000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3633000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3478000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3492000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3552000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3630000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3729000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3765000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3967000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3968000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3854000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3610000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3976000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4024000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3779000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3419000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3422000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3461000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3649000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3673000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3693000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3876000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3903000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3916000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3963000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3907000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3804000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3287000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3343000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3283000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3078000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2852000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2807000</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1784000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1795000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1728000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1771000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1889000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1929000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1911000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1939000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1942000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1976000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1897000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1746000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1814000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2053000</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>1828000</v>
       </c>
       <c r="R44" s="3">
         <v>1828000</v>
       </c>
       <c r="S44" s="3">
+        <v>1828000</v>
+      </c>
+      <c r="T44" s="3">
         <v>2050000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2007000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2010000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2002000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2208000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2194000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2224000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2301000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2241000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2130000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2050000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2057000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2313000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2465000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2361000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2394000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>2233000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>2222000</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>108000</v>
+      </c>
+      <c r="E45" s="3">
         <v>139000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>147000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>140000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>114000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>150000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>189000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>239000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>259000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>168000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>204000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>262000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>132000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1745000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>818000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>923000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>322000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>331000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>281000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>325000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>247000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>467000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>501000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>217000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>250000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>199000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>242000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>258000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1659000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>405000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>552000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>251000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>851000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>512000</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6424000</v>
+      </c>
+      <c r="E46" s="3">
         <v>6643000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6557000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6459000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6608000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6780000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6476000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6615000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6770000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6622000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7046000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7184000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7096000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9896000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>12226000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>12167000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>11236000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>11288000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6599000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>7215000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6639000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7051000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7388000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7062000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6996000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>7318000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>7272000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>7260000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>8277000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>7211000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>7237000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>6721000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>6670000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>8103000</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E47" s="3">
         <v>161000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>163000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>160000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>163000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>184000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>183000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>187000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2480000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3215000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3214000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2888000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3026000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2983000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2888000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2972000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3435000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3352000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>8505000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>8463000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>8809000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>8735000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>8725000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>8844000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>8718000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>8680000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>8599000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>8546000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>7441000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>7383000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>7367000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>7348000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>7393000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>7353000</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>10091000</v>
+      </c>
+      <c r="E48" s="3">
         <v>10398000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10392000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10472000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10598000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10892000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10922000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10875000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10855000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10606000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10617000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10709000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10824000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12068000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12279000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>12367000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>12987000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>13120000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>13304000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>13421000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13829000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13648000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>13775000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>13887000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13469000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13476000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>13589000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>13788000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>13713000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>14533000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>14491000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>14520000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>13459000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>12652000</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3183000</v>
+      </c>
+      <c r="E49" s="3">
         <v>3194000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3204000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3215000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3224000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3233000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3245000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3253000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3261000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3345000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3124000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3128000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3130000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3274000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3317000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3242000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3315000</v>
-      </c>
-      <c r="T49" s="3">
-        <v>3304000</v>
       </c>
       <c r="U49" s="3">
         <v>3304000</v>
@@ -4594,49 +4704,52 @@
         <v>3304000</v>
       </c>
       <c r="W49" s="3">
+        <v>3304000</v>
+      </c>
+      <c r="X49" s="3">
         <v>3347000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3412000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3441000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3393000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3374000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3371000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3378000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3414000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3411000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3420000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3409000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3402000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3364000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>3362000</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,112 +4959,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2423000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2523000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2492000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2462000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2430000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2632000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2618000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2603000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>574000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1077000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1281000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1249000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1167000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1250000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>738000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>729000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>745000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>776000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>807000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>812000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>847000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1002000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1018000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>992000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1019000</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>958000</v>
       </c>
       <c r="AC52" s="3">
         <v>958000</v>
       </c>
       <c r="AD52" s="3">
+        <v>958000</v>
+      </c>
+      <c r="AE52" s="3">
         <v>1022000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1061000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1266000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1373000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1310000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2207000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1131000</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>22800000</v>
+      </c>
+      <c r="E54" s="3">
         <v>23161000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>23063000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>23028000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>23261000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>23951000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>23683000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>23771000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>23940000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>24865000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>25282000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>25158000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>25243000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>29471000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>31448000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>31477000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>31718000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>31840000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>32519000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>33215000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>33471000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>33848000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>34347000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>34178000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>33576000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>33803000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>33796000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>34030000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>33903000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>33813000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>33877000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>33301000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>33093000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>32601000</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,632 +5360,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2316000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2436000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2350000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2322000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2442000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2363000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2394000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2541000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2708000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2668000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2678000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2657000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2606000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2704000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2565000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2354000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2320000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2226000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2206000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2379000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2423000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2349000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2498000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2518000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2413000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2510000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2478000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2534000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2458000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2408000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2362000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2380000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2199000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2031000</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>349000</v>
+      </c>
+      <c r="E58" s="3">
         <v>413000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>410000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>287000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>291000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>271000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>400000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>510000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>763000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>616000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>293000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>197000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>196000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>233000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>116000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>31000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>29000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>179000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>33000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>664000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>168000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>402000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>676000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>809000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>639000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>555000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>684000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>587000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>311000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>958000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>824000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>454000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>239000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>78000</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>844000</v>
+      </c>
+      <c r="E59" s="3">
         <v>867000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>881000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>867000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>829000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>878000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>888000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>865000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1529000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1521000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1381000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1288000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1342000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1761000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5954000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6005000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5935000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>6071000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>6091000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>6299000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>6055000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1978000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1875000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1626000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1642000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1538000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1456000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1344000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2333000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1503000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1816000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1433000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1631000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1432000</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4258000</v>
+      </c>
+      <c r="E60" s="3">
         <v>4353000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4114000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3854000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3959000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3882000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4067000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4266000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5000000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4805000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4352000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4142000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4144000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4698000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8635000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8390000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8284000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8476000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8330000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>9342000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>8646000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4729000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5049000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4953000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4694000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4603000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4618000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4465000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5102000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4869000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5002000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>4267000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>4069000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>3541000</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5660000</v>
+      </c>
+      <c r="E61" s="3">
         <v>5602000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5628000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5760000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5767000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5866000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5876000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5757000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4816000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4766000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5275000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5468000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5383000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>8241000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>7073000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>7954000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>8064000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8525000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>9432000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>9561000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>9597000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>9957000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>10050000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>9965000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>10015000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>10700000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>10805000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>10759000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>10846000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>11373000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>10392000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>10823000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>11075000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>10823000</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3271000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3247000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3216000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3200000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3208000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3198000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3179000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3193000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5627000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5806000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6612000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6661000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6634000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6909000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7386000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7362000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7502000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7743000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7697000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>7451000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>7510000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>11706000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>11749000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>11791000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>11484000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>11442000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>11509000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>11541000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>11414000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>12638000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>13918000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>13617000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>13590000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>14008000</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14627000</v>
+      </c>
+      <c r="E66" s="3">
         <v>14532000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14468000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>14771000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>14906000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>15069000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>15279000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>15382000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>15443000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>15377000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>16239000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>16271000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>16161000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>19849000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>23096000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>23719000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>23864000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>24747000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>25462000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>26358000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>25758000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>26407000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>26865000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>26732000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>26214000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>26763000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>26952000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>26785000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>27381000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>28899000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>29332000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>28726000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>28752000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>28392000</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6895,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>9393000</v>
+      </c>
+      <c r="E72" s="3">
         <v>9705000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9719000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>9386000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9491000</v>
-      </c>
-      <c r="H72" s="3">
-        <v>9938000</v>
       </c>
       <c r="I72" s="3">
         <v>9938000</v>
       </c>
       <c r="J72" s="3">
+        <v>9938000</v>
+      </c>
+      <c r="K72" s="3">
         <v>9866000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9855000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>10340000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9557000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9218000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9029000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9103000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>8442000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>8214000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8070000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8122000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>8123000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>8062000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>8408000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>8447000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>8302000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>8211000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>7465000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>7353000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6988000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6783000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>6180000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4918000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4717000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4832000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>4818000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>4793000</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8173000</v>
+      </c>
+      <c r="E76" s="3">
         <v>8629000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8595000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8257000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8355000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8882000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8404000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8389000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8497000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9488000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9043000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8887000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9082000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9622000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8352000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7758000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7854000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7093000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7057000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>6857000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7713000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7441000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7482000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7446000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7362000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7040000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6844000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>7245000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6522000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4914000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4545000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>4575000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>4341000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>4209000</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7537,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-147000</v>
+      </c>
+      <c r="E81" s="3">
         <v>150000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>498000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>56000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-284000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>165000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>235000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>172000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-318000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>951000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>511000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>360000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>107000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>864000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>432000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>349000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>482000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>204000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>266000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-141000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>165000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>344000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>292000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>424000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>316000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>562000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>405000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>729000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1460000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>395000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>80000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>209000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>218000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,112 +7797,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>257000</v>
+      </c>
+      <c r="E83" s="3">
         <v>249000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>235000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>232000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>240000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>250000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>256000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>250000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>251000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>261000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>267000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>261000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>277000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>318000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>306000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>309000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1287000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>320000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>312000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>323000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>343000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>327000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>321000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>315000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>338000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>335000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>330000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>325000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>348000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>373000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>357000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>345000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>328000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>314000</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8437,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>397000</v>
+      </c>
+      <c r="E89" s="3">
         <v>521000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>365000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>395000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>492000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>468000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>528000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>345000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>761000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>435000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>390000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>588000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>107000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>690000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>775000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>458000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3061000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>737000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>886000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>640000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>947000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>884000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1046000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>733000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>821000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>941000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>801000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>663000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1188000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-705000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>641000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>633000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>912000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>341000</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,112 +8585,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-260000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-212000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-198000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-251000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-305000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-228000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-267000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-341000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-322000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-238000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-186000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-185000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-201000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-126000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-133000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-89000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-751000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-119000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-252000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-286000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-363000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-285000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-335000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-293000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-286000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-357000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-440000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-489000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-456000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-271000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-290000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-374000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-445000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-266000</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8904,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-174000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-188000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-199000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-247000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-310000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>245000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-264000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-339000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-315000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-76000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-37000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-180000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-130000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>5598000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>328000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>258000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-269000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>134000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-299000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-35000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-306000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-279000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-421000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-294000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-259000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-346000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-475000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-489000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-383000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-278000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-330000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-400000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-2527000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-279000</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9052,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8829,13 +9062,13 @@
         <v>161000</v>
       </c>
       <c r="E96" s="3">
+        <v>161000</v>
+      </c>
+      <c r="F96" s="3">
         <v>160000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>161000</v>
-      </c>
-      <c r="G96" s="3">
-        <v>160000</v>
       </c>
       <c r="H96" s="3">
         <v>160000</v>
@@ -8844,73 +9077,73 @@
         <v>160000</v>
       </c>
       <c r="J96" s="3">
+        <v>160000</v>
+      </c>
+      <c r="K96" s="3">
         <v>162000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-164000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-165000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-170000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-174000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-178000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-199000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-201000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-202000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-806000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-202000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-201000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-202000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-201000</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-197000</v>
       </c>
       <c r="Y96" s="3">
         <v>-197000</v>
       </c>
       <c r="Z96" s="3">
-        <v>-201000</v>
+        <v>-197000</v>
       </c>
       <c r="AA96" s="3">
         <v>-201000</v>
       </c>
       <c r="AB96" s="3">
+        <v>-201000</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-195000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-196000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-197000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-196000</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-191000</v>
       </c>
       <c r="AG96" s="3">
         <v>-191000</v>
@@ -8919,13 +9152,16 @@
         <v>-191000</v>
       </c>
       <c r="AI96" s="3">
+        <v>-191000</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-190000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-181000</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,316 +9478,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-187000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-223000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-174000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-191000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-222000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-306000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-230000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-108000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-159000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-669000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-643000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-583000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2301000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3359000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1211000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-504000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2700000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1042000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-982000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>165000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-842000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-671000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-487000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-389000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1000000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-636000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-354000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-56000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-779000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>930000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-266000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-284000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>104000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>1232000</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>4000</v>
-      </c>
-      <c r="F101" s="3">
-        <v>6000</v>
       </c>
       <c r="G101" s="3">
         <v>6000</v>
       </c>
       <c r="H101" s="3">
+        <v>6000</v>
+      </c>
+      <c r="I101" s="3">
         <v>-5000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-3000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>6000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-3000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>27000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-20000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-8000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>2000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>3000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-42000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>15000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-24000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>8000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>2000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-40000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>5000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>10000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>16000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-18000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E102" s="3">
         <v>110000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-21000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-43000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-36000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>403000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>38000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-96000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>293000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-315000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-293000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-176000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2326000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2915000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-81000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>192000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>84000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-169000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-392000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>728000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-186000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-90000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>146000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>52000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-437000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-47000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-68000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>123000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>20000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-43000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>43000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-35000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1529000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1308000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
   <si>
     <t>IP</t>
   </si>
@@ -656,479 +656,492 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5901000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4580000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4686000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4734000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4619000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4601000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4613000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4682000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5020000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5133000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5402000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5389000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5237000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5086000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4914000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4770000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4593000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>17565000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5123000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4866000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5352000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5498000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5568000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5667000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5643000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5951000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5901000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5833000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5621000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5711000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5517000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5383000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>5132000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3797000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>5266000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3167000</v>
+        <v>4259000</v>
       </c>
       <c r="E9" s="3">
+        <v>3161000</v>
+      </c>
+      <c r="F9" s="3">
         <v>3329000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3335000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3424000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3246000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3316000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3360000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3642000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3668000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3830000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3806000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3839000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3659000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3423000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3402000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3348000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>12339000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3541000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3427000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3732000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3669000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3766000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3902000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3932000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3800000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3889000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3923000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3946000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3702000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3705000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3749000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3635000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2712000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>3622000</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1413000</v>
+        <v>1642000</v>
       </c>
       <c r="E10" s="3">
+        <v>1419000</v>
+      </c>
+      <c r="F10" s="3">
         <v>1357000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1399000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1195000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1355000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1297000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1322000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1378000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1465000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1572000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1583000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1398000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1427000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1491000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1368000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1245000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>5226000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1582000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1439000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1620000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1829000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1802000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1765000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1711000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2151000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2012000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1910000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1675000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2009000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1812000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1634000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1497000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1085000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1644000</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1166,8 +1179,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1273,8 +1287,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1380,222 +1397,231 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>500000</v>
+        <v>16000</v>
       </c>
       <c r="E14" s="3">
+        <v>506000</v>
+      </c>
+      <c r="F14" s="3">
         <v>120000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>49000</v>
       </c>
-      <c r="G14" s="3">
-        <v>13000</v>
-      </c>
       <c r="H14" s="3">
+        <v>8000</v>
+      </c>
+      <c r="I14" s="3">
         <v>557000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>29000</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>72000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>93000</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>266000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-321000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>165000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>32000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>660000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>100000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>26000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>352000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>88000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>61000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>152000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-7000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-19000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>122000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>26000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>22000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>83000</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>347000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>-6000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>7000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>51000</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>571000</v>
+      </c>
+      <c r="E15" s="3">
         <v>266000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>267000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>261000</v>
       </c>
-      <c r="G15" s="3">
-        <v>273000</v>
-      </c>
       <c r="H15" s="3">
+        <v>278000</v>
+      </c>
+      <c r="I15" s="3">
         <v>267000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>258000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>244000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>241000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>251000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>261000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>267000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>261000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>277000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>280000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>272000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>268000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1091000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>320000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>312000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>323000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>343000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>327000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>321000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>315000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>338000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>335000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>330000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>325000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>339000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>350000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>334000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>320000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>225000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>314000</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,222 +1656,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4248000</v>
+        <v>5939000</v>
       </c>
       <c r="E17" s="3">
+        <v>4242000</v>
+      </c>
+      <c r="F17" s="3">
         <v>4435000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4424000</v>
       </c>
-      <c r="G17" s="3">
-        <v>4475000</v>
-      </c>
       <c r="H17" s="3">
+        <v>4480000</v>
+      </c>
+      <c r="I17" s="3">
         <v>4318000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4294000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4368000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4737000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4790000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5030000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4851000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4901000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4981000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4485000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4613000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4320000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>16866000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4742000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4503000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5276000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4979000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4978000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5204000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5085000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5007000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5192000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5175000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5124000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4976000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4851000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5223000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4732000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3542000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>4761000</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>332000</v>
+        <v>-38000</v>
       </c>
       <c r="E18" s="3">
+        <v>338000</v>
+      </c>
+      <c r="F18" s="3">
         <v>251000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>310000</v>
       </c>
-      <c r="G18" s="3">
-        <v>144000</v>
-      </c>
       <c r="H18" s="3">
+        <v>139000</v>
+      </c>
+      <c r="I18" s="3">
         <v>283000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>319000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>314000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>283000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>343000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>372000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>538000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>336000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>105000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>429000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>157000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>273000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>699000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>381000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>363000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>76000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>519000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>590000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>463000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>558000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>944000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>709000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>658000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>497000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>735000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>666000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>160000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>400000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>255000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>505000</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,8 +1916,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1898,528 +1932,543 @@
         <v>1000</v>
       </c>
       <c r="G20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H20" s="3">
         <v>2000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>19000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1000</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>72000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>91000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>59000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>103000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>24000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>72000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>212000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>157000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-367000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>49000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>54000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>71000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>49000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>39000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>48000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>44000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-375000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>28000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>15000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>39000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-351000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-11000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>3000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>4000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>46000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>49000</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>597000</v>
+        <v>532000</v>
       </c>
       <c r="E21" s="3">
+        <v>603000</v>
+      </c>
+      <c r="F21" s="3">
         <v>517000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>570000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>415000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>531000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>576000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>558000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>523000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>666000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>724000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>864000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>700000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>406000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>819000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>675000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>739000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1619000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>750000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>729000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>470000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>911000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>956000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>832000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>917000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>907000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1072000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1003000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>861000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>732000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1028000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>520000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>749000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>629000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>868000</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>133000</v>
+      </c>
+      <c r="E22" s="3">
         <v>108000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>106000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>55000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>109000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>110000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>105000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>59000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>103000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>93000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>150000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>83000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>77000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>85000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>104000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>117000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>124000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>3000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>148000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>156000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>163000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>168000</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>177000</v>
       </c>
       <c r="Z22" s="3">
         <v>177000</v>
       </c>
       <c r="AA22" s="3">
+        <v>177000</v>
+      </c>
+      <c r="AB22" s="3">
         <v>184000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>187000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>184000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>183000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>180000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>187000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>198000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>186000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>187000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>182000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>181000</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-136000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-225000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>79000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>205000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>83000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-345000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>231000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>255000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>220000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>322000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>313000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>514000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>362000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>44000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>397000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>252000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>306000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>329000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>282000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>261000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-16000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>400000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>452000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>334000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>418000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>382000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>553000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>490000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>356000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>197000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>457000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-23000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>217000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>119000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>373000</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-78000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-71000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-293000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>27000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-61000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>39000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>33000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>48000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>148000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-575000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>96000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>95000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>59000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>46000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>88000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>176000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>50000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>67000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>94000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>262000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>137000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>128000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>106000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>145000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>119000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>130000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>89000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>13000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>136000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-87000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>73000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>54000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>107000</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,222 +2574,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-105000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-147000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>150000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>498000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>56000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-284000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>192000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>222000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>172000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>174000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>888000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>418000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>267000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>49000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>338000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>206000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>218000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>153000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>232000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>194000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-110000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>138000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>315000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>206000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>312000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>237000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>434000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>360000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>267000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>184000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>321000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>64000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>144000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>65000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>266000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-105000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-147000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>150000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>498000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>56000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-284000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>165000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>235000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>172000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-81000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>887000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>416000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>267000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-196000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>432000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>308000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>267000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>230000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>204000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>266000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-141000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>166000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>344000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>292000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>424000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>314000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>526000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>428000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>361000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>248000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>366000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>84000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>192000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>111000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2867,43 +2928,43 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-27000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>13000</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-237000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>64000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>95000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>93000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>303000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>432000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>124000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>82000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>252000</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
@@ -2911,12 +2972,12 @@
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
       <c r="Z29" s="3">
         <v>0</v>
       </c>
@@ -2924,37 +2985,40 @@
         <v>0</v>
       </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>2000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>36000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-23000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>368000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>1212000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>29000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-4000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>17000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>107000</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,8 +3234,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3182,207 +3252,213 @@
         <v>-1000</v>
       </c>
       <c r="G32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H32" s="3">
         <v>-2000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-19000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1000</v>
       </c>
-      <c r="J32" s="3" t="s">
+      <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-72000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-91000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-59000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-103000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-24000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-72000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-212000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-157000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>367000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-49000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-54000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-71000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-49000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-39000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-48000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-44000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>375000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-28000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-15000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-39000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>351000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>11000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-46000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-49000</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-105000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-147000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>150000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>498000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>56000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-284000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>165000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>235000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>172000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-318000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>951000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>511000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>360000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>107000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>864000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>432000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>349000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>482000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>204000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>266000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-141000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>165000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>344000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>292000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>424000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>316000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>562000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>405000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>729000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1460000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>395000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>80000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>209000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>218000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,227 +3564,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-105000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-147000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>150000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>498000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>56000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-284000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>165000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>235000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>172000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-318000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>951000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>511000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>360000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>107000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>864000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>432000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>349000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>482000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>204000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>266000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-141000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>165000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>344000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>292000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>424000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>316000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>562000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>405000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>729000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1460000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>395000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>80000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>209000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>218000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,115 +3871,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1156000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1170000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1159000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1049000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1070000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1113000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1149000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>746000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>636000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>804000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>511000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>826000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1031000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1295000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2122000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>706000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>787000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>595000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>678000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>847000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1239000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>511000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>697000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>787000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>641000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>589000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1026000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1073000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1141000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1018000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>998000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1041000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>998000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1033000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2562000</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3928,19 +4018,19 @@
         <v>0</v>
       </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>151000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>291000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>245000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
-        <v>4850000</v>
+        <v>0</v>
       </c>
       <c r="S42" s="3">
         <v>4850000</v>
@@ -3951,8 +4041,8 @@
       <c r="U42" s="3">
         <v>4850000</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>8</v>
+      <c r="V42" s="3">
+        <v>4850000</v>
       </c>
       <c r="W42" s="3" t="s">
         <v>8</v>
@@ -3969,8 +4059,8 @@
       <c r="AA42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB42" s="3">
-        <v>0</v>
+      <c r="AB42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC42" s="3">
         <v>0</v>
@@ -3999,706 +4089,727 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5008000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3362000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3550000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3633000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3478000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3492000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3552000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3630000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3729000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3765000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3967000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3968000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3854000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3610000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3976000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4024000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3779000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3419000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3422000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3461000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3649000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3673000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3693000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3876000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3903000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3916000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3963000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3907000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3804000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3287000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3343000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3283000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3078000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2852000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2807000</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2590000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1784000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1795000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1728000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1771000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1889000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1929000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1911000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1939000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1942000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1976000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1897000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1746000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1814000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2053000</v>
-      </c>
-      <c r="R44" s="3">
-        <v>1828000</v>
       </c>
       <c r="S44" s="3">
         <v>1828000</v>
       </c>
       <c r="T44" s="3">
+        <v>1828000</v>
+      </c>
+      <c r="U44" s="3">
         <v>2050000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2007000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2010000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2002000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2208000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2194000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2224000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2301000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2241000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2130000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2050000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2057000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2313000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2465000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2361000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>2394000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>2233000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>2222000</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>534000</v>
+      </c>
+      <c r="E45" s="3">
         <v>108000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>139000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>147000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>140000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>114000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>150000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>189000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>239000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>259000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>168000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>204000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>262000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>132000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1745000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>818000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>923000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>322000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>331000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>281000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>325000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>247000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>467000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>501000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>217000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>250000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>199000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>242000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>258000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1659000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>405000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>552000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>251000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>851000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>512000</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9288000</v>
+      </c>
+      <c r="E46" s="3">
         <v>6424000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6643000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6557000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6459000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6608000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6780000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6476000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6615000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6770000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6622000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7046000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7184000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>7096000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9896000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>12226000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>12167000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>11236000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>11288000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6599000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>7215000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6639000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7051000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7388000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>7062000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6996000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>7318000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>7272000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>7260000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>8277000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>7211000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>7237000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>6721000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>6670000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>8103000</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3">
         <v>160000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>161000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>163000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>160000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>163000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>184000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>183000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>187000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2480000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3215000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3214000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2888000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3026000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2983000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2888000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2972000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3435000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>3352000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>8505000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>8463000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>8809000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>8735000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>8725000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>8844000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>8718000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>8680000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>8599000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>8546000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>7441000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>7383000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>7367000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>7348000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>7393000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>7353000</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>16721000</v>
+      </c>
+      <c r="E48" s="3">
         <v>10091000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10398000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10392000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10472000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10598000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10892000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10922000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10875000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10855000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10606000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10617000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10709000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10824000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12068000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>12279000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>12367000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>12987000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>13120000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>13304000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13421000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13829000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>13648000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>13775000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13887000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13469000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>13476000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>13589000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>13788000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>13713000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>14533000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>14491000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>14520000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>13459000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>12652000</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11827000</v>
+      </c>
+      <c r="E49" s="3">
         <v>3183000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3194000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3204000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3215000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3224000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3233000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3245000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3253000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3261000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3345000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3124000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3128000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3130000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3274000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3317000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3242000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3315000</v>
-      </c>
-      <c r="U49" s="3">
-        <v>3304000</v>
       </c>
       <c r="V49" s="3">
         <v>3304000</v>
@@ -4707,49 +4818,52 @@
         <v>3304000</v>
       </c>
       <c r="X49" s="3">
+        <v>3304000</v>
+      </c>
+      <c r="Y49" s="3">
         <v>3347000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3412000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3441000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3393000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3374000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3371000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3378000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3414000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3411000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3420000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3409000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3402000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>3364000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>3362000</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,115 +5079,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2547000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2423000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2523000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2492000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2462000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2430000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2632000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2618000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2603000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>574000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1077000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1281000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1249000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1167000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1250000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>738000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>729000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>745000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>776000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>807000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>812000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>847000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1002000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1018000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>992000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1019000</v>
-      </c>
-      <c r="AC52" s="3">
-        <v>958000</v>
       </c>
       <c r="AD52" s="3">
         <v>958000</v>
       </c>
       <c r="AE52" s="3">
+        <v>958000</v>
+      </c>
+      <c r="AF52" s="3">
         <v>1022000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1061000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1266000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1373000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1310000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>2207000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1131000</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>41168000</v>
+      </c>
+      <c r="E54" s="3">
         <v>22800000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>23161000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>23063000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>23028000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>23261000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>23951000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>23683000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>23771000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>23940000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>24865000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>25282000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>25158000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>25243000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>29471000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>31448000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>31477000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>31718000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>31840000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>32519000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>33215000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>33471000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>33848000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>34347000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>34178000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>33576000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>33803000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>33796000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>34030000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>33903000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>33813000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>33877000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>33301000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>33093000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>32601000</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,650 +5491,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4224000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2316000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2436000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2350000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2322000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2442000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2363000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2394000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2541000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2708000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2668000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2678000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2657000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2606000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2704000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2565000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2354000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2320000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2226000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2206000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2379000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2423000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2349000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2498000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2518000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2413000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2510000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2478000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2534000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2458000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2408000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2362000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2380000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2199000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>2031000</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>676000</v>
+      </c>
+      <c r="E58" s="3">
         <v>349000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>413000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>410000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>287000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>291000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>271000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>400000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>510000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>763000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>616000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>293000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>197000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>196000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>233000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>116000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>31000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>29000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>179000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>33000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>664000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>168000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>402000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>676000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>809000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>639000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>555000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>684000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>587000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>311000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>958000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>824000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>454000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>239000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>78000</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1492000</v>
+      </c>
+      <c r="E59" s="3">
         <v>844000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>867000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>881000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>867000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>829000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>878000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>888000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>865000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1529000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1521000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1381000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1288000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1342000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1761000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5954000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6005000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5935000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>6071000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>6091000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>6299000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>6055000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1978000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1875000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1626000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1642000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1538000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1456000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1344000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2333000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1503000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1816000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1433000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1631000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1432000</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6988000</v>
+      </c>
+      <c r="E60" s="3">
         <v>4258000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4353000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4114000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3854000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3959000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3882000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4067000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4266000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5000000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4805000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4352000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4142000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4144000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4698000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8635000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8390000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8284000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8476000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>8330000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>9342000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>8646000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4729000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5049000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4953000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4694000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4603000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4618000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4465000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>5102000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4869000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>5002000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>4267000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>4069000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>3541000</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9652000</v>
+      </c>
+      <c r="E61" s="3">
         <v>5660000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5602000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5628000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5760000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5767000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5866000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5876000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5757000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4816000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4766000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5275000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5468000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5383000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8241000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>7073000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>7954000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8064000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>8525000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>9432000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>9561000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>9597000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>9957000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>10050000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>9965000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>10015000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>10700000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>10805000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>10759000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>10846000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>11373000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>10392000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>10823000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>11075000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>10823000</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3464000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3271000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3247000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3216000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3200000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3208000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3198000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3179000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3193000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5627000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5806000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6612000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6661000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6634000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6909000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7386000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7362000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7502000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7743000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>7697000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>7451000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>7510000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>11706000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>11749000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>11791000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>11484000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>11442000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>11509000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>11541000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>11414000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>12638000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>13918000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>13617000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>13590000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>14008000</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>23076000</v>
+      </c>
+      <c r="E66" s="3">
         <v>14627000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14532000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>14468000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>14771000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>14906000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>15069000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>15279000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>15382000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>15443000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>15377000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>16239000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>16271000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>16161000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>19849000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>23096000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>23719000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>23864000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>24747000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>25462000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>26358000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>25758000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>26407000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>26865000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>26732000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>26214000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>26763000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>26952000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>26785000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>27381000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>28899000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>29332000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>28726000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>28752000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>28392000</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6791,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>9038000</v>
+      </c>
+      <c r="E72" s="3">
         <v>9393000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9705000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>9719000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9386000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9491000</v>
-      </c>
-      <c r="I72" s="3">
-        <v>9938000</v>
       </c>
       <c r="J72" s="3">
         <v>9938000</v>
       </c>
       <c r="K72" s="3">
+        <v>9938000</v>
+      </c>
+      <c r="L72" s="3">
         <v>9866000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9855000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>10340000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9557000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9218000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9029000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>9103000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>8442000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8214000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8070000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>8122000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>8123000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>8062000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>8408000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>8447000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>8302000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>8211000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>7465000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>7353000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6988000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>6783000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>6180000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4918000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4717000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>4832000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>4818000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>4793000</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18092000</v>
+      </c>
+      <c r="E76" s="3">
         <v>8173000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8629000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8595000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8257000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8355000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8882000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8404000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8389000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8497000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9488000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9043000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8887000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9082000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9622000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8352000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7758000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7854000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7093000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7057000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>6857000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7713000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7441000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7482000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7446000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7362000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>7040000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6844000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>7245000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6522000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4914000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>4545000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>4575000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>4341000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>4209000</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,227 +7729,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-105000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-147000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>150000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>498000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>56000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-284000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>165000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>235000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>172000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-318000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>951000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>511000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>360000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>107000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>864000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>432000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>349000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>482000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>204000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>266000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-141000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>165000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>344000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>292000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>424000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>316000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>562000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>405000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>729000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1460000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>395000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>80000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>209000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>218000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,115 +7996,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>269000</v>
+      </c>
+      <c r="E83" s="3">
         <v>257000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>249000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>235000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>232000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>240000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>250000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>256000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>250000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>251000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>261000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>267000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>261000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>277000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>318000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>306000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>309000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1287000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>320000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>312000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>323000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>343000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>327000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>321000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>315000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>338000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>335000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>330000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>325000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>348000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>373000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>357000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>345000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>328000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>314000</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-288000</v>
+      </c>
+      <c r="E89" s="3">
         <v>397000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>521000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>365000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>395000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>492000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>468000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>528000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>345000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>761000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>435000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>390000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>588000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>107000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>690000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>775000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>458000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3061000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>737000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>886000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>640000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>947000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>884000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1046000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>733000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>821000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>941000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>801000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>663000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1188000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-705000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>641000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>633000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>912000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>341000</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,115 +8806,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-330000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-260000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-212000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-198000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-251000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-305000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-228000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-267000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-341000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-322000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-238000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-186000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-185000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-201000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-126000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-133000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-89000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-751000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-119000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-252000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-286000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-363000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-285000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-335000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-293000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-286000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-357000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-440000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-489000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-456000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-271000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-290000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-374000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-445000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-266000</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,115 +9134,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>237000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-174000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-188000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-199000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-247000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-310000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>245000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-264000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-339000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-315000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-76000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-37000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-180000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-130000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>5598000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>328000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>258000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-269000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>134000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-299000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-35000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-306000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-279000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-421000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-294000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-259000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-346000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-475000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-489000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-383000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-278000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-330000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-400000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-2527000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-279000</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,25 +9286,26 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>161000</v>
+        <v>244000</v>
       </c>
       <c r="E96" s="3">
         <v>161000</v>
       </c>
       <c r="F96" s="3">
+        <v>161000</v>
+      </c>
+      <c r="G96" s="3">
         <v>160000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>161000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>160000</v>
       </c>
       <c r="I96" s="3">
         <v>160000</v>
@@ -9080,73 +9314,73 @@
         <v>160000</v>
       </c>
       <c r="K96" s="3">
+        <v>160000</v>
+      </c>
+      <c r="L96" s="3">
         <v>162000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-164000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-165000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-170000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-174000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-178000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-199000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-201000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-202000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-806000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-202000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-201000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-202000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-201000</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-197000</v>
       </c>
       <c r="Z96" s="3">
         <v>-197000</v>
       </c>
       <c r="AA96" s="3">
-        <v>-201000</v>
+        <v>-197000</v>
       </c>
       <c r="AB96" s="3">
         <v>-201000</v>
       </c>
       <c r="AC96" s="3">
+        <v>-201000</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-195000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-196000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-197000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-196000</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-191000</v>
       </c>
       <c r="AH96" s="3">
         <v>-191000</v>
@@ -9155,13 +9389,16 @@
         <v>-191000</v>
       </c>
       <c r="AJ96" s="3">
+        <v>-191000</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-190000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-181000</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,325 +9724,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-187000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-223000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-174000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-191000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-222000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-306000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-230000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-108000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-159000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-669000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-643000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-583000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2301000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3359000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1211000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-504000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2700000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1042000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-982000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>165000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-842000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-671000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-487000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-389000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1000000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-636000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-354000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-56000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-779000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>930000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-266000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-284000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>104000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>1232000</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3">
         <v>4000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-4000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>4000</v>
-      </c>
-      <c r="G101" s="3">
-        <v>6000</v>
       </c>
       <c r="H101" s="3">
         <v>6000</v>
       </c>
       <c r="I101" s="3">
+        <v>6000</v>
+      </c>
+      <c r="J101" s="3">
         <v>-5000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>6000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-5000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-14000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>27000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-20000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-8000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>2000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>3000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-42000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>15000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-24000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>8000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>2000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-40000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>5000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>10000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>16000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-18000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E102" s="3">
         <v>11000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>110000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-21000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-43000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-36000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>403000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>38000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-96000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>293000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-315000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-293000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-176000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2326000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2915000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-81000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>192000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>84000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-169000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-392000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>728000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-186000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-90000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>146000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>52000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-437000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-47000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-68000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>123000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>20000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-43000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>43000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-35000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-1529000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>1308000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
   <si>
     <t>IP</t>
   </si>
@@ -656,492 +656,505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6767000</v>
+      </c>
+      <c r="E8" s="3">
         <v>5901000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4580000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4686000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4734000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4619000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4601000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4613000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4682000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5020000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5133000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5402000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5389000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5237000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5086000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4914000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4770000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4593000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>17565000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5123000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4866000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5352000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5498000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5568000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5667000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5643000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5951000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5901000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5833000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5621000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5711000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5517000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>5383000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>5132000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3797000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>5266000</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4876000</v>
+      </c>
+      <c r="E9" s="3">
         <v>4259000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3161000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3329000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3335000</v>
       </c>
-      <c r="H9" s="3">
-        <v>3424000</v>
-      </c>
       <c r="I9" s="3">
+        <v>3414000</v>
+      </c>
+      <c r="J9" s="3">
         <v>3246000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3316000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3360000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3642000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3668000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3830000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3806000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3839000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3659000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3423000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3402000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3348000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>12339000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3541000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3427000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3732000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3669000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3766000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3902000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3932000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3800000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3889000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3923000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3946000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3702000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3705000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3749000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>3635000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2712000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>3622000</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1891000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1642000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1419000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1357000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1399000</v>
       </c>
-      <c r="H10" s="3">
-        <v>1195000</v>
-      </c>
       <c r="I10" s="3">
+        <v>1205000</v>
+      </c>
+      <c r="J10" s="3">
         <v>1355000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1297000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1322000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1378000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1465000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1572000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1583000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1398000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1427000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1491000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1368000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1245000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5226000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1582000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1439000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1620000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1829000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1802000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1765000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1711000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2151000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2012000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1910000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1675000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2009000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1812000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1634000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1497000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1085000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1644000</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1180,8 +1193,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1290,8 +1304,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,228 +1417,237 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>16000</v>
+        <v>35000</v>
       </c>
       <c r="E14" s="3">
+        <v>213000</v>
+      </c>
+      <c r="F14" s="3">
         <v>506000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>120000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>49000</v>
       </c>
-      <c r="H14" s="3">
-        <v>8000</v>
-      </c>
       <c r="I14" s="3">
+        <v>23000</v>
+      </c>
+      <c r="J14" s="3">
         <v>557000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>29000</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>72000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>93000</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>266000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-321000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>165000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>32000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>660000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>100000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>26000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>352000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>88000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>61000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>152000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-7000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-19000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>122000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>26000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>22000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>83000</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>347000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>-6000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>7000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>51000</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>571000</v>
+        <v>480000</v>
       </c>
       <c r="E15" s="3">
+        <v>374000</v>
+      </c>
+      <c r="F15" s="3">
         <v>266000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>267000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>261000</v>
       </c>
-      <c r="H15" s="3">
-        <v>278000</v>
-      </c>
       <c r="I15" s="3">
+        <v>273000</v>
+      </c>
+      <c r="J15" s="3">
         <v>267000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>258000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>244000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>241000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>251000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>261000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>267000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>261000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>277000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>280000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>272000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>268000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1091000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>320000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>312000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>323000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>343000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>327000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>321000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>315000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>338000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>335000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>330000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>325000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>339000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>350000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>334000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>320000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>225000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>314000</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>5939000</v>
+        <v>6509000</v>
       </c>
       <c r="E17" s="3">
+        <v>5742000</v>
+      </c>
+      <c r="F17" s="3">
         <v>4242000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4435000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4424000</v>
       </c>
-      <c r="H17" s="3">
-        <v>4480000</v>
-      </c>
       <c r="I17" s="3">
+        <v>4465000</v>
+      </c>
+      <c r="J17" s="3">
         <v>4318000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4294000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4368000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4737000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4790000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5030000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4851000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4901000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4981000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4485000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4613000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4320000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>16866000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4742000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4503000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5276000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4979000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4978000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5204000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5085000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5007000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5192000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5175000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5124000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4976000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4851000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>5223000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4732000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3542000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>4761000</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-38000</v>
+        <v>258000</v>
       </c>
       <c r="E18" s="3">
+        <v>159000</v>
+      </c>
+      <c r="F18" s="3">
         <v>338000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>251000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>310000</v>
       </c>
-      <c r="H18" s="3">
-        <v>139000</v>
-      </c>
       <c r="I18" s="3">
+        <v>154000</v>
+      </c>
+      <c r="J18" s="3">
         <v>283000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>319000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>314000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>283000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>343000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>372000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>538000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>336000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>105000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>429000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>157000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>273000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>699000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>381000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>363000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>76000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>519000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>590000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>463000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>558000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>944000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>709000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>658000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>497000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>735000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>666000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>160000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>400000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>255000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>505000</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,8 +1950,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1935,540 +1969,555 @@
         <v>1000</v>
       </c>
       <c r="H20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I20" s="3">
         <v>2000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>19000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1000</v>
       </c>
-      <c r="K20" s="3" t="s">
+      <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>72000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>91000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>59000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>103000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>24000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>72000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>212000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>157000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-367000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>49000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>54000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>71000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>49000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>39000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>48000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>44000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-375000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>28000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>15000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>39000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-351000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-11000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>4000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>46000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>49000</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>737000</v>
+      </c>
+      <c r="E21" s="3">
         <v>532000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>603000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>517000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>570000</v>
       </c>
-      <c r="H21" s="3">
-        <v>415000</v>
-      </c>
       <c r="I21" s="3">
+        <v>425000</v>
+      </c>
+      <c r="J21" s="3">
         <v>531000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>576000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>558000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>523000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>666000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>724000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>864000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>700000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>406000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>819000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>675000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>739000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1619000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>750000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>729000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>470000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>911000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>956000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>832000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>917000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>907000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1072000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1003000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>861000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>732000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1028000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>520000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>749000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>629000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>868000</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>143000</v>
+      </c>
+      <c r="E22" s="3">
         <v>133000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>108000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>106000</v>
       </c>
-      <c r="G22" s="3">
-        <v>55000</v>
-      </c>
       <c r="H22" s="3">
+        <v>107000</v>
+      </c>
+      <c r="I22" s="3">
         <v>109000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>110000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>105000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>59000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>103000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>93000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>150000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>83000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>77000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>85000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>104000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>117000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>124000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>3000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>148000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>156000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>163000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>168000</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>177000</v>
       </c>
       <c r="AA22" s="3">
         <v>177000</v>
       </c>
       <c r="AB22" s="3">
+        <v>177000</v>
+      </c>
+      <c r="AC22" s="3">
         <v>184000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>187000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>184000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>183000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>180000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>187000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>198000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>186000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>187000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>182000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>181000</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>115000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-136000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-225000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>79000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>205000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>83000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-345000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>231000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>255000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>220000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>322000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>313000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>514000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>362000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>44000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>397000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>252000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>306000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>329000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>282000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>261000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-16000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>400000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>452000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>334000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>418000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>382000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>553000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>490000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>356000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>197000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>457000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-23000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>217000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>119000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>373000</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-31000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-78000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-71000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-293000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>27000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-61000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>39000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>33000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>48000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>148000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-575000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>96000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>95000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-5000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>59000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>46000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>88000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>176000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>50000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>67000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>94000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>262000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>137000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>128000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>106000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>145000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>119000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>130000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>89000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>13000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>136000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-87000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>73000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>54000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>107000</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-105000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-147000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>150000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>498000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>56000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-284000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>192000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>222000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>172000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>174000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>888000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>418000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>267000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>49000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>338000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>206000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>218000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>153000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>232000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>194000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-110000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>138000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>315000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>206000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>312000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>237000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>434000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>360000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>267000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>184000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>321000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>64000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>144000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>65000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>266000</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-105000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-147000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>150000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>498000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>56000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-284000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>165000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>235000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>172000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-81000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>887000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>416000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>267000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-196000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>432000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>308000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>267000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>230000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>204000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>266000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-141000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>166000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>344000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>292000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>424000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>314000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>526000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>428000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>361000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>248000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>366000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>84000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>192000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>111000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2931,43 +2992,43 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>-27000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>13000</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-237000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>64000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>95000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>93000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>303000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>432000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>124000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>82000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>252000</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2975,12 +3036,12 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
       <c r="AA29" s="3">
         <v>0</v>
       </c>
@@ -2988,37 +3049,40 @@
         <v>0</v>
       </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>2000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>36000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-23000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>368000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>1212000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>29000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-4000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>17000</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>107000</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,8 +3304,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3255,210 +3325,216 @@
         <v>-1000</v>
       </c>
       <c r="H32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-2000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-19000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1000</v>
       </c>
-      <c r="K32" s="3" t="s">
+      <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-72000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-91000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-59000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-103000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-24000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-72000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-212000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-157000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>367000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-49000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-54000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-71000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-49000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-39000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-48000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-44000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>375000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-28000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-15000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-39000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>351000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>11000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-46000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-49000</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-105000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-147000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>150000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>498000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>56000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-284000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>165000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>235000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>172000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-318000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>951000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>511000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>360000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>107000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>864000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>432000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>349000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>482000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>204000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>266000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-141000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>165000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>344000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>292000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>424000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>316000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>562000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>405000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>729000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1460000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>395000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>80000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>209000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>218000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-105000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-147000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>150000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>498000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>56000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-284000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>165000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>235000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>172000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-318000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>951000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>511000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>360000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>107000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>864000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>432000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>349000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>482000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>204000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>266000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-141000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>165000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>344000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>292000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>424000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>316000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>562000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>405000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>729000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1460000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>395000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>80000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>209000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>218000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,118 +3958,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1135000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1156000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1170000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1159000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1049000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1070000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1113000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1149000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>746000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>636000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>804000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>511000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>826000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1031000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1295000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2122000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>706000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>787000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>595000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>678000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>847000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1239000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>511000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>697000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>787000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>641000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>589000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1026000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1073000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1141000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1018000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>998000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1041000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>998000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1033000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2562000</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4021,19 +4111,19 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>151000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>291000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>245000</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
-      </c>
       <c r="S42" s="3">
-        <v>4850000</v>
+        <v>0</v>
       </c>
       <c r="T42" s="3">
         <v>4850000</v>
@@ -4044,8 +4134,8 @@
       <c r="V42" s="3">
         <v>4850000</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>8</v>
+      <c r="W42" s="3">
+        <v>4850000</v>
       </c>
       <c r="X42" s="3" t="s">
         <v>8</v>
@@ -4062,8 +4152,8 @@
       <c r="AB42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC42" s="3">
-        <v>0</v>
+      <c r="AC42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD42" s="3">
         <v>0</v>
@@ -4092,727 +4182,748 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5218000</v>
+      </c>
+      <c r="E43" s="3">
         <v>5008000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3362000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3550000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3633000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3478000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3492000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3552000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3630000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3729000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3765000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3967000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3968000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3854000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3610000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3976000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4024000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3779000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3419000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3422000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3461000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3649000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3673000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3693000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3876000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3903000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3916000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3963000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3907000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3804000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3287000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3343000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3283000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3078000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2852000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>2807000</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2658000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2590000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1784000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1795000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1728000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1771000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1889000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1929000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1911000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1939000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1942000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1976000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1897000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1746000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1814000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2053000</v>
-      </c>
-      <c r="S44" s="3">
-        <v>1828000</v>
       </c>
       <c r="T44" s="3">
         <v>1828000</v>
       </c>
       <c r="U44" s="3">
+        <v>1828000</v>
+      </c>
+      <c r="V44" s="3">
         <v>2050000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2007000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2010000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2002000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2208000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2194000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2224000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2301000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2241000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2130000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2050000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2057000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2313000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2465000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>2361000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>2394000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>2233000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>2222000</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>488000</v>
+      </c>
+      <c r="E45" s="3">
         <v>534000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>108000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>139000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>147000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>140000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>114000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>150000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>189000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>239000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>259000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>168000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>204000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>262000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>132000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1745000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>818000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>923000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>322000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>331000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>281000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>325000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>247000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>467000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>501000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>217000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>250000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>199000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>242000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>258000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1659000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>405000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>552000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>251000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>851000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>512000</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9499000</v>
+      </c>
+      <c r="E46" s="3">
         <v>9288000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6424000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6643000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6557000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6459000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6608000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6780000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6476000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6615000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6770000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6622000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7046000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>7184000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>7096000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9896000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>12226000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>12167000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>11236000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>11288000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6599000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7215000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6639000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7051000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>7388000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>7062000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6996000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>7318000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>7272000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>7260000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>8277000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>7211000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>7237000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>6721000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>6670000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>8103000</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3">
         <v>160000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>161000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>163000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>160000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>163000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>184000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>183000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>187000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2480000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3215000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3214000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2888000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3026000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2983000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2888000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2972000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>3435000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>3352000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>8505000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>8463000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>8809000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>8735000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>8725000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>8844000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>8718000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>8680000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>8599000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>8546000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>7441000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>7383000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>7367000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>7348000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>7393000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>7353000</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>17588000</v>
+      </c>
+      <c r="E48" s="3">
         <v>16721000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10091000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10398000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10392000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10472000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10598000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10892000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10922000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10875000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10855000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10606000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10617000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10709000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>10824000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>12068000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>12279000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>12367000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>12987000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>13120000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13304000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13421000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>13829000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>13648000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13775000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13887000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>13469000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>13476000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>13589000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>13788000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>13713000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>14533000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>14491000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>14520000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>13459000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>12652000</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11937000</v>
+      </c>
+      <c r="E49" s="3">
         <v>11827000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3183000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3194000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3204000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3215000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3224000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3233000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3245000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3253000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3261000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3345000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3124000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3128000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3130000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3274000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3317000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3242000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3315000</v>
-      </c>
-      <c r="V49" s="3">
-        <v>3304000</v>
       </c>
       <c r="W49" s="3">
         <v>3304000</v>
@@ -4821,49 +4932,52 @@
         <v>3304000</v>
       </c>
       <c r="Y49" s="3">
+        <v>3304000</v>
+      </c>
+      <c r="Z49" s="3">
         <v>3347000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3412000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3441000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3393000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3374000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3371000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3378000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3414000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3411000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3420000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3409000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>3402000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>3364000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>3362000</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,118 +5199,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2583000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2547000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2423000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2523000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2492000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2462000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2430000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2632000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2618000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2603000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>574000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1077000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1281000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1249000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1167000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1250000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>738000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>729000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>745000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>776000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>807000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>812000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>847000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1002000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1018000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>992000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1019000</v>
-      </c>
-      <c r="AD52" s="3">
-        <v>958000</v>
       </c>
       <c r="AE52" s="3">
         <v>958000</v>
       </c>
       <c r="AF52" s="3">
+        <v>958000</v>
+      </c>
+      <c r="AG52" s="3">
         <v>1022000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1061000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1266000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1373000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1310000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>2207000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1131000</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>42376000</v>
+      </c>
+      <c r="E54" s="3">
         <v>41168000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>22800000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>23161000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>23063000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>23028000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>23261000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>23951000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>23683000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>23771000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>23940000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>24865000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>25282000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>25158000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>25243000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>29471000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>31448000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>31477000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>31718000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>31840000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>32519000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>33215000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>33471000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>33848000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>34347000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>34178000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>33576000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>33803000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>33796000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>34030000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>33903000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>33813000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>33877000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>33301000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>33093000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>32601000</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,668 +5622,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4336000</v>
+      </c>
+      <c r="E57" s="3">
         <v>4224000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2316000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2436000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2350000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2322000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2442000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2363000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2394000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2541000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2708000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2668000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2678000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2657000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2606000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2704000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2565000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2354000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2320000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2226000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2206000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2379000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2423000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2349000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2498000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2518000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2413000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2510000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2478000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2534000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2458000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2408000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2362000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2380000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>2199000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>2031000</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>472000</v>
+      </c>
+      <c r="E58" s="3">
         <v>676000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>349000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>413000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>410000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>287000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>291000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>271000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>400000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>510000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>763000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>616000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>293000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>197000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>196000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>233000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>116000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>31000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>29000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>179000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>33000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>664000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>168000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>402000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>676000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>809000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>639000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>555000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>684000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>587000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>311000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>958000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>824000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>454000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>239000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>78000</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1638000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1492000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>844000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>867000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>881000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>867000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>829000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>878000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>888000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>865000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1529000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1521000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1381000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1288000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1342000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1761000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5954000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>6005000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5935000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>6071000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>6091000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>6299000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>6055000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1978000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1875000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1626000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1642000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1538000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1456000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1344000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2333000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1503000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1816000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1433000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1631000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1432000</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7121000</v>
+      </c>
+      <c r="E60" s="3">
         <v>6988000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4258000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4353000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4114000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3854000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3959000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3882000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4067000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4266000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5000000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4805000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4352000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4142000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4144000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4698000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8635000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8390000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8284000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>8476000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>8330000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>9342000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>8646000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4729000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5049000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4953000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4694000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4603000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4618000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4465000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5102000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>4869000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>5002000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>4267000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>4069000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>3541000</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10169000</v>
+      </c>
+      <c r="E61" s="3">
         <v>9652000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5660000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5602000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5628000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5760000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5767000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5866000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5876000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5757000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4816000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4766000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5275000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5468000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5383000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>8241000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>7073000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>7954000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>8064000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>8525000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>9432000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>9561000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>9597000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>9957000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>10050000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>9965000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>10015000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>10700000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>10805000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>10759000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>10846000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>11373000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>10392000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>10823000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>11075000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>10823000</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3446000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3464000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3271000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3247000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3216000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3200000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3208000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3198000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3179000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3193000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5627000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5806000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6612000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6661000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6634000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6909000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7386000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7362000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7502000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>7743000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>7697000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>7451000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>7510000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>11706000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>11749000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>11791000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>11484000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>11442000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>11509000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>11541000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>11414000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>12638000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>13918000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>13617000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>13590000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>14008000</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>23759000</v>
+      </c>
+      <c r="E66" s="3">
         <v>23076000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14627000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>14532000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>14468000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>14771000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14906000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>15069000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>15279000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>15382000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>15443000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>15377000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>16239000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>16271000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>16161000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>19849000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>23096000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>23719000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>23864000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>24747000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>25462000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>26358000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>25758000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>26407000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>26865000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>26732000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>26214000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>26763000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>26952000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>26785000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>27381000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>28899000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>29332000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>28726000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>28752000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>28392000</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8865000</v>
+      </c>
+      <c r="E72" s="3">
         <v>9038000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9393000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>9705000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9719000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9386000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9491000</v>
-      </c>
-      <c r="J72" s="3">
-        <v>9938000</v>
       </c>
       <c r="K72" s="3">
         <v>9938000</v>
       </c>
       <c r="L72" s="3">
+        <v>9938000</v>
+      </c>
+      <c r="M72" s="3">
         <v>9866000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9855000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>10340000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9557000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9218000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>9029000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>9103000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8442000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8214000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>8070000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>8122000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>8123000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>8062000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>8408000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>8447000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>8302000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>8211000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>7465000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>7353000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>6988000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>6783000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>6180000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4918000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>4717000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>4832000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>4818000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>4793000</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18617000</v>
+      </c>
+      <c r="E76" s="3">
         <v>18092000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8173000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8629000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8595000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8257000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8355000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8882000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8404000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8389000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8497000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9488000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9043000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8887000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9082000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9622000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8352000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7758000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7854000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7093000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7057000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>6857000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7713000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7441000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7482000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7446000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>7362000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>7040000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6844000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>7245000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6522000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>4914000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>4545000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>4575000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>4341000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>4209000</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-105000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-147000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>150000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>498000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>56000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-284000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>165000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>235000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>172000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-318000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>951000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>511000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>360000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>107000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>864000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>432000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>349000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>482000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>204000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>266000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-141000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>165000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>344000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>292000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>424000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>316000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>562000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>405000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>729000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1460000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>395000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>80000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>209000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>218000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,118 +8195,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>251000</v>
+      </c>
+      <c r="E83" s="3">
         <v>269000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>257000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>249000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>235000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>232000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>240000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>250000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>256000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>250000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>251000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>261000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>267000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>261000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>277000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>318000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>306000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>309000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1287000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>320000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>312000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>323000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>343000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>327000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>321000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>315000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>338000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>335000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>330000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>325000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>348000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>373000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>357000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>345000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>328000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>314000</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>476000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-288000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>397000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>521000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>365000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>395000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>492000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>468000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>528000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>345000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>761000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>435000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>390000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>588000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>107000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>690000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>775000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>458000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3061000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>737000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>886000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>640000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>947000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>884000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1046000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>733000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>821000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>941000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>801000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>663000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1188000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-705000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>641000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>633000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>912000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>341000</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,118 +9027,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-422000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-330000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-260000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-212000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-198000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-251000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-305000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-228000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-267000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-341000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-322000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-238000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-186000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-185000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-201000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-126000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-133000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-89000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-751000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-119000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-252000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-286000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-363000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-285000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-335000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-293000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-286000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-357000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-440000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-489000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-456000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-271000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-290000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-374000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-445000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-266000</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,118 +9364,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-275000</v>
+      </c>
+      <c r="E94" s="3">
         <v>237000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-174000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-188000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-199000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-247000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-310000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>245000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-264000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-339000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-315000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-76000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-37000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-180000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-130000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>5598000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>328000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>258000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-269000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>134000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-299000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-35000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-306000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-279000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-421000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-294000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-259000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-346000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-475000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-489000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-383000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-278000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-330000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-400000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-2527000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-279000</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,8 +9520,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9296,19 +9530,19 @@
         <v>244000</v>
       </c>
       <c r="E96" s="3">
-        <v>161000</v>
+        <v>244000</v>
       </c>
       <c r="F96" s="3">
         <v>161000</v>
       </c>
       <c r="G96" s="3">
+        <v>161000</v>
+      </c>
+      <c r="H96" s="3">
         <v>160000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>161000</v>
-      </c>
-      <c r="I96" s="3">
-        <v>160000</v>
       </c>
       <c r="J96" s="3">
         <v>160000</v>
@@ -9317,73 +9551,73 @@
         <v>160000</v>
       </c>
       <c r="L96" s="3">
+        <v>160000</v>
+      </c>
+      <c r="M96" s="3">
         <v>162000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-164000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-165000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-170000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-174000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-178000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-199000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-201000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-202000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-806000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-202000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-201000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-202000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-201000</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-197000</v>
       </c>
       <c r="AA96" s="3">
         <v>-197000</v>
       </c>
       <c r="AB96" s="3">
-        <v>-201000</v>
+        <v>-197000</v>
       </c>
       <c r="AC96" s="3">
         <v>-201000</v>
       </c>
       <c r="AD96" s="3">
+        <v>-201000</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-195000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-196000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-197000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-196000</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>-191000</v>
       </c>
       <c r="AI96" s="3">
         <v>-191000</v>
@@ -9392,13 +9626,16 @@
         <v>-191000</v>
       </c>
       <c r="AK96" s="3">
+        <v>-191000</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-190000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-181000</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,334 +9970,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-274000</v>
+      </c>
+      <c r="E100" s="3">
         <v>21000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-187000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-223000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-174000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-191000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-222000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-306000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-230000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-108000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-159000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-669000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-643000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-583000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2301000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3359000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1211000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-504000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2700000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1042000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-982000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>165000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-842000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-671000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-487000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-389000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1000000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-636000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-354000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-56000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-779000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>930000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-266000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-284000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>104000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>1232000</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
+      <c r="D101" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>4000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-4000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>4000</v>
-      </c>
-      <c r="H101" s="3">
-        <v>6000</v>
       </c>
       <c r="I101" s="3">
         <v>6000</v>
       </c>
       <c r="J101" s="3">
+        <v>6000</v>
+      </c>
+      <c r="K101" s="3">
         <v>-5000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>6000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-5000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-2000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-14000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>27000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-20000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-8000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>2000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>3000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-42000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>15000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-24000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>8000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>2000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>1000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-40000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>5000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>10000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>16000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-18000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-12000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>11000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>110000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-21000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-43000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-36000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>403000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>38000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-96000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>293000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-315000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-293000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-176000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2326000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2915000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-81000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>192000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>84000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-169000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-392000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>728000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-186000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-90000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>146000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>52000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-437000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-47000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-68000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>123000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>20000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-43000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>43000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-35000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-1529000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>1308000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="92">
   <si>
     <t>IP</t>
   </si>
@@ -656,518 +656,530 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6006000</v>
+      </c>
+      <c r="E8" s="3">
         <v>6222000</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5901000</v>
       </c>
-      <c r="G8" s="3">
-        <v>4580000</v>
-      </c>
       <c r="H8" s="3">
+        <v>3922000</v>
+      </c>
+      <c r="I8" s="3">
         <v>3979000</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4619000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4601000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4613000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4682000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5020000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5133000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5402000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5389000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5237000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5086000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4914000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4770000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4593000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>17565000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5123000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4866000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5352000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5498000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5568000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5667000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5643000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5951000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5901000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5833000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5621000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>5711000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>5517000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>5383000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>5132000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>3797000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>5266000</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4092000</v>
+      </c>
+      <c r="E9" s="3">
         <v>4280000</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4259000</v>
       </c>
-      <c r="G9" s="3">
-        <v>3161000</v>
-      </c>
       <c r="H9" s="3">
+        <v>2688000</v>
+      </c>
+      <c r="I9" s="3">
         <v>2873000</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3414000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3246000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3316000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3360000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3642000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3668000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3830000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3806000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3839000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3659000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3423000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3402000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3348000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>12339000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3541000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3427000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3732000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3669000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3766000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3902000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3932000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3800000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3889000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3923000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3946000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3702000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>3705000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>3749000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>3635000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>2712000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>3622000</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1914000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1942000</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1642000</v>
       </c>
-      <c r="G10" s="3">
-        <v>1419000</v>
-      </c>
       <c r="H10" s="3">
+        <v>1234000</v>
+      </c>
+      <c r="I10" s="3">
         <v>1106000</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1205000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1355000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1297000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1322000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1378000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1465000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1572000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1583000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1398000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1427000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1491000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1368000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1245000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>5226000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1582000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1439000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1620000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1829000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1802000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1765000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1711000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2151000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2012000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1910000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1675000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2009000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1812000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1634000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1497000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1085000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1644000</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1208,8 +1220,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1324,8 +1337,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1440,240 +1456,249 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>380000</v>
-      </c>
-      <c r="E14" s="3" t="s">
+        <v>2948000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1055000</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>213000</v>
       </c>
-      <c r="G14" s="3">
-        <v>506000</v>
-      </c>
       <c r="H14" s="3">
+        <v>424000</v>
+      </c>
+      <c r="I14" s="3">
         <v>62000</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>23000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>557000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>29000</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
         <v>72000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>93000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>266000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-321000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>165000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>32000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>660000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>100000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>26000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>352000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>88000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>61000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>152000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-7000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-19000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>122000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>26000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>22000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>83000</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
-      </c>
       <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
         <v>347000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>-6000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>7000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>51000</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1099000</v>
+        <v>611000</v>
       </c>
       <c r="E15" s="3">
+        <v>424000</v>
+      </c>
+      <c r="F15" s="3">
         <v>480000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>374000</v>
       </c>
-      <c r="G15" s="3">
-        <v>266000</v>
-      </c>
       <c r="H15" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="I15" s="3">
         <v>208000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>261000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>273000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>267000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>258000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>244000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>241000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>251000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>261000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>267000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>261000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>277000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>280000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>272000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>268000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1091000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>320000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>312000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>323000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>343000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>327000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>321000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>315000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>338000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>335000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>330000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>325000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>339000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>350000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>334000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>320000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>225000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>314000</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,240 +1736,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>6432000</v>
-      </c>
-      <c r="E17" s="3" t="s">
+        <v>5617000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>5757000</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5742000</v>
       </c>
-      <c r="G17" s="3">
-        <v>4242000</v>
-      </c>
       <c r="H17" s="3">
+        <v>3327000</v>
+      </c>
+      <c r="I17" s="3">
         <v>3860000</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4465000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4318000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4294000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4368000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4737000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4790000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5030000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4851000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4901000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4981000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4485000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4613000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4320000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>16866000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4742000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4503000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5276000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4979000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4978000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5204000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5085000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5007000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5192000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5175000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5124000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4976000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4851000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>5223000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>4732000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>3542000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>4761000</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-210000</v>
-      </c>
-      <c r="E18" s="3" t="s">
+        <v>389000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>465000</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>159000</v>
       </c>
-      <c r="G18" s="3">
-        <v>338000</v>
-      </c>
       <c r="H18" s="3">
+        <v>595000</v>
+      </c>
+      <c r="I18" s="3">
         <v>119000</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>154000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>283000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>319000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>314000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>283000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>343000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>372000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>538000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>336000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>105000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>429000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>157000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>273000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>699000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>381000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>363000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>76000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>519000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>590000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>463000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>558000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>944000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>709000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>658000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>497000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>735000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>666000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>160000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>400000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>255000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>505000</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1985,19 +2017,20 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>1000</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="F20" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="F20" s="3">
-        <v>1000</v>
       </c>
       <c r="G20" s="3">
         <v>1000</v>
@@ -2005,568 +2038,583 @@
       <c r="H20" s="3">
         <v>1000</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="I20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>19000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1000</v>
       </c>
-      <c r="M20" s="3" t="s">
+      <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>72000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>91000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>59000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>103000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>24000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>72000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>212000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>157000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-367000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>49000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>54000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>71000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>49000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>39000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>48000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>44000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-375000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>28000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>15000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>39000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-351000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-11000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>3000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>4000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>46000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>49000</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1000000</v>
+      </c>
+      <c r="E21" s="3">
         <v>888000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>480000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>532000</v>
       </c>
-      <c r="G21" s="3">
-        <v>603000</v>
-      </c>
       <c r="H21" s="3">
+        <v>582000</v>
+      </c>
+      <c r="I21" s="3">
         <v>326000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>261000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>425000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>531000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>576000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>558000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>523000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>666000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>724000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>864000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>700000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>406000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>819000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>675000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>739000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1619000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>750000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>729000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>470000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>911000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>956000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>832000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>917000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>907000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1072000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1003000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>861000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>732000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1028000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>520000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>749000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>629000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>868000</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>138000</v>
+      </c>
+      <c r="E22" s="3">
         <v>135000</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="F22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>133000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>108000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>107000</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>109000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>110000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>105000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>59000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>103000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>93000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>150000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>83000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>77000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>85000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>104000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>117000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>124000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>3000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>148000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>156000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>163000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>168000</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>177000</v>
       </c>
       <c r="AC22" s="3">
         <v>177000</v>
       </c>
       <c r="AD22" s="3">
+        <v>177000</v>
+      </c>
+      <c r="AE22" s="3">
         <v>184000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>187000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>184000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>183000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>180000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>187000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>198000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>186000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>187000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>182000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>181000</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2654000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-676000</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="F23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-136000</v>
       </c>
-      <c r="G23" s="3">
-        <v>-225000</v>
-      </c>
       <c r="H23" s="3">
+        <v>112000</v>
+      </c>
+      <c r="I23" s="3">
         <v>4000</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>83000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-345000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>231000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>255000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>220000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>322000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>313000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>514000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>362000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>44000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>397000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>252000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>306000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>329000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>282000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>261000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-16000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>400000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>452000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>334000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>418000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>382000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>553000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>490000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>356000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>197000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>457000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-23000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>217000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>119000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>373000</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-291000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-250000</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-31000</v>
       </c>
-      <c r="G24" s="3">
-        <v>-78000</v>
-      </c>
       <c r="H24" s="3">
+        <v>24000</v>
+      </c>
+      <c r="I24" s="3">
         <v>-107000</v>
       </c>
-      <c r="I24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>27000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-61000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>39000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>33000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>48000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>148000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-575000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>96000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>95000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-5000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>59000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>46000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>88000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>176000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>50000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>67000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>94000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>262000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>137000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>128000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>106000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>145000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>119000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>130000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>89000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>13000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>136000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-87000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>73000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>54000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>107000</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,240 +2729,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2363000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-426000</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="F26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-105000</v>
       </c>
-      <c r="G26" s="3">
-        <v>-147000</v>
-      </c>
       <c r="H26" s="3">
+        <v>88000</v>
+      </c>
+      <c r="I26" s="3">
         <v>111000</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>56000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-284000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>192000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>222000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>172000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>174000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>888000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>418000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>267000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>49000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>338000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>206000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>218000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>153000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>232000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>194000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-110000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>138000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>315000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>206000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>312000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>237000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>434000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>360000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>267000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>184000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>321000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>64000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>144000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>65000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>266000</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2384000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1102000</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="F27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-105000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-147000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>150000</v>
       </c>
-      <c r="I27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>56000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-284000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>165000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>235000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>172000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-81000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>887000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>416000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>267000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-196000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>432000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>308000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>267000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>230000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>204000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>266000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-141000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>166000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>344000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>292000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>424000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>314000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>526000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>428000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>361000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>248000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>366000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>84000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>192000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>111000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,17 +3086,20 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E29" s="3">
         <v>-676000</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
       <c r="F29" s="3">
         <v>0</v>
       </c>
@@ -3047,11 +3107,11 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>-235000</v>
+      </c>
+      <c r="I29" s="3">
         <v>39000</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
         <v>0</v>
       </c>
@@ -3059,43 +3119,43 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-27000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>13000</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>-237000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>64000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>95000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>93000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>303000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>432000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>124000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>82000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>252000</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -3103,12 +3163,12 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
       <c r="AC29" s="3">
         <v>0</v>
       </c>
@@ -3116,37 +3176,40 @@
         <v>0</v>
       </c>
       <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>2000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>36000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-23000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>368000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>1212000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>29000</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-4000</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>17000</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AN29" s="3">
         <v>107000</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3324,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,19 +3443,22 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1000</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="F32" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-1000</v>
       </c>
       <c r="G32" s="3">
         <v>-1000</v>
@@ -3397,220 +3466,226 @@
       <c r="H32" s="3">
         <v>-1000</v>
       </c>
-      <c r="I32" s="3" t="s">
+      <c r="I32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-19000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1000</v>
       </c>
-      <c r="M32" s="3" t="s">
+      <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-72000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-91000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-59000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-103000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-24000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-72000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-212000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-157000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>367000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-49000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-54000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-71000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-49000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-39000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-48000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-44000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>375000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-28000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-15000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-39000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>351000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>11000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-46000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-49000</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2384000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1102000</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="F33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-105000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-147000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>150000</v>
       </c>
-      <c r="I33" s="3" t="s">
+      <c r="J33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>56000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-284000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>165000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>235000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>172000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-318000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>951000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>511000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>360000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>107000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>864000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>432000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>349000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>482000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>204000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>266000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-141000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>165000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>344000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>292000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>424000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>316000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>562000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>405000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>729000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1460000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>395000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>80000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>209000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>218000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,245 +3800,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2384000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1102000</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="F35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-105000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-147000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>150000</v>
       </c>
-      <c r="I35" s="3" t="s">
+      <c r="J35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>56000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-284000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>165000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>235000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>172000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-318000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>951000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>511000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>360000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>107000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>864000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>432000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>349000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>482000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>204000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>266000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-141000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>165000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>344000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>292000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>424000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>316000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>562000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>405000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>729000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1460000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>395000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>80000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>209000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>218000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4088,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,124 +4131,128 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1145000</v>
+      </c>
+      <c r="E41" s="3">
         <v>995000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1135000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1156000</v>
       </c>
-      <c r="G41" s="3">
-        <v>1170000</v>
-      </c>
       <c r="H41" s="3">
+        <v>1062000</v>
+      </c>
+      <c r="I41" s="3">
         <v>1159000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1049000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1070000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1113000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1149000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>746000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>636000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>804000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>511000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>826000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1031000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1295000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2122000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>706000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>787000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>595000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>678000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>847000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1239000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>511000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>697000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>787000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>641000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>589000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1026000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1073000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1141000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1018000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>998000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1041000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>998000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1033000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>2562000</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4207,19 +4296,19 @@
         <v>0</v>
       </c>
       <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>151000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>291000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>245000</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
-      </c>
       <c r="U42" s="3">
-        <v>4850000</v>
+        <v>0</v>
       </c>
       <c r="V42" s="3">
         <v>4850000</v>
@@ -4230,8 +4319,8 @@
       <c r="X42" s="3">
         <v>4850000</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>8</v>
+      <c r="Y42" s="3">
+        <v>4850000</v>
       </c>
       <c r="Z42" s="3" t="s">
         <v>8</v>
@@ -4248,8 +4337,8 @@
       <c r="AD42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE42" s="3">
-        <v>0</v>
+      <c r="AE42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF42" s="3">
         <v>0</v>
@@ -4278,472 +4367,487 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4426000</v>
+      </c>
+      <c r="E43" s="3">
         <v>4777000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5218000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5008000</v>
       </c>
-      <c r="G43" s="3">
-        <v>3362000</v>
-      </c>
       <c r="H43" s="3">
+        <v>2764000</v>
+      </c>
+      <c r="I43" s="3">
         <v>3550000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3633000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3478000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3492000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3552000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3630000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3729000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3765000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3967000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3968000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3854000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3610000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3976000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4024000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3779000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3419000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3422000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3461000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3649000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3673000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3693000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3876000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3903000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3916000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3963000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3907000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3804000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3287000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3343000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>3283000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>3078000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>2852000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>2807000</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2012000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2179000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2658000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2590000</v>
       </c>
-      <c r="G44" s="3">
-        <v>1784000</v>
-      </c>
       <c r="H44" s="3">
+        <v>1486000</v>
+      </c>
+      <c r="I44" s="3">
         <v>1795000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1728000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1771000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1889000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1929000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1911000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1939000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1942000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1976000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1897000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1746000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1814000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2053000</v>
-      </c>
-      <c r="U44" s="3">
-        <v>1828000</v>
       </c>
       <c r="V44" s="3">
         <v>1828000</v>
       </c>
       <c r="W44" s="3">
+        <v>1828000</v>
+      </c>
+      <c r="X44" s="3">
         <v>2050000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2007000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2010000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2002000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2208000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2194000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2224000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2301000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2241000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2130000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2050000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2057000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>2313000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>2465000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>2361000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>2394000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>2233000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>2222000</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2523000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2513000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>488000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>534000</v>
       </c>
-      <c r="G45" s="3">
-        <v>108000</v>
-      </c>
       <c r="H45" s="3">
+        <v>1112000</v>
+      </c>
+      <c r="I45" s="3">
         <v>139000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>147000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>140000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>114000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>150000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>189000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>239000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>259000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>168000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>204000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>262000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>132000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1745000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>818000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>923000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>322000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>331000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>281000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>325000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>247000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>467000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>501000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>217000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>250000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>199000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>242000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>258000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1659000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>405000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>552000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>251000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>851000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>512000</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10106000</v>
+      </c>
+      <c r="E46" s="3">
         <v>10464000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9499000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9288000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6424000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6643000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6557000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6459000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6608000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6780000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6476000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6615000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6770000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6622000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>7046000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>7184000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>7096000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>9896000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>12226000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>12167000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>11236000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>11288000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6599000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7215000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6639000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>7051000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>7388000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>7062000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6996000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>7318000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>7272000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>7260000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>8277000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>7211000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>7237000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>6721000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>6670000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>8103000</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4756,291 +4860,297 @@
       <c r="F47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3">
+        <v>161000</v>
+      </c>
+      <c r="J47" s="3">
+        <v>163000</v>
+      </c>
+      <c r="K47" s="3">
         <v>160000</v>
       </c>
-      <c r="H47" s="3">
-        <v>161000</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="L47" s="3">
         <v>163000</v>
       </c>
-      <c r="J47" s="3">
-        <v>160000</v>
-      </c>
-      <c r="K47" s="3">
-        <v>163000</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>184000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>183000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>187000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2480000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3215000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3214000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2888000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3026000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2983000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2888000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2972000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>3435000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>3352000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>8505000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>8463000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>8809000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>8735000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>8725000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>8844000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>8718000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>8680000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>8599000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>8546000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>7441000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>7383000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>7367000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>7348000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>7393000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>7353000</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15140000</v>
+      </c>
+      <c r="E48" s="3">
         <v>15179000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>17588000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>16721000</v>
       </c>
-      <c r="G48" s="3">
-        <v>10091000</v>
-      </c>
       <c r="H48" s="3">
+        <v>8318000</v>
+      </c>
+      <c r="I48" s="3">
         <v>10398000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10392000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10472000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10598000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10892000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10922000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10875000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10855000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10606000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>10617000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>10709000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>10824000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>12068000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>12279000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>12367000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>12987000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13120000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>13304000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>13421000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13829000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13648000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>13775000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>13887000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>13469000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>13476000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>13589000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>13788000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>13713000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>14533000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>14491000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>14520000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>13459000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>12652000</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9369000</v>
+      </c>
+      <c r="E49" s="3">
         <v>11847000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11937000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11827000</v>
       </c>
-      <c r="G49" s="3">
-        <v>3183000</v>
-      </c>
       <c r="H49" s="3">
+        <v>3110000</v>
+      </c>
+      <c r="I49" s="3">
         <v>3194000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3204000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3215000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3224000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3233000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3245000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3253000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3261000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3345000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3124000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3128000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3130000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3274000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3317000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3242000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3315000</v>
-      </c>
-      <c r="X49" s="3">
-        <v>3304000</v>
       </c>
       <c r="Y49" s="3">
         <v>3304000</v>
@@ -5049,49 +5159,52 @@
         <v>3304000</v>
       </c>
       <c r="AA49" s="3">
+        <v>3304000</v>
+      </c>
+      <c r="AB49" s="3">
         <v>3347000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3412000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3441000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3393000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3374000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3371000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3378000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3414000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3411000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>3420000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>3409000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>3402000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>3364000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>3362000</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5319,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,124 +5438,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2835000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2622000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2583000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2547000</v>
       </c>
-      <c r="G52" s="3">
-        <v>2423000</v>
-      </c>
       <c r="H52" s="3">
+        <v>4300000</v>
+      </c>
+      <c r="I52" s="3">
         <v>2523000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2492000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2462000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2430000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2632000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2618000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2603000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>574000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1077000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1281000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1249000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1167000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1250000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>738000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>729000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>745000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>776000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>807000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>812000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>847000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1002000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1018000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>992000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1019000</v>
-      </c>
-      <c r="AF52" s="3">
-        <v>958000</v>
       </c>
       <c r="AG52" s="3">
         <v>958000</v>
       </c>
       <c r="AH52" s="3">
+        <v>958000</v>
+      </c>
+      <c r="AI52" s="3">
         <v>1022000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1061000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1266000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1373000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1310000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>2207000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1131000</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,124 +5676,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>37964000</v>
+      </c>
+      <c r="E54" s="3">
         <v>40568000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>42376000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>41168000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>22800000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>23161000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>23063000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>23028000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>23261000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>23951000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>23683000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>23771000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>23940000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>24865000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>25282000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>25158000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>25243000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>29471000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>31448000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>31477000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>31718000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>31840000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>32519000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>33215000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>33471000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>33848000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>34347000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>34178000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>33576000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>33803000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>33796000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>34030000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>33903000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>33813000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>33877000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>33301000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>33093000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>32601000</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5840,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,704 +5883,723 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3902000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3818000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4336000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4224000</v>
       </c>
-      <c r="G57" s="3">
-        <v>2316000</v>
-      </c>
       <c r="H57" s="3">
+        <v>2110000</v>
+      </c>
+      <c r="I57" s="3">
         <v>2436000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2350000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2322000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2442000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2363000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2394000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2541000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2708000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2668000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2678000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2657000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2606000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2704000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2565000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2354000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2320000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2226000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2206000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2379000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2423000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2349000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2498000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2518000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2413000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2510000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2478000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2534000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2458000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2408000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>2362000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>2380000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>2199000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>2031000</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1213000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1206000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>472000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>676000</v>
       </c>
-      <c r="G58" s="3">
-        <v>349000</v>
-      </c>
       <c r="H58" s="3">
+        <v>335000</v>
+      </c>
+      <c r="I58" s="3">
         <v>413000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>410000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>287000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>291000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>271000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>400000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>510000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>763000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>616000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>293000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>197000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>196000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>233000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>116000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>31000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>29000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>179000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>33000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>664000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>168000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>402000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>676000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>809000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>639000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>555000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>684000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>587000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>311000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>958000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>824000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>454000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>239000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>78000</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1950000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2124000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1638000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1492000</v>
       </c>
-      <c r="G59" s="3">
-        <v>844000</v>
-      </c>
       <c r="H59" s="3">
+        <v>1133000</v>
+      </c>
+      <c r="I59" s="3">
         <v>867000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>881000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>867000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>829000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>878000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>888000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>865000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1529000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1521000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1381000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1288000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1342000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1761000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5954000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>6005000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>5935000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>6071000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>6091000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>6299000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>6055000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1978000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1875000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1626000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1642000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1538000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1456000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1344000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2333000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1503000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1816000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1433000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1631000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1432000</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7899000</v>
+      </c>
+      <c r="E60" s="3">
         <v>7969000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7121000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6988000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4258000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4353000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4114000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3854000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3959000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3882000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4067000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4266000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5000000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4805000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4352000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4142000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4144000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4698000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8635000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>8390000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>8284000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>8476000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>8330000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>9342000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>8646000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4729000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5049000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4953000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4694000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4603000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4618000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>4465000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>5102000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>4869000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>5002000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>4267000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>4069000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>3541000</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9325000</v>
+      </c>
+      <c r="E61" s="3">
         <v>9440000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>10169000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9652000</v>
       </c>
-      <c r="G61" s="3">
-        <v>5660000</v>
-      </c>
       <c r="H61" s="3">
+        <v>5631000</v>
+      </c>
+      <c r="I61" s="3">
         <v>5602000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5628000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5760000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5767000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5866000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5876000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5757000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4816000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4766000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5275000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5468000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5383000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8241000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7073000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7954000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>8064000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>8525000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>9432000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>9561000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>9597000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>9957000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>10050000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>9965000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>10015000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>10700000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>10805000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>10759000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>10846000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>11373000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>10392000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>10823000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>11075000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>10823000</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3566000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3492000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3446000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3464000</v>
       </c>
-      <c r="G62" s="3">
-        <v>3271000</v>
-      </c>
       <c r="H62" s="3">
+        <v>3345000</v>
+      </c>
+      <c r="I62" s="3">
         <v>3247000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3216000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3200000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3208000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3198000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3179000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3193000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5627000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5806000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6612000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6661000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6634000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>6909000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7386000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>7362000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>7502000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>7743000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>7697000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>7451000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>7510000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>11706000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>11749000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>11791000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>11484000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>11442000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>11509000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>11541000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>11414000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>12638000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>13918000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>13617000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>13590000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>14008000</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6714,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6833,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,124 +6952,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>23137000</v>
+      </c>
+      <c r="E66" s="3">
         <v>23251000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>23759000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>23076000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>14627000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>14532000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14468000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>14771000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14906000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>15069000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>15279000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>15382000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>15443000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>15377000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>16239000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>16271000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>16161000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>19849000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>23096000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>23719000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>23864000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>24747000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>25462000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>26358000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>25758000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>26407000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>26865000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>26732000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>26214000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>26763000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>26952000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>26785000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>27381000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>28899000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>29332000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>28726000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>28752000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>28392000</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7116,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7233,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7352,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7304,8 +7471,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,124 +7590,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4885000</v>
+      </c>
+      <c r="E72" s="3">
         <v>7517000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>8865000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>9038000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9393000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9705000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9719000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9386000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9491000</v>
-      </c>
-      <c r="L72" s="3">
-        <v>9938000</v>
       </c>
       <c r="M72" s="3">
         <v>9938000</v>
       </c>
       <c r="N72" s="3">
+        <v>9938000</v>
+      </c>
+      <c r="O72" s="3">
         <v>9866000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9855000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>10340000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>9557000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>9218000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>9029000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>9103000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>8442000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>8214000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>8070000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>8122000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>8123000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>8062000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>8408000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>8447000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>8302000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>8211000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>7465000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>7353000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>6988000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>6783000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>6180000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>4918000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>4717000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>4832000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>4818000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>4793000</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +7828,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +7947,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,124 +8066,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>14827000</v>
+      </c>
+      <c r="E76" s="3">
         <v>17317000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>18617000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>18092000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8173000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8629000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8595000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8257000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8355000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8882000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8404000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8389000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8497000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9488000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9043000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8887000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9082000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9622000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8352000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7758000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7854000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7093000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7057000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6857000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7713000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7441000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>7482000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>7446000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>7362000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>7040000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6844000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>7245000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>6522000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>4914000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>4545000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>4575000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>4341000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>4209000</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,245 +8304,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2384000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1102000</v>
       </c>
-      <c r="E81" s="3" t="s">
+      <c r="F81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-105000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-147000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>150000</v>
       </c>
-      <c r="I81" s="3" t="s">
+      <c r="J81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>56000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-284000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>165000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>235000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>172000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-318000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>951000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>511000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>360000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>107000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>864000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>432000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>349000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>482000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>204000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>266000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-141000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>165000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>344000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>292000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>424000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>316000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>562000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>405000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>729000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1460000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>395000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>80000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>209000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>218000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,124 +8592,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>267000</v>
+        <v>220000</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83" s="3">
         <v>269000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>257000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>249000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>235000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>232000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>240000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>250000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>256000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>250000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>251000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>261000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>267000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>261000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>277000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>318000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>306000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>309000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1287000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>320000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>312000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>323000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>343000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>327000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>321000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>315000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>338000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>335000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>330000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>325000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>348000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>373000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>357000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>345000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>328000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>314000</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +8828,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +8947,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9066,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9185,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,124 +9304,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>905000</v>
+      </c>
+      <c r="E89" s="3">
         <v>605000</v>
       </c>
-      <c r="E89" s="3" t="s">
+      <c r="F89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-288000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>397000</v>
-      </c>
-      <c r="H89" s="3">
-        <v>521000</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K89" s="3">
         <v>395000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>492000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>468000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>528000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>345000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>761000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>435000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>390000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>588000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>107000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>690000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>775000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>458000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3061000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>737000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>886000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>640000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>947000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>884000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1046000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>733000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>821000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>941000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>801000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>663000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1188000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-705000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>641000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>633000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>912000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>341000</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,124 +9468,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-650000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-455000</v>
       </c>
-      <c r="E91" s="3" t="s">
+      <c r="F91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-330000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-260000</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-212000</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J91" s="3">
+      <c r="J91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K91" s="3">
         <v>-251000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-305000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-228000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-267000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-341000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-322000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-238000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-186000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-185000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-201000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-126000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-133000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-89000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-751000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-119000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-252000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-286000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-363000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-285000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-335000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-293000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-286000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-357000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-440000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-489000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-456000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-271000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-290000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-374000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-445000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-266000</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9704,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,124 +9823,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-546000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-440000</v>
       </c>
-      <c r="E94" s="3" t="s">
+      <c r="F94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>237000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-174000</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-188000</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K94" s="3">
         <v>-247000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-310000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>245000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-264000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-339000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-315000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-76000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-37000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-180000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-130000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>5598000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>328000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>258000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-269000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>134000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-299000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-35000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-306000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-279000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-421000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-294000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-259000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-346000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-475000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-489000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-383000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-278000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-330000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-400000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-2527000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-279000</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,22 +9987,23 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>244000</v>
+      </c>
+      <c r="E96" s="3">
         <v>245000</v>
       </c>
-      <c r="E96" s="3" t="s">
+      <c r="F96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>244000</v>
-      </c>
-      <c r="G96" s="3">
-        <v>161000</v>
       </c>
       <c r="H96" s="3">
         <v>161000</v>
@@ -9778,11 +10011,11 @@
       <c r="I96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K96" s="3">
         <v>161000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>160000</v>
       </c>
       <c r="L96" s="3">
         <v>160000</v>
@@ -9791,73 +10024,73 @@
         <v>160000</v>
       </c>
       <c r="N96" s="3">
+        <v>160000</v>
+      </c>
+      <c r="O96" s="3">
         <v>162000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-164000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-165000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-170000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-174000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-178000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-199000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-201000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-202000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-806000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-202000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-201000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-202000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-201000</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-197000</v>
       </c>
       <c r="AC96" s="3">
         <v>-197000</v>
       </c>
       <c r="AD96" s="3">
-        <v>-201000</v>
+        <v>-197000</v>
       </c>
       <c r="AE96" s="3">
         <v>-201000</v>
       </c>
       <c r="AF96" s="3">
+        <v>-201000</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-195000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-196000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-197000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-196000</v>
-      </c>
-      <c r="AJ96" s="3">
-        <v>-191000</v>
       </c>
       <c r="AK96" s="3">
         <v>-191000</v>
@@ -9866,13 +10099,16 @@
         <v>-191000</v>
       </c>
       <c r="AM96" s="3">
+        <v>-191000</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-190000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-181000</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10223,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10342,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,129 +10461,135 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-153000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-302000</v>
       </c>
-      <c r="E100" s="3" t="s">
+      <c r="F100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>21000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-187000</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-223000</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K100" s="3">
         <v>-191000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-222000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-306000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-230000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-108000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-159000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-669000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-643000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-583000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2301000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-3359000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1211000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-504000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2700000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1042000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-982000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>165000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-842000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-671000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-487000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-389000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1000000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-636000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-354000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-56000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-779000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>930000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-266000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-284000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>104000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>1232000</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-25000</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>8</v>
@@ -10349,222 +10597,228 @@
       <c r="F101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G101" s="3">
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3">
         <v>4000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>4000</v>
-      </c>
-      <c r="J101" s="3">
-        <v>6000</v>
       </c>
       <c r="K101" s="3">
         <v>6000</v>
       </c>
       <c r="L101" s="3">
+        <v>6000</v>
+      </c>
+      <c r="M101" s="3">
         <v>-5000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-3000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>6000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-3000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-2000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-14000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>27000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-20000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-8000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>2000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>3000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-42000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>15000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-24000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>8000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>2000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-40000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>5000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>10000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>16000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-18000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>156000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-130000</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-12000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>11000</v>
       </c>
-      <c r="H102" s="3">
-        <v>110000</v>
-      </c>
       <c r="I102" s="3">
         <v>0</v>
       </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-43000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-36000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>403000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>38000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-96000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>293000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-315000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-293000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-176000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2326000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2915000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-81000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>192000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>84000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-169000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-392000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>728000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-186000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-90000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>146000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>52000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-437000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-47000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-68000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>123000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>20000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-43000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>43000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-35000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-1529000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>1308000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
   <si>
     <t>IP</t>
   </si>
@@ -656,530 +656,543 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5971000</v>
+      </c>
+      <c r="E8" s="3">
         <v>6006000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6222000</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="G8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="3">
+        <v>5264000</v>
+      </c>
+      <c r="I8" s="3">
+        <v>3922000</v>
+      </c>
+      <c r="J8" s="3">
+        <v>3979000</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L8" s="3">
+        <v>4619000</v>
+      </c>
+      <c r="M8" s="3">
+        <v>4601000</v>
+      </c>
+      <c r="N8" s="3">
+        <v>4613000</v>
+      </c>
+      <c r="O8" s="3">
+        <v>4682000</v>
+      </c>
+      <c r="P8" s="3">
+        <v>5020000</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>5133000</v>
+      </c>
+      <c r="R8" s="3">
+        <v>5402000</v>
+      </c>
+      <c r="S8" s="3">
+        <v>5389000</v>
+      </c>
+      <c r="T8" s="3">
+        <v>5237000</v>
+      </c>
+      <c r="U8" s="3">
+        <v>5086000</v>
+      </c>
+      <c r="V8" s="3">
+        <v>4914000</v>
+      </c>
+      <c r="W8" s="3">
+        <v>4770000</v>
+      </c>
+      <c r="X8" s="3">
+        <v>4593000</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>17565000</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>5123000</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>4866000</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>5352000</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>5498000</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>5568000</v>
+      </c>
+      <c r="AE8" s="3">
+        <v>5667000</v>
+      </c>
+      <c r="AF8" s="3">
+        <v>5643000</v>
+      </c>
+      <c r="AG8" s="3">
+        <v>5951000</v>
+      </c>
+      <c r="AH8" s="3">
         <v>5901000</v>
       </c>
-      <c r="H8" s="3">
-        <v>3922000</v>
-      </c>
-      <c r="I8" s="3">
-        <v>3979000</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K8" s="3">
-        <v>4619000</v>
-      </c>
-      <c r="L8" s="3">
-        <v>4601000</v>
-      </c>
-      <c r="M8" s="3">
-        <v>4613000</v>
-      </c>
-      <c r="N8" s="3">
-        <v>4682000</v>
-      </c>
-      <c r="O8" s="3">
-        <v>5020000</v>
-      </c>
-      <c r="P8" s="3">
-        <v>5133000</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>5402000</v>
-      </c>
-      <c r="R8" s="3">
-        <v>5389000</v>
-      </c>
-      <c r="S8" s="3">
-        <v>5237000</v>
-      </c>
-      <c r="T8" s="3">
-        <v>5086000</v>
-      </c>
-      <c r="U8" s="3">
-        <v>4914000</v>
-      </c>
-      <c r="V8" s="3">
-        <v>4770000</v>
-      </c>
-      <c r="W8" s="3">
-        <v>4593000</v>
-      </c>
-      <c r="X8" s="3">
-        <v>17565000</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>5123000</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>4866000</v>
-      </c>
-      <c r="AA8" s="3">
-        <v>5352000</v>
-      </c>
-      <c r="AB8" s="3">
-        <v>5498000</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>5568000</v>
-      </c>
-      <c r="AD8" s="3">
-        <v>5667000</v>
-      </c>
-      <c r="AE8" s="3">
-        <v>5643000</v>
-      </c>
-      <c r="AF8" s="3">
-        <v>5951000</v>
-      </c>
-      <c r="AG8" s="3">
-        <v>5901000</v>
-      </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5833000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>5621000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>5711000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>5517000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>5383000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>5132000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>3797000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>5266000</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4244000</v>
+      </c>
+      <c r="E9" s="3">
         <v>4092000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4280000</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G9" s="3">
-        <v>4259000</v>
+      <c r="G9" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H9" s="3">
+        <v>3735000</v>
+      </c>
+      <c r="I9" s="3">
         <v>2688000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2873000</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L9" s="3">
         <v>3414000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3246000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3316000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3360000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3642000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3668000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3830000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3806000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3839000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3659000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3423000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3402000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3348000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>12339000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3541000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3427000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3732000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3669000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3766000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3902000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3932000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3800000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3889000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3923000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3946000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>3702000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>3705000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>3749000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>3635000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>2712000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>3622000</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1727000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1914000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1942000</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1642000</v>
+      <c r="G10" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H10" s="3">
+        <v>1529000</v>
+      </c>
+      <c r="I10" s="3">
         <v>1234000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1106000</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="K10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L10" s="3">
         <v>1205000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1355000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1297000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1322000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1378000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1465000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1572000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1583000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1398000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1427000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1491000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1368000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1245000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>5226000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1582000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1439000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1620000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1829000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1802000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1765000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1711000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2151000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2012000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1910000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1675000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2009000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1812000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1634000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1497000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1085000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1644000</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1221,8 +1234,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1340,8 +1354,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1459,246 +1476,255 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E14" s="3">
         <v>2948000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1055000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3">
-        <v>213000</v>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H14" s="3">
+        <v>384000</v>
+      </c>
+      <c r="I14" s="3">
         <v>424000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>62000</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>23000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>557000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>29000</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
         <v>72000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>93000</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>266000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-321000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>165000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>32000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>660000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>100000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>26000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>352000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>88000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>61000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>152000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-7000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-19000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>122000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>26000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>22000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>83000</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
       <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3">
         <v>347000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>-6000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>7000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>51000</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>473000</v>
+      </c>
+      <c r="E15" s="3">
         <v>611000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>424000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>480000</v>
       </c>
-      <c r="G15" s="3">
-        <v>374000</v>
-      </c>
       <c r="H15" s="3">
+        <v>323000</v>
+      </c>
+      <c r="I15" s="3">
         <v>-12000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>208000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>261000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>273000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>267000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>258000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>244000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>241000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>251000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>261000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>267000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>261000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>277000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>280000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>272000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>268000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1091000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>320000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>312000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>323000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>343000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>327000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>321000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>315000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>338000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>335000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>330000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>325000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>339000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>350000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>334000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>320000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>225000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>314000</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1737,246 +1763,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5749000</v>
+      </c>
+      <c r="E17" s="3">
         <v>5617000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5757000</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G17" s="3">
-        <v>5742000</v>
+      <c r="G17" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H17" s="3">
+        <v>4951000</v>
+      </c>
+      <c r="I17" s="3">
         <v>3327000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3860000</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="3">
         <v>4465000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4318000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4294000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4368000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4737000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4790000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5030000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4851000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4901000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4981000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4485000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4613000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4320000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>16866000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4742000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4503000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5276000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4979000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4978000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5204000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5085000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5007000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5192000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5175000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>5124000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4976000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>4851000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>5223000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>4732000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>3542000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>4761000</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>222000</v>
+      </c>
+      <c r="E18" s="3">
         <v>389000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>465000</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G18" s="3">
-        <v>159000</v>
+      <c r="G18" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H18" s="3">
+        <v>313000</v>
+      </c>
+      <c r="I18" s="3">
         <v>595000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>119000</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="3">
         <v>154000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>283000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>319000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>314000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>283000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>343000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>372000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>538000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>336000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>105000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>429000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>157000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>273000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>699000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>381000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>363000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>76000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>519000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>590000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>463000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>558000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>944000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>709000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>658000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>497000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>735000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>666000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>160000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>400000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>255000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>505000</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2018,22 +2051,23 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>1000</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G20" s="3">
-        <v>1000</v>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H20" s="3">
         <v>1000</v>
@@ -2041,580 +2075,595 @@
       <c r="I20" s="3">
         <v>1000</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="J20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3">
         <v>2000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>19000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1000</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="3">
         <v>1000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>72000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>91000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>59000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>103000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>24000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>72000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>212000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>157000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-367000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>49000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>54000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>71000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>49000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>39000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>48000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>44000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-375000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>28000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>15000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>39000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-351000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-11000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>3000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>4000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>46000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>49000</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>695000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1000000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>888000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>480000</v>
       </c>
-      <c r="G21" s="3">
-        <v>532000</v>
-      </c>
       <c r="H21" s="3">
+        <v>635000</v>
+      </c>
+      <c r="I21" s="3">
         <v>582000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>326000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>261000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>425000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>531000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>576000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>558000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>523000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>666000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>724000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>864000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>700000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>406000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>819000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>675000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>739000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1619000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>750000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>729000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>470000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>911000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>956000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>832000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>917000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>907000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1072000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1003000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>861000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>732000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1028000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>520000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>749000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>629000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>868000</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>132000</v>
+      </c>
+      <c r="E22" s="3">
         <v>138000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>135000</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G22" s="3">
-        <v>133000</v>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H22" s="3">
+        <v>135000</v>
+      </c>
+      <c r="I22" s="3">
         <v>108000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>107000</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="3">
         <v>109000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>110000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>105000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>59000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>103000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>93000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>150000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>83000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>77000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>85000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>104000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>117000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>124000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>3000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>148000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>156000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>163000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>168000</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>177000</v>
       </c>
       <c r="AD22" s="3">
         <v>177000</v>
       </c>
       <c r="AE22" s="3">
+        <v>177000</v>
+      </c>
+      <c r="AF22" s="3">
         <v>184000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>187000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>184000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>183000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>180000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>187000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>198000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>186000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>187000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>182000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>181000</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>93000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2654000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-676000</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-136000</v>
+      <c r="G23" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H23" s="3">
+        <v>-156000</v>
+      </c>
+      <c r="I23" s="3">
         <v>112000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4000</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="3">
         <v>83000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-345000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>231000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>255000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>220000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>322000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>313000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>514000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>362000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>44000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>397000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>252000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>306000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>329000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>282000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>261000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-16000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>400000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>452000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>334000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>418000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>382000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>553000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>490000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>356000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>197000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>457000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-23000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>217000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>119000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>373000</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-291000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-250000</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G24" s="3">
-        <v>-31000</v>
+      <c r="G24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H24" s="3">
+        <v>-32000</v>
+      </c>
+      <c r="I24" s="3">
         <v>24000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-107000</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="3">
         <v>27000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-61000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>39000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>33000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>48000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>148000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-575000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>96000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>95000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-5000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>59000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>46000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>88000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>176000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>50000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>67000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>94000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>262000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>137000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>128000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>106000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>145000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>119000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>130000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>89000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>13000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>136000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-87000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>73000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>54000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>107000</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2732,246 +2781,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>76000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2363000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-426000</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-105000</v>
+      <c r="G26" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H26" s="3">
+        <v>-124000</v>
+      </c>
+      <c r="I26" s="3">
         <v>88000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>111000</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L26" s="3">
         <v>56000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-284000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>192000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>222000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>172000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>174000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>888000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>418000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>267000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>49000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>338000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>206000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>218000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>153000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>232000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>194000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-110000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>138000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>315000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>206000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>312000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>237000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>434000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>360000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>267000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>184000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>321000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>64000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>144000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>65000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>266000</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>60000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2384000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1102000</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="G27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H27" s="3">
         <v>-105000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-147000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>150000</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L27" s="3">
         <v>56000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-284000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>165000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>235000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>172000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-81000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>887000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>416000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>267000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-196000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>432000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>308000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>267000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>230000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>204000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>266000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-141000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>166000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>344000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>292000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>424000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>314000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>526000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>428000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>361000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>248000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>366000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>84000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>192000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>111000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3089,32 +3147,35 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E29" s="3">
         <v>-21000</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-676000</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
       <c r="G29" s="3">
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>19000</v>
+      </c>
+      <c r="I29" s="3">
         <v>-235000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>39000</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
         <v>0</v>
       </c>
@@ -3122,56 +3183,56 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-27000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>13000</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>-237000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>64000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>95000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>93000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>303000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>432000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>124000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>82000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>252000</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
       <c r="AD29" s="3">
         <v>0</v>
       </c>
@@ -3179,37 +3240,40 @@
         <v>0</v>
       </c>
       <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
         <v>2000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>36000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-23000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>368000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>1212000</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>29000</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>-4000</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AN29" s="3">
         <v>17000</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>107000</v>
       </c>
-      <c r="AO29" s="3">
+      <c r="AP29" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3327,8 +3391,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3446,22 +3513,25 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1000</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-1000</v>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H32" s="3">
         <v>-1000</v>
@@ -3469,223 +3539,229 @@
       <c r="I32" s="3">
         <v>-1000</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="J32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3">
         <v>-2000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-19000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1000</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P32" s="3">
         <v>-1000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-72000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-91000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-59000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-103000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-24000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-72000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-212000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-157000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>367000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-49000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-54000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-71000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-49000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-39000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-48000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-44000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>375000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-28000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-15000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-39000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>351000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>11000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-46000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-49000</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>60000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2384000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1102000</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="G33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H33" s="3">
         <v>-105000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-147000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>150000</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L33" s="3">
         <v>56000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-284000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>165000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>235000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>172000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-318000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>951000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>511000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>360000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>107000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>864000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>432000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>349000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>482000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>204000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>266000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-141000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>165000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>344000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>292000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>424000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>316000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>562000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>405000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>729000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1460000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>395000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>80000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>209000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>218000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3803,251 +3879,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>60000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2384000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1102000</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="G35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H35" s="3">
         <v>-105000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-147000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>150000</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L35" s="3">
         <v>56000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-284000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>165000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>235000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>172000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-318000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>951000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>511000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>360000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>107000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>864000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>432000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>349000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>482000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>204000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>266000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-141000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>165000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>344000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>292000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>424000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>316000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>562000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>405000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>729000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1460000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>395000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>80000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>209000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>218000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4089,8 +4174,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4132,127 +4218,131 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1236000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1145000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>995000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1135000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1156000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1062000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1159000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1049000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1070000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1113000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1149000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>746000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>636000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>804000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>511000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>826000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1031000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1295000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2122000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>706000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>787000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>595000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>678000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>847000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1239000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>511000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>697000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>787000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>641000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>589000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1026000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1073000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1141000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1018000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>998000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1041000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>998000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1033000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>2562000</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4299,19 +4389,19 @@
         <v>0</v>
       </c>
       <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
         <v>151000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>291000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>245000</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
-      </c>
       <c r="V42" s="3">
-        <v>4850000</v>
+        <v>0</v>
       </c>
       <c r="W42" s="3">
         <v>4850000</v>
@@ -4322,8 +4412,8 @@
       <c r="Y42" s="3">
         <v>4850000</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>8</v>
+      <c r="Z42" s="3">
+        <v>4850000</v>
       </c>
       <c r="AA42" s="3" t="s">
         <v>8</v>
@@ -4340,8 +4430,8 @@
       <c r="AE42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF42" s="3">
-        <v>0</v>
+      <c r="AF42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG42" s="3">
         <v>0</v>
@@ -4370,484 +4460,499 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4692000</v>
+      </c>
+      <c r="E43" s="3">
         <v>4426000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4777000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5218000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5008000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2764000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3550000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3633000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3478000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3492000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3552000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3630000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3729000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3765000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3967000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3968000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3854000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3610000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3976000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4024000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3779000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3419000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3422000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3461000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3649000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3673000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3693000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3876000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3903000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3916000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3963000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3907000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3804000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3287000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>3343000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>3283000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>3078000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>2852000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>2807000</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1902000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2012000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2179000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2658000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2590000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1486000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1795000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1728000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1771000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1889000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1929000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1911000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1939000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1942000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1976000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1897000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1746000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1814000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2053000</v>
-      </c>
-      <c r="V44" s="3">
-        <v>1828000</v>
       </c>
       <c r="W44" s="3">
         <v>1828000</v>
       </c>
       <c r="X44" s="3">
+        <v>1828000</v>
+      </c>
+      <c r="Y44" s="3">
         <v>2050000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2007000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2010000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2002000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2208000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2194000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2224000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2301000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2241000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2130000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2050000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>2057000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>2313000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>2465000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>2361000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>2394000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>2233000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>2222000</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>687000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2523000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2513000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>488000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>534000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1112000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>139000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>147000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>140000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>114000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>150000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>189000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>239000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>259000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>168000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>204000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>262000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>132000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1745000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>818000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>923000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>322000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>331000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>281000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>325000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>247000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>467000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>501000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>217000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>250000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>199000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>242000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>258000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1659000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>405000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>552000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>251000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>851000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>512000</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8580000</v>
+      </c>
+      <c r="E46" s="3">
         <v>10106000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>10464000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9499000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9288000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6424000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6643000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6557000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6459000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6608000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6780000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6476000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6615000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6770000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6622000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>7046000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>7184000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>7096000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>9896000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>12226000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>12167000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>11236000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>11288000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6599000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>7215000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6639000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>7051000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>7388000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>7062000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>6996000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>7318000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>7272000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>7260000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>8277000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>7211000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>7237000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>6721000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>6670000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>8103000</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4866,294 +4971,300 @@
       <c r="H47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3">
         <v>161000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>163000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>160000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>163000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>184000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>183000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>187000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2480000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3215000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3214000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2888000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3026000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2983000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2888000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>2972000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>3435000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>3352000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>8505000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>8463000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>8809000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>8735000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>8725000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>8844000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>8718000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>8680000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>8599000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>8546000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>7441000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>7383000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>7367000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>7348000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>7393000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>7353000</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>14904000</v>
+      </c>
+      <c r="E48" s="3">
         <v>15140000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>15179000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>17588000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>16721000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8318000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10398000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10392000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10472000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10598000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10892000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10922000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10875000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10855000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>10606000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>10617000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>10709000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>10824000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>12068000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>12279000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>12367000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>12987000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>13120000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>13304000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13421000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13829000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>13648000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>13775000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>13887000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>13469000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>13476000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>13589000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>13788000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>13713000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>14533000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>14491000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>14520000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>13459000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>12652000</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9357000</v>
+      </c>
+      <c r="E49" s="3">
         <v>9369000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11847000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11937000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11827000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3110000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3194000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3204000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3215000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3224000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3233000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3245000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3253000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3261000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3345000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3124000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3128000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3130000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3274000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3317000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3242000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3315000</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>3304000</v>
       </c>
       <c r="Z49" s="3">
         <v>3304000</v>
@@ -5162,49 +5273,52 @@
         <v>3304000</v>
       </c>
       <c r="AB49" s="3">
+        <v>3304000</v>
+      </c>
+      <c r="AC49" s="3">
         <v>3347000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3412000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3441000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3393000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3374000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3371000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3378000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3414000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>3411000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>3420000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>3409000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>3402000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>3364000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>3362000</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5322,8 +5436,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5441,127 +5558,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2921000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2835000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2622000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2583000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2547000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4300000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2523000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2492000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2462000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2430000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2632000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2618000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2603000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>574000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1077000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1281000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1249000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1167000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1250000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>738000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>729000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>745000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>776000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>807000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>812000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>847000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1002000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1018000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>992000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1019000</v>
-      </c>
-      <c r="AG52" s="3">
-        <v>958000</v>
       </c>
       <c r="AH52" s="3">
         <v>958000</v>
       </c>
       <c r="AI52" s="3">
+        <v>958000</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>1022000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1061000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1266000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1373000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1310000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>2207000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>1131000</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5679,127 +5802,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>36434000</v>
+      </c>
+      <c r="E54" s="3">
         <v>37964000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>40568000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>42376000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>41168000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>22800000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>23161000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>23063000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>23028000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>23261000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>23951000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>23683000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>23771000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>23940000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>24865000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>25282000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>25158000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>25243000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>29471000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>31448000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>31477000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>31718000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>31840000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>32519000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>33215000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>33471000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>33848000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>34347000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>34178000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>33576000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>33803000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>33796000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>34030000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>33903000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>33813000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>33877000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>33301000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>33093000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>32601000</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5841,8 +5970,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5884,722 +6014,741 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3833000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3902000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3818000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4336000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4224000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2110000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2436000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2350000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2322000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2442000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2363000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2394000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2541000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2708000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2668000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2678000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2657000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2606000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2704000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2565000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2354000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2320000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2226000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2206000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2379000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2423000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2349000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2498000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2518000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2413000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2510000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2478000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2534000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2458000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>2408000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>2362000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>2380000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>2199000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>2031000</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1134000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1213000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1206000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>472000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>676000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>335000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>413000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>410000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>287000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>291000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>271000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>400000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>510000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>763000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>616000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>293000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>197000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>196000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>233000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>116000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>31000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>29000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>179000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>33000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>664000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>168000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>402000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>676000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>809000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>639000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>555000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>684000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>587000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>311000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>958000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>824000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>454000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>239000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>78000</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1413000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1950000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2124000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1638000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1492000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1133000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>867000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>881000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>867000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>829000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>878000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>888000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>865000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1529000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1521000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1381000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1288000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1342000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1761000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5954000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>6005000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5935000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>6071000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>6091000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>6299000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>6055000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1978000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1875000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1626000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1642000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1538000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1456000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1344000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2333000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1503000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1816000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1433000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1631000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>1432000</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7073000</v>
+      </c>
+      <c r="E60" s="3">
         <v>7899000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7969000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7121000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6988000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4258000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4353000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4114000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3854000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3959000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3882000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4067000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4266000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5000000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4805000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4352000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4142000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4144000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4698000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>8635000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>8390000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>8284000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>8476000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>8330000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>9342000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>8646000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4729000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5049000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4953000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4694000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4603000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>4618000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>4465000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>5102000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>4869000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>5002000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>4267000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>4069000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>3541000</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8625000</v>
+      </c>
+      <c r="E61" s="3">
         <v>9325000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9440000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10169000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>9652000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5631000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5602000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5628000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5760000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5767000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5866000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5876000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5757000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4816000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4766000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5275000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5468000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5383000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>8241000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7073000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>7954000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>8064000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>8525000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>9432000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>9561000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>9597000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>9957000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>10050000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>9965000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>10015000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>10700000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>10805000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>10759000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>10846000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>11373000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>10392000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>10823000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>11075000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>10823000</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3537000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3566000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3492000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3446000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3464000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3345000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3247000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3216000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3200000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3208000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3198000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3179000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3193000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5627000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5806000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6612000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6661000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>6634000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>6909000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>7386000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>7362000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>7502000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>7743000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>7697000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>7451000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>7510000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>11706000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>11749000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>11791000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>11484000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>11442000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>11509000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>11541000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>11414000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>12638000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>13918000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>13617000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>13590000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>14008000</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6717,8 +6866,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6836,8 +6988,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6955,127 +7110,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>21626000</v>
+      </c>
+      <c r="E66" s="3">
         <v>23137000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>23251000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>23759000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>23076000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>14627000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14532000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>14468000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14771000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14906000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>15069000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>15279000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>15382000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>15443000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>15377000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>16239000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>16271000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>16161000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>19849000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>23096000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>23719000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>23864000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>24747000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>25462000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>26358000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>25758000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>26407000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>26865000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>26732000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>26214000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>26763000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>26952000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>26785000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>27381000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>28899000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>29332000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>28726000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>28752000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>28392000</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7117,8 +7278,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7236,8 +7398,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7355,8 +7520,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7474,8 +7642,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7593,127 +7764,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4699000</v>
+      </c>
+      <c r="E72" s="3">
         <v>4885000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7517000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>8865000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9038000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9393000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9705000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9719000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9386000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9491000</v>
-      </c>
-      <c r="M72" s="3">
-        <v>9938000</v>
       </c>
       <c r="N72" s="3">
         <v>9938000</v>
       </c>
       <c r="O72" s="3">
+        <v>9938000</v>
+      </c>
+      <c r="P72" s="3">
         <v>9866000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9855000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>10340000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>9557000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>9218000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>9029000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>9103000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>8442000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>8214000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>8070000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>8122000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>8123000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>8062000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>8408000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>8447000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>8302000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>8211000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>7465000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>7353000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>6988000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>6783000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>6180000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>4918000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>4717000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>4832000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>4818000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>4793000</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7831,8 +8008,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7950,8 +8130,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8069,127 +8252,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>14808000</v>
+      </c>
+      <c r="E76" s="3">
         <v>14827000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>17317000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>18617000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>18092000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8173000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8629000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8595000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8257000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8355000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8882000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8404000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8389000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8497000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9488000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9043000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8887000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9082000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9622000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>8352000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7758000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7854000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7093000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7057000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6857000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7713000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>7441000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>7482000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>7446000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>7362000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>7040000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6844000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>7245000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>6522000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>4914000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>4545000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>4575000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>4341000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>4209000</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8307,251 +8496,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>60000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2384000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1102000</v>
       </c>
-      <c r="F81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="G81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H81" s="3">
         <v>-105000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-147000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>150000</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L81" s="3">
         <v>56000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-284000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>165000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>235000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>172000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-318000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>951000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>511000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>360000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>107000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>864000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>432000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>349000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>482000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>204000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>266000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-141000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>165000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>344000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>292000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>424000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>316000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>562000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>405000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>729000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1460000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>395000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>80000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>209000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>218000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>312000</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8593,127 +8791,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>275000</v>
+      </c>
+      <c r="E83" s="3">
         <v>220000</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G83" s="3">
+      <c r="G83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H83" s="3">
         <v>269000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>257000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>249000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>235000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>232000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>240000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>250000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>256000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>250000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>251000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>261000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>267000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>261000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>277000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>318000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>306000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>309000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1287000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>320000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>312000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>323000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>343000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>327000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>321000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>315000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>338000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>335000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>330000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>325000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>348000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>373000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>357000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>345000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>328000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>314000</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8831,8 +9033,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8950,8 +9155,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9069,8 +9277,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9188,8 +9399,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9307,127 +9521,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>611000</v>
+      </c>
+      <c r="E89" s="3">
         <v>905000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>605000</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G89" s="3">
+      <c r="G89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H89" s="3">
         <v>-288000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>397000</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L89" s="3">
         <v>395000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>492000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>468000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>528000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>345000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>761000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>435000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>390000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>588000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>107000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>690000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>775000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>458000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>3061000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>737000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>886000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>640000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>947000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>884000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1046000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>733000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>821000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>941000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>801000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>663000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1188000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-705000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>641000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>633000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>912000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>341000</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9469,127 +9689,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-517000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-650000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-455000</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="G91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3">
         <v>-330000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-260000</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L91" s="3">
         <v>-251000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-305000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-228000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-267000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-341000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-322000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-238000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-186000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-185000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-201000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-126000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-133000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-89000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-751000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-119000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-252000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-286000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-363000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-285000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-335000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-293000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-286000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-357000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-440000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-489000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-456000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-271000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-290000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-374000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-445000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-266000</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9707,8 +9931,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9826,127 +10053,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>565000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-546000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-440000</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="G94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H94" s="3">
         <v>237000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-174000</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K94" s="3">
+      <c r="K94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L94" s="3">
         <v>-247000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-310000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>245000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-264000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-339000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-315000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-76000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-37000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-180000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-130000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>5598000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>328000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>258000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-269000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>134000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-299000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-35000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-306000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-279000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-421000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-294000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-259000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-346000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-475000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-489000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-383000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-278000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-330000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-400000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-2527000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-279000</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9988,37 +10221,38 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>245000</v>
+      </c>
+      <c r="E96" s="3">
         <v>244000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>245000</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G96" s="3">
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3">
         <v>244000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>161000</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3">
         <v>161000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>160000</v>
       </c>
       <c r="M96" s="3">
         <v>160000</v>
@@ -10027,73 +10261,73 @@
         <v>160000</v>
       </c>
       <c r="O96" s="3">
+        <v>160000</v>
+      </c>
+      <c r="P96" s="3">
         <v>162000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-164000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-165000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-170000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-174000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-178000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-199000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-201000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-202000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-806000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-202000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-201000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-202000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-201000</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-197000</v>
       </c>
       <c r="AD96" s="3">
         <v>-197000</v>
       </c>
       <c r="AE96" s="3">
-        <v>-201000</v>
+        <v>-197000</v>
       </c>
       <c r="AF96" s="3">
         <v>-201000</v>
       </c>
       <c r="AG96" s="3">
+        <v>-201000</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-195000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-196000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-197000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-196000</v>
-      </c>
-      <c r="AK96" s="3">
-        <v>-191000</v>
       </c>
       <c r="AL96" s="3">
         <v>-191000</v>
@@ -10102,13 +10336,16 @@
         <v>-191000</v>
       </c>
       <c r="AN96" s="3">
+        <v>-191000</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-190000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-181000</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10226,8 +10463,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10345,8 +10585,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10464,361 +10707,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1019000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-153000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-302000</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="G100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H100" s="3">
         <v>21000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-187000</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L100" s="3">
         <v>-191000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-222000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-306000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-230000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-108000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-159000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-669000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-643000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-583000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2301000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-3359000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1211000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-504000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2700000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1042000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-982000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>165000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-842000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-671000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-487000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-389000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1000000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-636000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-354000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-56000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-779000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>930000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-266000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-284000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>104000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>1232000</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-25000</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F101" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3">
         <v>4000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-4000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>4000</v>
-      </c>
-      <c r="K101" s="3">
-        <v>6000</v>
       </c>
       <c r="L101" s="3">
         <v>6000</v>
       </c>
       <c r="M101" s="3">
+        <v>6000</v>
+      </c>
+      <c r="N101" s="3">
         <v>-5000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>6000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-5000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-3000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-2000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-14000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>27000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-20000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>2000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>3000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-42000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>15000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-24000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>8000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>2000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>1000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-40000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>5000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>10000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>16000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-18000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>146000</v>
+      </c>
+      <c r="E102" s="3">
         <v>156000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-130000</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-12000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>11000</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-43000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-36000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>403000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>38000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-96000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>293000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-315000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-293000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-176000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2326000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2915000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-81000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>192000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>84000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-169000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-392000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>728000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-186000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-90000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>146000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>52000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-437000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-47000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-68000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>123000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>20000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-43000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>43000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-35000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-1529000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>1308000</v>
       </c>
     </row>
